--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -9,13 +9,16 @@
   <sheets>
     <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="全部节点" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="生态酵母谱系" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="历史时间线" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="势力格局" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="存在体谱系" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="燃料闭环" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="讽刺主题链" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="叙事入口" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="殖民星球" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="污染起源方案" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="十三月 Undecimber" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="生态酵母谱系" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="历史时间线" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="势力格局" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="存在体谱系" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="燃料闭环" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="讽刺主题链" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="叙事入口" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -516,198 +519,1087 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15-v1</t>
+          <t>2026-07-16-v2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>星球</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>赛博西部 / 生物朋克（Weird West + Biopunk）</t>
+          <t>垦锈带 Calico Reach（地球联邦边境殖民星）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>当前时间线</t>
+          <t>当前</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>垦历 C.Y. 42 · 十三月 Undecimber</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>命名</t>
+          <t>污染主干</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>井 = 井源计划 / 净水本意；瓶 = 醇民 / 铁瓶 / 酿民 / 容器化生存</t>
+          <t>方案 A 深井毒卤 + 方案 B 流浪赤潮</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>核心讽刺</t>
+          <t>命名</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>本意为掘井求生，结果为造瓶产油</t>
+          <t>井 = 井源计划 / 净水本意；瓶 = 醇民 / 铁瓶 / 酿民 / 容器化生存</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>关联文档</t>
+          <t>核心讽刺</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>docs/worldbuilding-tree.md</t>
+          <t>本意为掘井求生，结果为造瓶产油</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>关联文档</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>docs/worldbuilding-tree.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>工作表说明</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>各模块支持 Excel 行折叠（点击行号左侧 − / +）</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>模块统计</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>节点数</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>生态酵母谱系</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>势力格局</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>叙事入口</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B23" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>生态酵母主干（速览）</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>生态酵母 → W-Strain → 井源计划 → 井兵 → 井醒
-         → R-Strain → 生态酿（2–4%）
-         → F-Strain → 醇民 Gen-0 → 铁瓶 Gen-1 → 酿民 Gen-2 → 瓶醒</t>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>垦锈带 Calico Reach → 深井毒卤 + Undecimber 赤潮
+生态酵母 → W-Strain → 井兵 | R-Strain → 生态酿 | F-Strain → 铁瓶 → 酿民
+垦历 C.Y. 42 Undecimber：水质最差 · 觉醒临界 · 酒镇风暴季</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B10:G10"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B5:G5"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="B4:G4"/>
-    <mergeCell ref="A23:G23"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与井》· 燃料闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>英文名</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>父节点</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>时期</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>▸ 燃料闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" outlineLevel="1">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Fuel Perpetual Loop</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶计划遗产</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" outlineLevel="1">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>输入层</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Input Layer</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>毒水、玉米浆、仙人掌糖浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>运输层</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Transport Layer</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 25–</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>饲料搬运者 Dust Walker</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>生产层</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Production Layer</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶 Synth-Bottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" outlineLevel="1">
+      <c r="A9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>一次发酵</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Primary Fermentation</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>生产层</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>生态酿 2–4% 副产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" outlineLevel="1">
+      <c r="A10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>二次发酵</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Secondary Fermentation</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>生产层</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>燃料乙醇 40%+ 主产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>输出层</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Output Layer</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>机车、发电机、营地、Saloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>闭环裂缝</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Loop Fracture</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>二次发酵阈值，酿民觉醒</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与井》· 讽刺主题链</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>英文名</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>父节点</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>时期</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>▸ 讽刺主题链</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" outlineLevel="1">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Survival Obsession</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>无论如何都要活下去</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" outlineLevel="1">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>士兵净水</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Soldiers Purify Water</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 12–</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>最正当的起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>人体验证</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Human Vessel Proven</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 14–</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>技术门槛跨越</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>贫民燃料化</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Poor as Fuel</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 15–</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>对象降级，话术不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" outlineLevel="1">
+      <c r="A9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>人道抗争</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Humanitarian Protest</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 20–</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>别把人变成瓶子</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" outlineLevel="1">
+      <c r="A10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶妥协</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Synth-Bottle Compromise</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>机械燃料，解放人性</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>机械量产</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Mass Production</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 30–</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>人性换效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>酿民觉醒</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Brewfolk Awakening</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>容器发问，闭环裂缝</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与井》· 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>英文名</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>父节点</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>时期</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>▸ 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" outlineLevel="1">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>井兵末裔</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Well-Soldier Scion</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>W-Strain 残留，各方追逐</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" outlineLevel="1">
+      <c r="A6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>刚觉醒酿民</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Newly Awakened Brewfolk</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>意识到自己是净水者也是油箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>鏽釘</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Rust Nail</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>赏金猎人，禁忌井兵委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Saloon 酒保</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Saloon Bartender</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>半觉醒老旧铁瓶</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" outlineLevel="1">
+      <c r="A9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>酿造帮档案员</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Cartel Archivist</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>发现抗议领袖在铁瓶合同上</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -719,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -778,7 +1670,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
@@ -786,12 +1678,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>生态酵母（基础株）</t>
+          <t>垦锈带 Calico Reach</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Saccharomyces vitae</t>
+          <t>Calico Reach</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -801,19 +1693,19 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>2047–</t>
+          <t>C.Y. 0–</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>基因改造酵母，可利用毒水发酵</t>
+          <t>地球联邦第三序列边境殖民星球</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
@@ -821,454 +1713,454 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>W-Strain</t>
+          <t>星球特征</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>W-Strain (Military)</t>
+          <t>Planet Traits</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>生态酵母</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>军用稳态型</t>
+          <t>双恒星、干燥荒原、深井采水、稀薄大气</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>井源计划</t>
+          <t>殖民形态</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Wellspring Program</t>
+          <t>Colonial Form</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>W-Strain</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>C.Y. 0–</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>第一批植入者为净水超级士兵</t>
+          <t>财团殖民、边境新西部、公司法自治</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>净水士兵（井兵）</t>
+          <t>垦历 C.Y.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Aqua-Soldiers</t>
+          <t>Colonial Year</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>井源计划</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>C.Y. 0–</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>毒水→内源生态酿 2–4%</t>
+          <t>殖民年号，替代地球公历</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>井醒</t>
+          <t>标准十二月</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Well-Awake</t>
+          <t>Standard Twelve Months</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>净水士兵</t>
+          <t>垦历</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>W-Strain 残留 / 幸存井兵</t>
+          <t>沿用地球月份名便于行政</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>R-Strain</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>R-Strain (Civilian)</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>生态酵母</t>
+          <t>垦历</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>2049–</t>
+          <t>每年</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>民用救灾型</t>
+          <t>闰余月 37 垦日，账外之月</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>殖民星球</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>生态酿</t>
+          <t>当前时点</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Eco-Brew</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>R-Strain</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>2049–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>2–4%，公开合法，社会认知「酵母=希望」</t>
+          <t>Undecimber 中旬，酒镇风暴季</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>F-Strain</t>
+          <t>方案 A 深井毒卤</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>F-Strain (Fuel)</t>
+          <t>Deep-Brine Toxicity</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>生态酵母</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>推荐主干</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>燃料高产型</t>
+          <t>高氯酸盐/砷/铜卤层，深井采水全域污染</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>活燃料计划</t>
+          <t>Undecimber 卤压峰值</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Living Fuel Program</t>
+          <t>Undecimber Brine Peak</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>F-Strain</t>
+          <t>方案 A</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>2050–2058</t>
+          <t>每年</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>人体活体发酵容器</t>
+          <t>地下卤层渗透率年度最高</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>醇民 Gen-0</t>
+          <t>方案 B 流浪赤潮</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Gen-0</t>
+          <t>Wandering Red Tide</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>活燃料计划</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>2050–2058</t>
+          <t>推荐叠加</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>血肉容器，已基本灭绝</t>
+          <t>本土嗜盐菌季节性神经毒素</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>铁瓶计划</t>
+          <t>赤潮高峰</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Synth-Bottle Program</t>
+          <t>Red Tide Peak</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>F-Strain</t>
+          <t>方案 B</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>2058–2065</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>菌株移植至机械载体</t>
+          <t>全年水质最差月份</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>方案 C terraform 遗产</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Synth-Bottle Gen-1</t>
+          <t>Terraform Legacy</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>铁瓶计划</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>无意识机械产力，圈养/野生</t>
+          <t>早期大气改造站催化剂泄漏</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>瓶醒</t>
+          <t>方案 D 矿冶尾液</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Synth-Awake</t>
+          <t>Smelting Tailings</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>F-Strain 网络共振，集体性觉醒</t>
+          <t>机甲燃料炼矿尾液渗入含水层</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>生态酵母谱系</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>方案 E 化武残留</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Gen-2</t>
+          <t>Chemical War Residue</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>觉醒意识体，冲突中心</t>
+          <t>殖民内战化学剂污染流域</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
@@ -1276,12 +2168,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>毒水时代</t>
+          <t>方案 F 尘暴带电粒子</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Toxic Water Era</t>
+          <t>Dust Storm Ions</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -1291,19 +2183,19 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>2040–2047</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>大干旱、水源污染、社会崩解为新西部</t>
+          <t>双恒星尘暴金属微粒随雨入水</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
@@ -1311,12 +2203,12 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>生态酵母问世</t>
+          <t>推荐组合 A+B</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Eco-Yeast Discovery</t>
+          <t>Recommended A+B</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1326,19 +2218,19 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>2047–2050</t>
+          <t>官方主干</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>生态酿概念确立</t>
+          <t>地质卤毒 + 年度赤潮叠加</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>污染起源方案</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
@@ -1346,12 +2238,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>井源计划</t>
+          <t>生态酵母（统一应答）</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Wellspring Program</t>
+          <t>Eco-Yeast Response</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1361,19 +2253,19 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>首批植入净水士兵，2049 战场验证</t>
+          <t>所有方案共同技术解：毒水→生态酿</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
@@ -1381,12 +2273,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>活燃料计划</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Living Fuel Program</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1396,229 +2288,229 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>2050–2058</t>
+          <t>每年 37 垦日</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>醇民 Gen-0 量产</t>
+          <t>垦历第 13 月，地球账本不承认</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>泄露与抗争</t>
+          <t>天文成因</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Exposure &amp; Resistance</t>
+          <t>Orbital Cause</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>2055–2058</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Don't Bottle Humanity! 戒酒教萌芽</t>
+          <t>公转 397 垦日，余数并入第 13 月</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>铁瓶计划</t>
+          <t>账外之月</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Synth-Bottle Program</t>
+          <t>Off-Ledger Month</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>2058–2065</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>机械燃料解放人性，醇民销毁</t>
+          <t>地球母公司不计 KPI 与编制</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>机械时代</t>
+          <t>法外之月</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Mechanical Era</t>
+          <t>Lawless Month</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>2065–2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>铁瓶量产，酿造帮商业化</t>
+          <t>悬赏翻倍、合同作废、黑市开市</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>酿民觉醒</t>
+          <t>水文峰值</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Awakening</t>
+          <t>Water Toxicity Peak</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>2072–2075</t>
+          <t>A+B</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>二次发酵阈值，瓶醒/井醒</t>
+          <t>卤压上升 + 赤潮全面暴发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>历史时间线</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>当前荒原</t>
+          <t>C.Y. 12 生态酵母验证</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Present Wasteland</t>
+          <t>Yeast Field Test</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>闭环运转 × 意识反抗，酒镇为风暴眼</t>
+          <t>首次现场验证生态酿</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>C.Y. 12 井源计划植入</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Stillwright Cartel</t>
+          <t>Wellspring Implant</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>铁瓶遗产继承人，专利垄断，最大受益者</t>
+          <t>首批净水士兵植入</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
@@ -1626,34 +2518,34 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>二次发酵专利</t>
+          <t>C.Y. 23 铁瓶招标截止</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Secondary Fermentation IP</t>
+          <t>Synth-Bottle Tender</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 23</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>燃料乙醇 40%+ 垄断</t>
+          <t>铁瓶计划招标在十三月截止</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
@@ -1661,34 +2553,34 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>商业化牧场</t>
+          <t>C.Y. 42 觉醒临界</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Commercial Ranches</t>
+          <t>Awakening Threshold</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>圈养铁瓶，悬赏回收</t>
+          <t>二次发酵阈值，当前叙事时点</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
@@ -1696,104 +2588,104 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>酿民回收令</t>
+          <t>Saloon 不打烊</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Reclamation Order</t>
+          <t>Saloon Always Open</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>觉醒酿民定义为废品</t>
+          <t>整月营业，情报与黑市高峰</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>酿造帮配额重置</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Bounty Hunters</t>
+          <t>Quota Reset</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>回收野生铁瓶，猎捕叛逃酿民</t>
+          <t>年度生产配额于十三月 1 日重置</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>鏽釘</t>
+          <t>生态酵母（基础株）</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Rust Nail</t>
+          <t>Saccharomyces vitae</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>职业猎人代表</t>
+          <t>基因改造酵母，可利用殖民毒水发酵</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
@@ -1801,524 +2693,524 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>井兵单禁忌</t>
+          <t>W-Strain</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Well-Soldier Taboo</t>
+          <t>W-Strain (Military)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>生态酵母</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>圈内不接井兵委托</t>
+          <t>军用稳态型</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>戒酒教</t>
+          <t>井源计划</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Temperance Riders</t>
+          <t>Wellspring Program</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>W-Strain</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>早期禁酒主义 + 反改造宗教</t>
+          <t>第一批植入者为净水超级士兵</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>收割派</t>
+          <t>净水士兵（井兵）</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Harvest Faction</t>
+          <t>Aqua-Soldiers</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>戒酒教</t>
+          <t>井源计划</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>招募利用酿民，接口赎罪</t>
+          <t>毒水→内源生态酿 2–4%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>火焰纯净派</t>
+          <t>井醒</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Flame Purity Faction</t>
+          <t>Well-Awake</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>戒酒教</t>
+          <t>净水士兵</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 37+</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>焚烧一切容器，铁瓶为伪善延续</t>
+          <t>W-Strain 残留 / 幸存井兵</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>流浪酒帮</t>
+          <t>R-Strain</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Wander Brews</t>
+          <t>R-Strain (Civilian)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>生态酵母</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>酿民反抗者，开源菌株，打破闭环</t>
+          <t>民用救灾型</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>主流酿民派</t>
+          <t>生态酿</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Mainstream Brewfolk</t>
+          <t>Eco-Brew</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>R-Strain</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>系统内求生，仍辅助生产</t>
+          <t>2–4%，公开合法，社会认知「酵母=希望」</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>势力格局</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>酒镇 / Saloon</t>
+          <t>F-Strain</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Saloon</t>
+          <t>F-Strain (Fuel)</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>生态酵母</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>中立枢纽，情报，黑市，表面和平</t>
+          <t>燃料高产型</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>活燃料计划</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Aqua-Soldiers</t>
+          <t>Living Fuel Program</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-Strain</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>2047–</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>第一代植入者，W-Strain，平行谱系</t>
+          <t>人体活体发酵容器</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B41" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>归档者</t>
+          <t>醇民 Gen-0</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>The Archived</t>
+          <t>Brewfolk Gen-0</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>活燃料计划</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>冷冻，记忆清洗</t>
+          <t>血肉容器，已基本灭绝</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>游荡老兵</t>
+          <t>铁瓶计划</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>The Dregs</t>
+          <t>Synth-Bottle Program</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>F-Strain</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 23–30</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>荒漠传说，靠毒水存活</t>
+          <t>菌株移植至机械载体</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B43" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>隐性血脉</t>
+          <t>铁瓶 Gen-1</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Carrier Line</t>
+          <t>Synth-Bottle Gen-1</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>铁瓶计划</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 23–</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>井醒来源</t>
+          <t>无意识机械产力，圈养/野生</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>醇民 Gen-0</t>
+          <t>瓶醒</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Gen-0</t>
+          <t>Synth-Awake</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>铁瓶 Gen-1</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>2050–2058</t>
+          <t>C.Y. 37+</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>血肉发酵容器，F-Strain，已灭绝</t>
+          <t>F-Strain 网络共振，集体性觉醒</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>生态酵母谱系</t>
         </is>
       </c>
       <c r="B45" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Brewfolk Gen-2</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
           <t>铁瓶 Gen-1</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Synth-Bottle Gen-1</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 37+</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>无意识 android，F-Strain 机械舱</t>
+          <t>觉醒意识体，冲突中心</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>圈养牧场型</t>
+          <t>毒水时代</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Ranch-Penned</t>
+          <t>Toxic Water Era</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 5–12</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>酿造帮控制</t>
+          <t>深井卤毒化、Undecimber 赤潮、边境崩解</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B47" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>野生游荡型</t>
+          <t>生态酵母问世</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Wild Roaming</t>
+          <t>Eco-Yeast Discovery</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>2060–</t>
+          <t>C.Y. 12 Undecimber</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>移动绿洲，赏金目标</t>
+          <t>垦锈带首次现场验证</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B48" s="9" t="n">
@@ -2326,12 +3218,12 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>井源计划</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Gen-2</t>
+          <t>Wellspring Program</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -2341,194 +3233,194 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>觉醒意识体</t>
+          <t>首批植入净水士兵，C.Y. 14 战场验证</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B49" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>瓶醒</t>
+          <t>活燃料计划</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Synth-Awake</t>
+          <t>Living Fuel Program</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>F-Strain 网络共振，数量大</t>
+          <t>醇民 Gen-0 量产</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B50" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>井醒</t>
+          <t>泄露与抗争</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Well-Awake</t>
+          <t>Exposure &amp; Resistance</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 20–23</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>W-Strain 残留，数量少</t>
+          <t>Don't Bottle Humanity! 戒酒教萌芽</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B51" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>主流酿民派</t>
+          <t>铁瓶计划</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Mainstream Brewfolk</t>
+          <t>Synth-Bottle Program</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 23 Undecimber</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>系统内求生</t>
+          <t>机械燃料解放人性，醇民销毁</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>流浪酒帮</t>
+          <t>机械时代</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Wander Brews</t>
+          <t>Mechanical Era</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 30–37</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>脱离闭环</t>
+          <t>铁瓶量产，酿造帮商业化</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>存在体谱系</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B53" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>觉醒个体</t>
+          <t>酿民觉醒</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Awakened Individuals</t>
+          <t>Brewfolk Awakening</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 37–42</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>独立思想者</t>
+          <t>二次发酵阈值，瓶醒/井醒</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>历史时间线</t>
         </is>
       </c>
       <c r="B54" s="9" t="n">
@@ -2536,12 +3428,12 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>当前荒原</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Fuel Perpetual Loop</t>
+          <t>Present Wasteland</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -2551,54 +3443,54 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42 Undecimber</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>铁瓶计划遗产</t>
+          <t>闭环运转 × 意识反抗，赤潮高峰</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B55" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>输入层</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Input Layer</t>
+          <t>Stillwright Cartel</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>毒水、玉米浆、仙人掌糖浆</t>
+          <t>铁瓶遗产继承人，专利垄断，最大受益者</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B56" s="9" t="n">
@@ -2606,34 +3498,34 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>运输层</t>
+          <t>二次发酵专利</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Transport Layer</t>
+          <t>Secondary Fermentation IP</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>2060–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>饲料搬运者 Dust Walker</t>
+          <t>燃料乙醇 40%+ 垄断</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B57" s="9" t="n">
@@ -2641,104 +3533,104 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>生产层</t>
+          <t>商业化牧场</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Production Layer</t>
+          <t>Commercial Ranches</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Bottle</t>
+          <t>圈养铁瓶，悬赏回收</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>一次发酵</t>
+          <t>酿民回收令</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Primary Fermentation</t>
+          <t>Brewfolk Reclamation Order</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>生产层</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>生态酿 2–4% 副产物</t>
+          <t>觉醒酿民定义为废品</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B59" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>二次发酵</t>
+          <t>赏金猎人</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Secondary Fermentation</t>
+          <t>Bounty Hunters</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>生产层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>燃料乙醇 40%+ 主产物</t>
+          <t>回收野生铁瓶，猎捕叛逃酿民</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B60" s="9" t="n">
@@ -2746,34 +3638,34 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>输出层</t>
+          <t>鏽釘</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Output Layer</t>
+          <t>Rust Nail</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>赏金猎人</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>机车、发电机、营地、Saloon</t>
+          <t>职业猎人代表</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>燃料闭环</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B61" s="9" t="n">
@@ -2781,34 +3673,34 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>闭环裂缝</t>
+          <t>井兵单禁忌</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Loop Fracture</t>
+          <t>Well-Soldier Taboo</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>赏金猎人</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>二次发酵阈值，酿民觉醒</t>
+          <t>圈内不接井兵委托</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B62" s="9" t="n">
@@ -2816,12 +3708,12 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>戒酒教</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Survival Obsession</t>
+          <t>Temperance Riders</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -2831,19 +3723,19 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>无论如何都要活下去</t>
+          <t>早期禁酒主义 + 反改造宗教</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B63" s="9" t="n">
@@ -2851,34 +3743,34 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>士兵净水</t>
+          <t>收割派</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Soldiers Purify Water</t>
+          <t>Harvest Faction</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>戒酒教</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>2047–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>最正当的起点</t>
+          <t>招募利用酿民，接口赎罪</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B64" s="9" t="n">
@@ -2886,174 +3778,174 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>人体验证</t>
+          <t>火焰纯净派</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Human Vessel Proven</t>
+          <t>Flame Purity Faction</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>戒酒教</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>2049–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>技术门槛跨越</t>
+          <t>焚烧一切容器，铁瓶为伪善延续</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B65" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>贫民燃料化</t>
+          <t>流浪酒帮</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Poor as Fuel</t>
+          <t>Wander Brews</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>对象降级，话术不变</t>
+          <t>酿民反抗者，开源菌株，打破闭环</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B66" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>人道抗争</t>
+          <t>主流酿民派</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Humanitarian Protest</t>
+          <t>Mainstream Brewfolk</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>2055–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>别把人变成瓶子</t>
+          <t>系统内求生，仍辅助生产</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>势力格局</t>
         </is>
       </c>
       <c r="B67" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>铁瓶妥协</t>
+          <t>酒镇 / Saloon</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Synth-Bottle Compromise</t>
+          <t>Saloon</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>机械燃料，解放人性</t>
+          <t>中立枢纽，情报，黑市，表面和平</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>存在体谱系</t>
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>机械量产</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Mass Production</t>
+          <t>Aqua-Soldiers</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>2065–</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>人性换效率</t>
+          <t>第一代植入者，W-Strain，平行谱系</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>讽刺主题链</t>
+          <t>存在体谱系</t>
         </is>
       </c>
       <c r="B69" s="9" t="n">
@@ -3061,104 +3953,104 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>酿民觉醒</t>
+          <t>归档者</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Awakening</t>
+          <t>The Archived</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>容器发问，闭环裂缝</t>
+          <t>冷冻，记忆清洗</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>叙事入口</t>
+          <t>存在体谱系</t>
         </is>
       </c>
       <c r="B70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>井兵末裔</t>
+          <t>游荡老兵</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Well-Soldier Scion</t>
+          <t>The Dregs</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>W-Strain 残留，各方追逐</t>
+          <t>荒漠传说，靠毒水存活</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>叙事入口</t>
+          <t>存在体谱系</t>
         </is>
       </c>
       <c r="B71" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>刚觉醒酿民</t>
+          <t>隐性血脉</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Newly Awakened Brewfolk</t>
+          <t>Carrier Line</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>意识到自己是净水者也是油箱</t>
+          <t>井醒来源</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>叙事入口</t>
+          <t>存在体谱系</t>
         </is>
       </c>
       <c r="B72" s="9" t="n">
@@ -3166,12 +4058,12 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>鏽釘</t>
+          <t>醇民 Gen-0</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Rust Nail</t>
+          <t>Brewfolk Gen-0</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -3181,19 +4073,19 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人，禁忌井兵委托</t>
+          <t>血肉发酵容器，F-Strain，已灭绝</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>叙事入口</t>
+          <t>存在体谱系</t>
         </is>
       </c>
       <c r="B73" s="9" t="n">
@@ -3201,12 +4093,12 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Saloon 酒保</t>
+          <t>铁瓶 Gen-1</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Saloon Bartender</t>
+          <t>Synth-Bottle Gen-1</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -3216,45 +4108,1025 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 23–</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>半觉醒老旧铁瓶</t>
+          <t>无意识 android，F-Strain 机械舱</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>圈养牧场型</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Ranch-Penned</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶 Gen-1</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>酿造帮控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>野生游荡型</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Wild Roaming</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶 Gen-1</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 25–</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>移动绿洲，赏金目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Brewfolk Gen-2</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>觉醒意识体</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>瓶醒</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Synth-Awake</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>F-Strain 网络共振，数量大</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>井醒</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Well-Awake</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>W-Strain 残留，数量少</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>主流酿民派</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Mainstream Brewfolk</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>系统内求生</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>流浪酒帮</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Wander Brews</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>脱离闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>存在体谱系</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>觉醒个体</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Awakened Individuals</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>独立思想者</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Fuel Perpetual Loop</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶计划遗产</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>输入层</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Input Layer</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>毒水、玉米浆、仙人掌糖浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>运输层</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Transport Layer</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 25–</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>饲料搬运者 Dust Walker</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>生产层</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Production Layer</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶 Synth-Bottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>一次发酵</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Primary Fermentation</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>生产层</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>生态酿 2–4% 副产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>二次发酵</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Secondary Fermentation</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>生产层</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>燃料乙醇 40%+ 主产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>输出层</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Output Layer</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>机车、发电机、营地、Saloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>燃料闭环</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>闭环裂缝</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Loop Fracture</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>燃料永续闭环</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>二次发酵阈值，酿民觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Survival Obsession</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>无论如何都要活下去</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>士兵净水</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Soldiers Purify Water</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 12–</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>最正当的起点</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>人体验证</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Human Vessel Proven</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 14–</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>技术门槛跨越</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>贫民燃料化</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Poor as Fuel</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 15–</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>对象降级，话术不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>人道抗争</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Humanitarian Protest</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 20–</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>别把人变成瓶子</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶妥协</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Synth-Bottle Compromise</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>机械燃料，解放人性</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>机械量产</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Mass Production</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 30–</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>人性换效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>讽刺主题链</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>酿民觉醒</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Brewfolk Awakening</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>旧时代生存执念</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>容器发问，闭环裂缝</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
           <t>叙事入口</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
+      <c r="B98" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>井兵末裔</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Well-Soldier Scion</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>W-Strain 残留，各方追逐</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>叙事入口</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>刚觉醒酿民</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Newly Awakened Brewfolk</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>意识到自己是净水者也是油箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>叙事入口</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>鏽釘</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Rust Nail</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>赏金猎人，禁忌井兵委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>叙事入口</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Saloon 酒保</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Saloon Bartender</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>半觉醒老旧铁瓶</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>叙事入口</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>酿造帮档案员</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Cartel Archivist</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>发现抗议领袖在铁瓶合同上</t>
         </is>
@@ -3274,7 +5146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3288,7 +5160,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 生态酵母谱系</t>
+          <t>《瓶与井》· 殖民星球</t>
         </is>
       </c>
     </row>
@@ -3327,7 +5199,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>▸ 生态酵母谱系</t>
+          <t>▸ 殖民星球</t>
         </is>
       </c>
     </row>
@@ -3337,12 +5209,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>生态酵母（基础株）</t>
+          <t>垦锈带 Calico Reach</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Saccharomyces vitae</t>
+          <t>Calico Reach</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -3352,12 +5224,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2047–</t>
+          <t>C.Y. 0–</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>基因改造酵母，可利用毒水发酵</t>
+          <t>地球联邦第三序列边境殖民星球</t>
         </is>
       </c>
     </row>
@@ -3367,387 +5239,177 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>W-Strain</t>
+          <t>星球特征</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>W-Strain (Military)</t>
+          <t>Planet Traits</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>生态酵母</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>军用稳态型</t>
+          <t>双恒星、干燥荒原、深井采水、稀薄大气</t>
         </is>
       </c>
     </row>
     <row r="7" outlineLevel="1">
       <c r="A7" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>井源计划</t>
+          <t>殖民形态</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Wellspring Program</t>
+          <t>Colonial Form</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>W-Strain</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>C.Y. 0–</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>第一批植入者为净水超级士兵</t>
+          <t>财团殖民、边境新西部、公司法自治</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1">
       <c r="A8" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>净水士兵（井兵）</t>
+          <t>垦历 C.Y.</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Aqua-Soldiers</t>
+          <t>Colonial Year</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>井源计划</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>C.Y. 0–</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>毒水→内源生态酿 2–4%</t>
+          <t>殖民年号，替代地球公历</t>
         </is>
       </c>
     </row>
     <row r="9" outlineLevel="1">
       <c r="A9" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>井醒</t>
+          <t>标准十二月</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Well-Awake</t>
+          <t>Standard Twelve Months</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>净水士兵</t>
+          <t>垦历</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>W-Strain 残留 / 幸存井兵</t>
+          <t>沿用地球月份名便于行政</t>
         </is>
       </c>
     </row>
     <row r="10" outlineLevel="1">
       <c r="A10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>R-Strain</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>R-Strain (Civilian)</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>生态酵母</t>
+          <t>垦历</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2049–</t>
+          <t>每年</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>民用救灾型</t>
+          <t>闰余月 37 垦日，账外之月</t>
         </is>
       </c>
     </row>
     <row r="11" outlineLevel="1">
       <c r="A11" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>生态酿</t>
+          <t>当前时点</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Eco-Brew</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>R-Strain</t>
+          <t>垦锈带</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2049–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>2–4%，公开合法，社会认知「酵母=希望」</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" outlineLevel="1">
-      <c r="A12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>F-Strain</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>F-Strain (Fuel)</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>生态酵母</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>2050–</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>燃料高产型</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" outlineLevel="1">
-      <c r="A13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>活燃料计划</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Living Fuel Program</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>F-Strain</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>2050–2058</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>人体活体发酵容器</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" outlineLevel="1">
-      <c r="A14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>醇民 Gen-0</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Brewfolk Gen-0</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>活燃料计划</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>2050–2058</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>血肉容器，已基本灭绝</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1">
-      <c r="A15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>铁瓶计划</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Synth-Bottle Program</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>F-Strain</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>2058–2065</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>菌株移植至机械载体</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" outlineLevel="1">
-      <c r="A16" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>铁瓶 Gen-1</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Synth-Bottle Gen-1</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>铁瓶计划</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>2058–</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>无意识机械产力，圈养/野生</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" outlineLevel="1">
-      <c r="A17" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>瓶醒</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Synth-Awake</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>铁瓶 Gen-1</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>2072+</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>F-Strain 网络共振，集体性觉醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" outlineLevel="1">
-      <c r="A18" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>酿民 Gen-2</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Brewfolk Gen-2</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>铁瓶 Gen-1</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>2072+</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>觉醒意识体，冲突中心</t>
+          <t>Undecimber 中旬，酒镇风暴季</t>
         </is>
       </c>
     </row>
@@ -3766,7 +5428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3780,7 +5442,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 历史时间线</t>
+          <t>《瓶与井》· 污染起源方案</t>
         </is>
       </c>
     </row>
@@ -3819,7 +5481,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>▸ 历史时间线</t>
+          <t>▸ 污染起源方案</t>
         </is>
       </c>
     </row>
@@ -3829,12 +5491,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>毒水时代</t>
+          <t>方案 A 深井毒卤</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Toxic Water Era</t>
+          <t>Deep-Brine Toxicity</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -3844,42 +5506,42 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2040–2047</t>
+          <t>推荐主干</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>大干旱、水源污染、社会崩解为新西部</t>
+          <t>高氯酸盐/砷/铜卤层，深井采水全域污染</t>
         </is>
       </c>
     </row>
     <row r="6" outlineLevel="1">
       <c r="A6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>生态酵母问世</t>
+          <t>Undecimber 卤压峰值</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Eco-Yeast Discovery</t>
+          <t>Undecimber Brine Peak</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>方案 A</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2047–2050</t>
+          <t>每年</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>生态酿概念确立</t>
+          <t>地下卤层渗透率年度最高</t>
         </is>
       </c>
     </row>
@@ -3889,12 +5551,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>井源计划</t>
+          <t>方案 B 流浪赤潮</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Wellspring Program</t>
+          <t>Wandering Red Tide</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -3904,42 +5566,42 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2047–2052</t>
+          <t>推荐叠加</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>首批植入净水士兵，2049 战场验证</t>
+          <t>本土嗜盐菌季节性神经毒素</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1">
       <c r="A8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>活燃料计划</t>
+          <t>赤潮高峰</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Living Fuel Program</t>
+          <t>Red Tide Peak</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>方案 B</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2050–2058</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>醇民 Gen-0 量产</t>
+          <t>全年水质最差月份</t>
         </is>
       </c>
     </row>
@@ -3949,12 +5611,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>泄露与抗争</t>
+          <t>方案 C terraform 遗产</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Exposure &amp; Resistance</t>
+          <t>Terraform Legacy</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -3964,12 +5626,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2055–2058</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Don't Bottle Humanity! 戒酒教萌芽</t>
+          <t>早期大气改造站催化剂泄漏</t>
         </is>
       </c>
     </row>
@@ -3979,12 +5641,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>铁瓶计划</t>
+          <t>方案 D 矿冶尾液</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Synth-Bottle Program</t>
+          <t>Smelting Tailings</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -3994,12 +5656,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2058–2065</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>机械燃料解放人性，醇民销毁</t>
+          <t>机甲燃料炼矿尾液渗入含水层</t>
         </is>
       </c>
     </row>
@@ -4009,12 +5671,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>机械时代</t>
+          <t>方案 E 化武残留</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Mechanical Era</t>
+          <t>Chemical War Residue</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -4024,12 +5686,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2065–2072</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>铁瓶量产，酿造帮商业化</t>
+          <t>殖民内战化学剂污染流域</t>
         </is>
       </c>
     </row>
@@ -4039,12 +5701,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>酿民觉醒</t>
+          <t>方案 F 尘暴带电粒子</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Awakening</t>
+          <t>Dust Storm Ions</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -4054,12 +5716,12 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2072–2075</t>
+          <t>可选</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>二次发酵阈值，瓶醒/井醒</t>
+          <t>双恒星尘暴金属微粒随雨入水</t>
         </is>
       </c>
     </row>
@@ -4069,12 +5731,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>当前荒原</t>
+          <t>推荐组合 A+B</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Present Wasteland</t>
+          <t>Recommended A+B</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -4084,12 +5746,42 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>官方主干</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>闭环运转 × 意识反抗，酒镇为风暴眼</t>
+          <t>地质卤毒 + 年度赤潮叠加</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1">
+      <c r="A14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>生态酵母（统一应答）</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Eco-Yeast Response</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 12–</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>所有方案共同技术解：毒水→生态酿</t>
         </is>
       </c>
     </row>
@@ -4108,7 +5800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4122,7 +5814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 势力格局</t>
+          <t>《瓶与井》· 十三月 Undecimber</t>
         </is>
       </c>
     </row>
@@ -4161,7 +5853,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>▸ 势力格局</t>
+          <t>▸ 十三月 Undecimber</t>
         </is>
       </c>
     </row>
@@ -4171,12 +5863,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>十三月 Undecimber</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Stillwright Cartel</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -4186,12 +5878,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>每年 37 垦日</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>铁瓶遗产继承人，专利垄断，最大受益者</t>
+          <t>垦历第 13 月，地球账本不承认</t>
         </is>
       </c>
     </row>
@@ -4201,27 +5893,27 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>二次发酵专利</t>
+          <t>天文成因</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Secondary Fermentation IP</t>
+          <t>Orbital Cause</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>燃料乙醇 40%+ 垄断</t>
+          <t>公转 397 垦日，余数并入第 13 月</t>
         </is>
       </c>
     </row>
@@ -4231,27 +5923,27 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>商业化牧场</t>
+          <t>账外之月</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Commercial Ranches</t>
+          <t>Off-Ledger Month</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>圈养铁瓶，悬赏回收</t>
+          <t>地球母公司不计 KPI 与编制</t>
         </is>
       </c>
     </row>
@@ -4261,57 +5953,57 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>酿民回收令</t>
+          <t>法外之月</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Reclamation Order</t>
+          <t>Lawless Month</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>酿造帮</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>觉醒酿民定义为废品</t>
+          <t>悬赏翻倍、合同作废、黑市开市</t>
         </is>
       </c>
     </row>
     <row r="9" outlineLevel="1">
       <c r="A9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>水文峰值</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Bounty Hunters</t>
+          <t>Water Toxicity Peak</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>A+B</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>回收野生铁瓶，猎捕叛逃酿民</t>
+          <t>卤压上升 + 赤潮全面暴发</t>
         </is>
       </c>
     </row>
@@ -4321,27 +6013,27 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>鏽釘</t>
+          <t>C.Y. 12 生态酵母验证</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Rust Nail</t>
+          <t>Yeast Field Test</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>职业猎人代表</t>
+          <t>首次现场验证生态酿</t>
         </is>
       </c>
     </row>
@@ -4351,57 +6043,57 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>井兵单禁忌</t>
+          <t>C.Y. 12 井源计划植入</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Well-Soldier Taboo</t>
+          <t>Wellspring Implant</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>圈内不接井兵委托</t>
+          <t>首批净水士兵植入</t>
         </is>
       </c>
     </row>
     <row r="12" outlineLevel="1">
       <c r="A12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>戒酒教</t>
+          <t>C.Y. 23 铁瓶招标截止</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Temperance Riders</t>
+          <t>Synth-Bottle Tender</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 23</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>早期禁酒主义 + 反改造宗教</t>
+          <t>铁瓶计划招标在十三月截止</t>
         </is>
       </c>
     </row>
@@ -4411,27 +6103,27 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>收割派</t>
+          <t>C.Y. 42 觉醒临界</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Harvest Faction</t>
+          <t>Awakening Threshold</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>戒酒教</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>招募利用酿民，接口赎罪</t>
+          <t>二次发酵阈值，当前叙事时点</t>
         </is>
       </c>
     </row>
@@ -4441,117 +6133,57 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>火焰纯净派</t>
+          <t>Saloon 不打烊</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Flame Purity Faction</t>
+          <t>Saloon Always Open</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>戒酒教</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>焚烧一切容器，铁瓶为伪善延续</t>
+          <t>整月营业，情报与黑市高峰</t>
         </is>
       </c>
     </row>
     <row r="15" outlineLevel="1">
       <c r="A15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>流浪酒帮</t>
+          <t>酿造帮配额重置</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Wander Brews</t>
+          <t>Quota Reset</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Undecimber</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>酿民反抗者，开源菌株，打破闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" outlineLevel="1">
-      <c r="A16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>主流酿民派</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Mainstream Brewfolk</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>系统内求生，仍辅助生产</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" outlineLevel="1">
-      <c r="A17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>酒镇 / Saloon</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Saloon</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>中立枢纽，情报，黑市，表面和平</t>
+          <t>年度生产配额于十三月 1 日重置</t>
         </is>
       </c>
     </row>
@@ -4584,7 +6216,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 存在体谱系</t>
+          <t>《瓶与井》· 生态酵母谱系</t>
         </is>
       </c>
     </row>
@@ -4623,7 +6255,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>▸ 存在体谱系</t>
+          <t>▸ 生态酵母谱系</t>
         </is>
       </c>
     </row>
@@ -4633,12 +6265,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>生态酵母（基础株）</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Aqua-Soldiers</t>
+          <t>Saccharomyces vitae</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -4648,12 +6280,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2047–</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>第一代植入者，W-Strain，平行谱系</t>
+          <t>基因改造酵母，可利用殖民毒水发酵</t>
         </is>
       </c>
     </row>
@@ -4663,177 +6295,177 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>归档者</t>
+          <t>W-Strain</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>The Archived</t>
+          <t>W-Strain (Military)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>生态酵母</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>冷冻，记忆清洗</t>
+          <t>军用稳态型</t>
         </is>
       </c>
     </row>
     <row r="7" outlineLevel="1">
       <c r="A7" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>游荡老兵</t>
+          <t>井源计划</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>The Dregs</t>
+          <t>Wellspring Program</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>W-Strain</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>荒漠传说，靠毒水存活</t>
+          <t>第一批植入者为净水超级士兵</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1">
       <c r="A8" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>隐性血脉</t>
+          <t>净水士兵（井兵）</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Carrier Line</t>
+          <t>Aqua-Soldiers</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>井兵</t>
+          <t>井源计划</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>井醒来源</t>
+          <t>毒水→内源生态酿 2–4%</t>
         </is>
       </c>
     </row>
     <row r="9" outlineLevel="1">
       <c r="A9" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>醇民 Gen-0</t>
+          <t>井醒</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Gen-0</t>
+          <t>Well-Awake</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>净水士兵</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2050–2058</t>
+          <t>C.Y. 37+</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>血肉发酵容器，F-Strain，已灭绝</t>
+          <t>W-Strain 残留 / 幸存井兵</t>
         </is>
       </c>
     </row>
     <row r="10" outlineLevel="1">
       <c r="A10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>R-Strain</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Synth-Bottle Gen-1</t>
+          <t>R-Strain (Civilian)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>生态酵母</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>无意识 android，F-Strain 机械舱</t>
+          <t>民用救灾型</t>
         </is>
       </c>
     </row>
     <row r="11" outlineLevel="1">
       <c r="A11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>圈养牧场型</t>
+          <t>生态酿</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Ranch-Penned</t>
+          <t>Eco-Brew</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>R-Strain</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>酿造帮控制</t>
+          <t>2–4%，公开合法，社会认知「酵母=希望」</t>
         </is>
       </c>
     </row>
@@ -4843,207 +6475,207 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>野生游荡型</t>
+          <t>F-Strain</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Wild Roaming</t>
+          <t>F-Strain (Fuel)</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1</t>
+          <t>生态酵母</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2060–</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>移动绿洲，赏金目标</t>
+          <t>燃料高产型</t>
         </is>
       </c>
     </row>
     <row r="13" outlineLevel="1">
       <c r="A13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>活燃料计划</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Gen-2</t>
+          <t>Living Fuel Program</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-Strain</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>觉醒意识体</t>
+          <t>人体活体发酵容器</t>
         </is>
       </c>
     </row>
     <row r="14" outlineLevel="1">
       <c r="A14" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>瓶醒</t>
+          <t>醇民 Gen-0</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Synth-Awake</t>
+          <t>Brewfolk Gen-0</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>活燃料计划</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>F-Strain 网络共振，数量大</t>
+          <t>血肉容器，已基本灭绝</t>
         </is>
       </c>
     </row>
     <row r="15" outlineLevel="1">
       <c r="A15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>井醒</t>
+          <t>铁瓶计划</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Well-Awake</t>
+          <t>Synth-Bottle Program</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>F-Strain</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 23–30</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>W-Strain 残留，数量少</t>
+          <t>菌株移植至机械载体</t>
         </is>
       </c>
     </row>
     <row r="16" outlineLevel="1">
       <c r="A16" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>主流酿民派</t>
+          <t>铁瓶 Gen-1</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Mainstream Brewfolk</t>
+          <t>Synth-Bottle Gen-1</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>铁瓶计划</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 23–</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>系统内求生</t>
+          <t>无意识机械产力，圈养/野生</t>
         </is>
       </c>
     </row>
     <row r="17" outlineLevel="1">
       <c r="A17" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>流浪酒帮</t>
+          <t>瓶醒</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Wander Brews</t>
+          <t>Synth-Awake</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>铁瓶 Gen-1</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 37+</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>脱离闭环</t>
+          <t>F-Strain 网络共振，集体性觉醒</t>
         </is>
       </c>
     </row>
     <row r="18" outlineLevel="1">
       <c r="A18" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>觉醒个体</t>
+          <t>酿民 Gen-2</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Awakened Individuals</t>
+          <t>Brewfolk Gen-2</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>酿民 Gen-2</t>
+          <t>铁瓶 Gen-1</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 37+</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>独立思想者</t>
+          <t>觉醒意识体，冲突中心</t>
         </is>
       </c>
     </row>
@@ -5062,7 +6694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5076,7 +6708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 燃料闭环</t>
+          <t>《瓶与井》· 历史时间线</t>
         </is>
       </c>
     </row>
@@ -5115,7 +6747,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>▸ 燃料闭环</t>
+          <t>▸ 历史时间线</t>
         </is>
       </c>
     </row>
@@ -5125,12 +6757,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>毒水时代</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Fuel Perpetual Loop</t>
+          <t>Toxic Water Era</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -5140,222 +6772,252 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 5–12</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>铁瓶计划遗产</t>
+          <t>深井卤毒化、Undecimber 赤潮、边境崩解</t>
         </is>
       </c>
     </row>
     <row r="6" outlineLevel="1">
       <c r="A6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>输入层</t>
+          <t>生态酵母问世</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Input Layer</t>
+          <t>Eco-Yeast Discovery</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 12 Undecimber</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>毒水、玉米浆、仙人掌糖浆</t>
+          <t>垦锈带首次现场验证</t>
         </is>
       </c>
     </row>
     <row r="7" outlineLevel="1">
       <c r="A7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>运输层</t>
+          <t>井源计划</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Transport Layer</t>
+          <t>Wellspring Program</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2060–</t>
+          <t>C.Y. 12–17</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>饲料搬运者 Dust Walker</t>
+          <t>首批植入净水士兵，C.Y. 14 战场验证</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1">
       <c r="A8" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>生产层</t>
+          <t>活燃料计划</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Production Layer</t>
+          <t>Living Fuel Program</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Bottle</t>
+          <t>醇民 Gen-0 量产</t>
         </is>
       </c>
     </row>
     <row r="9" outlineLevel="1">
       <c r="A9" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>一次发酵</t>
+          <t>泄露与抗争</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Primary Fermentation</t>
+          <t>Exposure &amp; Resistance</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>生产层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 20–23</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>生态酿 2–4% 副产物</t>
+          <t>Don't Bottle Humanity! 戒酒教萌芽</t>
         </is>
       </c>
     </row>
     <row r="10" outlineLevel="1">
       <c r="A10" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>二次发酵</t>
+          <t>铁瓶计划</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Secondary Fermentation</t>
+          <t>Synth-Bottle Program</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>生产层</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 23 Undecimber</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>燃料乙醇 40%+ 主产物</t>
+          <t>机械燃料解放人性，醇民销毁</t>
         </is>
       </c>
     </row>
     <row r="11" outlineLevel="1">
       <c r="A11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>输出层</t>
+          <t>机械时代</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Output Layer</t>
+          <t>Mechanical Era</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 30–37</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>机车、发电机、营地、Saloon</t>
+          <t>铁瓶量产，酿造帮商业化</t>
         </is>
       </c>
     </row>
     <row r="12" outlineLevel="1">
       <c r="A12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>闭环裂缝</t>
+          <t>酿民觉醒</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Loop Fracture</t>
+          <t>Brewfolk Awakening</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>燃料永续闭环</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 37–42</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>二次发酵阈值，酿民觉醒</t>
+          <t>二次发酵阈值，瓶醒/井醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>当前荒原</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Present Wasteland</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42 Undecimber</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>闭环运转 × 意识反抗，赤潮高峰</t>
         </is>
       </c>
     </row>
@@ -5374,7 +7036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5388,7 +7050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 讽刺主题链</t>
+          <t>《瓶与井》· 势力格局</t>
         </is>
       </c>
     </row>
@@ -5427,7 +7089,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>▸ 讽刺主题链</t>
+          <t>▸ 势力格局</t>
         </is>
       </c>
     </row>
@@ -5437,12 +7099,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Survival Obsession</t>
+          <t>Stillwright Cartel</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -5452,12 +7114,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>无论如何都要活下去</t>
+          <t>铁瓶遗产继承人，专利垄断，最大受益者</t>
         </is>
       </c>
     </row>
@@ -5467,27 +7129,27 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>士兵净水</t>
+          <t>二次发酵专利</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Soldiers Purify Water</t>
+          <t>Secondary Fermentation IP</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2047–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>最正当的起点</t>
+          <t>燃料乙醇 40%+ 垄断</t>
         </is>
       </c>
     </row>
@@ -5497,27 +7159,27 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>人体验证</t>
+          <t>商业化牧场</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Human Vessel Proven</t>
+          <t>Commercial Ranches</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2049–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>技术门槛跨越</t>
+          <t>圈养铁瓶，悬赏回收</t>
         </is>
       </c>
     </row>
@@ -5527,57 +7189,57 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>贫民燃料化</t>
+          <t>酿民回收令</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Poor as Fuel</t>
+          <t>Brewfolk Reclamation Order</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>酿造帮</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2050–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>对象降级，话术不变</t>
+          <t>觉醒酿民定义为废品</t>
         </is>
       </c>
     </row>
     <row r="9" outlineLevel="1">
       <c r="A9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>人道抗争</t>
+          <t>赏金猎人</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Humanitarian Protest</t>
+          <t>Bounty Hunters</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2055–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>别把人变成瓶子</t>
+          <t>回收野生铁瓶，猎捕叛逃酿民</t>
         </is>
       </c>
     </row>
@@ -5587,27 +7249,27 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>铁瓶妥协</t>
+          <t>鏽釘</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Synth-Bottle Compromise</t>
+          <t>Rust Nail</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>赏金猎人</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2058–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>机械燃料，解放人性</t>
+          <t>职业猎人代表</t>
         </is>
       </c>
     </row>
@@ -5617,57 +7279,207 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>机械量产</t>
+          <t>井兵单禁忌</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Mass Production</t>
+          <t>Well-Soldier Taboo</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>赏金猎人</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2065–</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>人性换效率</t>
+          <t>圈内不接井兵委托</t>
         </is>
       </c>
     </row>
     <row r="12" outlineLevel="1">
       <c r="A12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>酿民觉醒</t>
+          <t>戒酒教</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Brewfolk Awakening</t>
+          <t>Temperance Riders</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>旧时代生存执念</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2072+</t>
+          <t>C.Y. 42</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>容器发问，闭环裂缝</t>
+          <t>早期禁酒主义 + 反改造宗教</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>收割派</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Harvest Faction</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>戒酒教</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>招募利用酿民，接口赎罪</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1">
+      <c r="A14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>火焰纯净派</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Flame Purity Faction</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>戒酒教</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>焚烧一切容器，铁瓶为伪善延续</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1">
+      <c r="A15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>流浪酒帮</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Wander Brews</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>酿民反抗者，开源菌株，打破闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1">
+      <c r="A16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>主流酿民派</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Mainstream Brewfolk</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>系统内求生，仍辅助生产</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1">
+      <c r="A17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>酒镇 / Saloon</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Saloon</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 42</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>中立枢纽，情报，黑市，表面和平</t>
         </is>
       </c>
     </row>
@@ -5686,7 +7498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5700,7 +7512,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 叙事入口</t>
+          <t>《瓶与井》· 存在体谱系</t>
         </is>
       </c>
     </row>
@@ -5739,7 +7551,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>▸ 叙事入口</t>
+          <t>▸ 存在体谱系</t>
         </is>
       </c>
     </row>
@@ -5749,12 +7561,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>井兵末裔</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Well-Soldier Scion</t>
+          <t>Aqua-Soldiers</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -5764,102 +7576,102 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 12–</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>W-Strain 残留，各方追逐</t>
+          <t>第一代植入者，W-Strain，平行谱系</t>
         </is>
       </c>
     </row>
     <row r="6" outlineLevel="1">
       <c r="A6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>刚觉醒酿民</t>
+          <t>归档者</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Newly Awakened Brewfolk</t>
+          <t>The Archived</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>意识到自己是净水者也是油箱</t>
+          <t>冷冻，记忆清洗</t>
         </is>
       </c>
     </row>
     <row r="7" outlineLevel="1">
       <c r="A7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>鏽釘</t>
+          <t>游荡老兵</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Rust Nail</t>
+          <t>The Dregs</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>赏金猎人，禁忌井兵委托</t>
+          <t>荒漠传说，靠毒水存活</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1">
       <c r="A8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Saloon 酒保</t>
+          <t>隐性血脉</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Saloon Bartender</t>
+          <t>Carrier Line</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>井兵</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>半觉醒老旧铁瓶</t>
+          <t>井醒来源</t>
         </is>
       </c>
     </row>
@@ -5869,12 +7681,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>酿造帮档案员</t>
+          <t>醇民 Gen-0</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Cartel Archivist</t>
+          <t>Brewfolk Gen-0</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -5884,12 +7696,282 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>C.Y. 15–23</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>发现抗议领袖在铁瓶合同上</t>
+          <t>血肉发酵容器，F-Strain，已灭绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" outlineLevel="1">
+      <c r="A10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶 Gen-1</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Synth-Bottle Gen-1</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>无意识 android，F-Strain 机械舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>圈养牧场型</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Ranch-Penned</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶 Gen-1</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 23–</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>酿造帮控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>野生游荡型</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Wild Roaming</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>铁瓶 Gen-1</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 25–</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>移动绿洲，赏金目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Brewfolk Gen-2</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>觉醒意识体</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1">
+      <c r="A14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>瓶醒</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Synth-Awake</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>F-Strain 网络共振，数量大</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1">
+      <c r="A15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>井醒</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Well-Awake</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>W-Strain 残留，数量少</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1">
+      <c r="A16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>主流酿民派</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Mainstream Brewfolk</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>系统内求生</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1">
+      <c r="A17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>流浪酒帮</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Wander Brews</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>脱离闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1">
+      <c r="A18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>觉醒个体</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Awakened Individuals</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>C.Y. 37+</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>独立思想者</t>
         </is>
       </c>
     </row>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v4</t>
+          <t>2026-07-16-v5</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 毒水三层（官方主干 A+B+辐射尘）</t>
+          <t xml:space="preserve">    ├─ 锈水三层（官方主干 A+B+辐射尘）</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>毒水时代（Toxic Water Era） ──→ C.Y. 5–12 · 深井卤毒化、Undecimber 赤潮、边境崩解</t>
+          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 深井卤锈化、Undecimber 赤潮、边境崩解</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠毒水存活</t>
+          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 毒水(卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
     <row r="44" outlineLevel="1" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：毒水→生态酿</t>
+          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
     <row r="55" outlineLevel="1" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 与毒水闭环（Water Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
+          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 毒水→内源生态酿 2–4%</t>
+          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>毒水时代（Toxic Water Era） ──→ C.Y. 5–12 · 深井卤毒化、Undecimber 赤潮、边境崩解</t>
+          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 深井卤锈化、Undecimber 赤潮、边境崩解</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠毒水存活</t>
+          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
     <row r="174" outlineLevel="1" ht="16" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 毒水(卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：毒水→生态酿</t>
+          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 与毒水闭环（Water Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
+          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 毒水→内源生态酿 2–4%</t>
+          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
         </is>
       </c>
     </row>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v5</t>
+          <t>2026-07-16-v6</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>垦锈带 Calico Reach（地球联邦边境殖民星）</t>
+          <t>赭锈带 Ochre Reach（民间旧称 垦锈带 · 地球联邦边境殖民星）</t>
         </is>
       </c>
     </row>
@@ -582,201 +582,210 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 垦锈带 Calico Reach ──→ 边境殖民星 · 陆海沙海 · 辐射尘</t>
+          <t xml:space="preserve">    ├─ 赭锈带 Ochre Reach ──→ 边境殖民星 · 陆海沙海 · 辐射尘</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 民间旧称：垦锈带</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 锈水三层（官方主干 A+B+辐射尘）</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 化学层：深井毒卤</t>
+          <t xml:space="preserve">    ├─ 锈水三层（官方主干 A+B+辐射尘）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 生物层：流浪赤潮（Undecimber 峰值）</t>
+          <t xml:space="preserve">    │       ├─ 化学层：深井毒卤</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 放射层：辐射尘（沙海富集）</t>
+          <t xml:space="preserve">    │       ├─ 生物层：流浪赤潮（Undecimber 峰值）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 放射层：辐射尘（沙海富集）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生态酵母 ──→ 三重净化 · 2–4% 生态酿 · 40%+ 燃料乙醇</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ W/R/F-Strain → 井兵 / 醇民 / 铁瓶 / 酿民</t>
+          <t xml:space="preserve">    ├─ 生态酵母 ──→ 三重净化 · 2–4% 生态酿 · 40%+ 燃料乙醇</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ W/R/F-Strain → 井兵 / 醇民 / 铁瓶 / 酿民</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 陆海 + 沙豚 ──→ 重砂流态海 · 磁泳生物</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 陆海 + 沙豚 ──→ 重砂流态海 · 磁泳生物</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 十三月 Undecimber ──→ 账外之月 · 水质最差 · 觉醒临界</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>模块索引</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  01. 殖民星球</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  02. 污染官方主干</t>
+          <t xml:space="preserve">  01. 殖民星球</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  03. 污染起源方案</t>
+          <t xml:space="preserve">  02. 污染官方主干</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  04. 陆海沙海</t>
+          <t xml:space="preserve">  03. 污染起源方案</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  05. 沙豚</t>
+          <t xml:space="preserve">  04. 陆海沙海</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  06. 十三月 Undecimber</t>
+          <t xml:space="preserve">  05. 沙豚</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  07. 生态酵母谱系</t>
+          <t xml:space="preserve">  06. 十三月 Undecimber</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  08. 历史时间线</t>
+          <t xml:space="preserve">  07. 生态酵母谱系</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  09. 势力格局</t>
+          <t xml:space="preserve">  08. 历史时间线</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. 存在体谱系</t>
+          <t xml:space="preserve">  09. 势力格局</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. 燃料闭环</t>
+          <t xml:space="preserve">  10. 存在体谱系</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12. 讽刺主题链</t>
+          <t xml:space="preserve">  11. 燃料闭环</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  12. 讽刺主题链</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  13. 叙事入口</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
@@ -789,7 +798,6 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A31:C31"/>
@@ -844,7 +852,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 垦锈带首次现场验证</t>
+          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1673,7 +1681,7 @@
     <row r="5" outlineLevel="1" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>垦锈带 Calico Reach ──→ C.Y. 0– · 地球联邦第三序列边境殖民星球</t>
+          <t>赭锈带 Ochre Reach ──→ C.Y. 0– · 地球联邦第三序列边境殖民星球 · 官方名</t>
         </is>
       </c>
     </row>
@@ -1687,1235 +1695,1241 @@
     <row r="7" outlineLevel="1" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、辐射尘、陆海沙海、稀薄大气</t>
+          <t xml:space="preserve">    ├─ 垦锈带（民间旧称）（Folk Name） ──→ C.Y. 0– · 垦殖年代沿用，路牌与口语仍常见</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 殖民形态（Colonial Form） ──→ C.Y. 0– · 财团殖民、边境新西部、公司法自治</t>
+          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、辐射尘、陆海沙海、稀薄大气</t>
         </is>
       </c>
     </row>
     <row r="9" outlineLevel="1" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 垦历 C.Y.（Colonial Year） ──→ C.Y. 0– · 殖民年号，替代地球公历</t>
+          <t xml:space="preserve">    ├─ 殖民形态（Colonial Form） ──→ C.Y. 0– · 财团殖民、边境新西部、公司法自治</t>
         </is>
       </c>
     </row>
     <row r="10" outlineLevel="1" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 标准十二月（Standard Twelve Months） ──→ 沿用地球月份名便于行政</t>
+          <t xml:space="preserve">    ├─ 垦历 C.Y.（Colonial Year） ──→ C.Y. 0– · 殖民年号，替代地球公历</t>
         </is>
       </c>
     </row>
     <row r="11" outlineLevel="1" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 十三月 Undecimber ──→ 每年 · 闰余月 37 垦日，账外之月</t>
+          <t xml:space="preserve">    │       ├─ 标准十二月（Standard Twelve Months） ──→ 沿用地球月份名便于行政</t>
         </is>
       </c>
     </row>
     <row r="12" outlineLevel="1" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │       └─ 十三月 Undecimber ──→ 每年 · 闰余月 37 垦日，账外之月</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 当前时点（Present） ──→ C.Y. 42 · Undecimber 中旬，酒镇风暴季</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>▸ 污染官方主干</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
         </is>
       </c>
     </row>
     <row r="16" outlineLevel="1" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
         </is>
       </c>
     </row>
     <row r="17" outlineLevel="1" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="18" outlineLevel="1" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
+          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
         </is>
       </c>
     </row>
     <row r="19" outlineLevel="1" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
+          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
         </is>
       </c>
     </row>
     <row r="20" outlineLevel="1" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
         </is>
       </c>
     </row>
     <row r="21" outlineLevel="1" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
         </is>
       </c>
     </row>
-    <row r="22" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr"/>
-    </row>
     <row r="23" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>支线方案 C–F（Optional C–F） ──→ 局部 · 可作区域历史诱因，非主行星主干</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>▸ 污染起源方案</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>方案 A 深井毒卤（Deep-Brine Toxicity） ──→ 推荐主干 · 高氯酸盐/砷/铜卤层，深井采水全域污染</t>
         </is>
       </c>
     </row>
     <row r="27" outlineLevel="1" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>方案 A 深井毒卤（Deep-Brine Toxicity） ──→ 推荐主干 · 高氯酸盐/砷/铜卤层，深井采水全域污染</t>
         </is>
       </c>
     </row>
     <row r="28" outlineLevel="1" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ Undecimber 卤压峰值（Undecimber Brine Peak） ──→ 每年 · 地下卤层渗透率年度最高</t>
         </is>
       </c>
     </row>
-    <row r="29" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A29" s="7" t="inlineStr"/>
-    </row>
     <row r="30" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 本土嗜盐菌季节性神经毒素</t>
-        </is>
-      </c>
+      <c r="A30" s="7" t="inlineStr"/>
     </row>
     <row r="31" outlineLevel="1" ht="16" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 本土嗜盐菌季节性神经毒素</t>
         </is>
       </c>
     </row>
     <row r="32" outlineLevel="1" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 赤潮高峰（Red Tide Peak） ──→ Undecimber · 全年水质最差月份</t>
         </is>
       </c>
     </row>
-    <row r="33" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A33" s="7" t="inlineStr"/>
-    </row>
     <row r="34" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>方案 C terraform 遗产（Terraform Legacy） ──→ 可选 · 早期大气改造站催化剂泄漏</t>
         </is>
       </c>
     </row>
-    <row r="35" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A35" s="7" t="inlineStr"/>
-    </row>
     <row r="36" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>方案 D 矿冶尾液（Smelting Tailings） ──→ 可选 · 机甲燃料炼矿尾液渗入含水层</t>
         </is>
       </c>
     </row>
-    <row r="37" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A37" s="7" t="inlineStr"/>
-    </row>
     <row r="38" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>方案 E 化武残留（Chemical War Residue） ──→ 可选 · 殖民内战化学剂污染流域</t>
         </is>
       </c>
     </row>
-    <row r="39" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A39" s="7" t="inlineStr"/>
-    </row>
     <row r="40" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>方案 F 尘暴带电粒子（Dust Storm Ions） ──→ 可选 · 双恒星尘暴金属微粒随雨入水</t>
         </is>
       </c>
     </row>
-    <row r="41" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A41" s="7" t="inlineStr"/>
-    </row>
     <row r="42" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>推荐组合 A+B（Recommended A+B） ──→ 已并入主干 · 见「污染官方主干」模块</t>
         </is>
       </c>
     </row>
-    <row r="43" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A43" s="7" t="inlineStr"/>
-    </row>
     <row r="44" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>▸ 陆海沙海</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>陆海 / 沙海（The Landsea） ──→ 特殊密度重砂构成的陆地之海</t>
         </is>
       </c>
     </row>
     <row r="48" outlineLevel="1" ht="16" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>陆海 / 沙海（The Landsea） ──→ 特殊密度重砂构成的陆地之海</t>
         </is>
       </c>
     </row>
     <row r="49" outlineLevel="1" ht="16" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 重砂 Dense Sand ──→ 硅铁复合砂，密度约为地球沙漠沙2.8–3.2倍</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="50" outlineLevel="1" ht="16" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 流态砂波（Sand Swell） ──→ 风力与地热震动下缓慢流动如海浪</t>
+          <t xml:space="preserve">    ├─ 重砂 Dense Sand ──→ 硅铁复合砂，密度约为地球沙漠沙2.8–3.2倍</t>
         </is>
       </c>
     </row>
     <row r="51" outlineLevel="1" ht="16" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
+          <t xml:space="preserve">    ├─ 流态砂波（Sand Swell） ──→ 风力与地热震动下缓慢流动如海浪</t>
         </is>
       </c>
     </row>
     <row r="52" outlineLevel="1" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
+          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
         </is>
       </c>
     </row>
     <row r="53" outlineLevel="1" ht="16" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
+          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
         </is>
       </c>
     </row>
     <row r="54" outlineLevel="1" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
+          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
         </is>
       </c>
     </row>
     <row r="55" outlineLevel="1" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>▸ 沙豚</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>沙豚（Sand Porpoise） ──→ Magnetodelphis arenarius，本土磁泳生物</t>
         </is>
       </c>
     </row>
     <row r="59" outlineLevel="1" ht="16" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>沙豚（Sand Porpoise） ──→ Magnetodelphis arenarius，本土磁泳生物</t>
         </is>
       </c>
     </row>
     <row r="60" outlineLevel="1" ht="16" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 磁泳腺（Magneto-Swim Gland） ──→ 生物电磁器官，降低周围重砂有效密度</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="61" outlineLevel="1" ht="16" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 磁泳能力（Magneto-Swimming） ──→ 在陆海重砂中如豚类游水般前进</t>
+          <t xml:space="preserve">    ├─ 磁泳腺（Magneto-Swim Gland） ──→ 生物电磁器官，降低周围重砂有效密度</t>
         </is>
       </c>
     </row>
     <row r="62" outlineLevel="1" ht="16" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
+          <t xml:space="preserve">    ├─ 磁泳能力（Magneto-Swimming） ──→ 在陆海重砂中如豚类游水般前进</t>
         </is>
       </c>
     </row>
     <row r="63" outlineLevel="1" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 酿造帮猎杀（Cartel Hunting） ──→ C.Y. 20– · 取磁泳腺用于铁瓶导航与军用研究</t>
+          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
         </is>
       </c>
     </row>
     <row r="64" outlineLevel="1" ht="16" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews View） ──→ C.Y. 37+ · 部分派系视其为未容器化的净生者</t>
+          <t xml:space="preserve">    ├─ 酿造帮猎杀（Cartel Hunting） ──→ C.Y. 20– · 取磁泳腺用于铁瓶导航与军用研究</t>
         </is>
       </c>
     </row>
     <row r="65" outlineLevel="1" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 戒酒教收割派（Harvest Faction View） ──→ 称「会游泳的清泉使者」</t>
+          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews View） ──→ C.Y. 37+ · 部分派系视其为未容器化的净生者</t>
         </is>
       </c>
     </row>
     <row r="66" outlineLevel="1" ht="16" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 戒酒教纯净派（Purity Faction View） ──→ 视为应焚毁的脏物载体</t>
+          <t xml:space="preserve">    ├─ 戒酒教收割派（Harvest Faction View） ──→ 称「会游泳的清泉使者」</t>
         </is>
       </c>
     </row>
     <row r="67" outlineLevel="1" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
+          <t xml:space="preserve">    ├─ 戒酒教纯净派（Purity Faction View） ──→ 视为应焚毁的脏物载体</t>
         </is>
       </c>
     </row>
     <row r="68" outlineLevel="1" ht="16" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ C.Y. 42 异常迁徙（Abnormal Migration） ──→ C.Y. 42 · Undecimber大规模迁徙或催化觉醒</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>▸ 十三月 Undecimber</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
         </is>
       </c>
     </row>
     <row r="72" outlineLevel="1" ht="16" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
         </is>
       </c>
     </row>
     <row r="73" outlineLevel="1" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="74" outlineLevel="1" ht="16" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
+          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
         </is>
       </c>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
+          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
         </is>
       </c>
     </row>
     <row r="77" outlineLevel="1" ht="16" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
+          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
         </is>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="16" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
+          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
         </is>
       </c>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
+          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
         </is>
       </c>
     </row>
     <row r="80" outlineLevel="1" ht="16" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
+          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
         </is>
       </c>
     </row>
     <row r="81" outlineLevel="1" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
+          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
         </is>
       </c>
     </row>
     <row r="82" outlineLevel="1" ht="16" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 酿造帮配额重置（Quota Reset） ──→ 年度生产配额于十三月 1 日重置</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>▸ 生态酵母谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>生态酵母（基础株）（Saccharomyces vitae） ──→ C.Y. 12– · 三重净化：化学毒+生物毒+辐射尘</t>
         </is>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="16" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>生态酵母（基础株）（Saccharomyces vitae） ──→ C.Y. 12– · 三重净化：化学毒+生物毒+辐射尘</t>
         </is>
       </c>
     </row>
     <row r="87" outlineLevel="1" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ W-Strain（W-Strain (Military)） ──→ C.Y. 12–17 · 军用稳态型</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="88" outlineLevel="1" ht="16" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    ├─ W-Strain（W-Strain (Military)） ──→ C.Y. 12–17 · 军用稳态型</t>
         </is>
       </c>
     </row>
     <row r="89" outlineLevel="1" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 井源计划（Wellspring Program） ──→ C.Y. 12–17 · 第一批植入者为净水超级士兵</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="90" outlineLevel="1" ht="16" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │           │</t>
+          <t xml:space="preserve">    │       └─ 井源计划（Wellspring Program） ──→ C.Y. 12–17 · 第一批植入者为净水超级士兵</t>
         </is>
       </c>
     </row>
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
+          <t xml:space="preserve">    │           │</t>
         </is>
       </c>
     </row>
     <row r="92" outlineLevel="1" ht="16" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │               │</t>
+          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
         </is>
       </c>
     </row>
     <row r="93" outlineLevel="1" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │               └─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留 / 幸存井兵</t>
+          <t xml:space="preserve">    │               │</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="16" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ R-Strain（R-Strain (Civilian)） ──→ C.Y. 12– · 民用救灾型</t>
+          <t xml:space="preserve">    │               └─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留 / 幸存井兵</t>
         </is>
       </c>
     </row>
     <row r="95" outlineLevel="1" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    ├─ R-Strain（R-Strain (Civilian)） ──→ C.Y. 12– · 民用救灾型</t>
         </is>
       </c>
     </row>
     <row r="96" outlineLevel="1" ht="16" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 生态酿（Eco-Brew） ──→ C.Y. 12– · 2–4%，公开合法，社会认知「酵母=希望」</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1" ht="16" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ F-Strain（F-Strain (Fuel)） ──→ C.Y. 15– · 燃料高产型</t>
+          <t xml:space="preserve">    │       └─ 生态酿（Eco-Brew） ──→ C.Y. 12– · 2–4%，公开合法，社会认知「酵母=希望」</t>
         </is>
       </c>
     </row>
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 人体活体发酵容器</t>
+          <t xml:space="preserve">    └─ F-Strain（F-Strain (Fuel)） ──→ C.Y. 15– · 燃料高产型</t>
         </is>
       </c>
     </row>
     <row r="99" outlineLevel="1" ht="16" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        │   │</t>
+          <t xml:space="preserve">        ├─ 活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 人体活体发酵容器</t>
         </is>
       </c>
     </row>
     <row r="100" outlineLevel="1" ht="16" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        │       └─ 醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉容器，已基本灭绝</t>
+          <t xml:space="preserve">        │   │</t>
         </is>
       </c>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ 铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23–30 · 菌株移植至机械载体</t>
+          <t xml:space="preserve">        │       └─ 醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉容器，已基本灭绝</t>
         </is>
       </c>
     </row>
     <row r="102" outlineLevel="1" ht="16" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                ├─ 铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识机械产力，圈养/野生</t>
+          <t xml:space="preserve">        └─ 铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23–30 · 菌株移植至机械载体</t>
         </is>
       </c>
     </row>
     <row r="103" outlineLevel="1" ht="16" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                │   │</t>
+          <t xml:space="preserve">                ├─ 铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识机械产力，圈养/野生</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">            │       └─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，集体性觉醒</t>
+          <t xml:space="preserve">                │   │</t>
         </is>
       </c>
     </row>
     <row r="105" outlineLevel="1" ht="16" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">            │       └─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，集体性觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">                └─ 酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体，冲突中心</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>▸ 历史时间线</t>
         </is>
       </c>
     </row>
-    <row r="108" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
+    <row r="109" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 深井卤锈化、Undecimber 赤潮、边境崩解</t>
         </is>
       </c>
     </row>
-    <row r="109" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A109" s="7" t="inlineStr"/>
-    </row>
     <row r="110" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 垦锈带首次现场验证</t>
-        </is>
-      </c>
+      <c r="A110" s="7" t="inlineStr"/>
     </row>
     <row r="111" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A111" s="7" t="inlineStr"/>
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
+        </is>
+      </c>
     </row>
     <row r="112" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>井源计划（Wellspring Program） ──→ C.Y. 12–17 · 首批植入净水士兵，C.Y. 14 战场验证</t>
         </is>
       </c>
     </row>
-    <row r="113" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A113" s="7" t="inlineStr"/>
-    </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 醇民 Gen-0 量产</t>
         </is>
       </c>
     </row>
-    <row r="115" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A115" s="7" t="inlineStr"/>
-    </row>
     <row r="116" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>泄露与抗争（Exposure &amp; Resistance） ──→ C.Y. 20–23 · Don't Bottle Humanity! 戒酒教萌芽</t>
         </is>
       </c>
     </row>
-    <row r="117" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A117" s="7" t="inlineStr"/>
-    </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23 Undecimber · 机械燃料解放人性，醇民销毁</t>
         </is>
       </c>
     </row>
-    <row r="119" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A119" s="7" t="inlineStr"/>
-    </row>
     <row r="120" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>机械时代（Mechanical Era） ──→ C.Y. 30–37 · 铁瓶量产，酿造帮商业化</t>
         </is>
       </c>
     </row>
-    <row r="121" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A121" s="7" t="inlineStr"/>
-    </row>
     <row r="122" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37–42 · 二次发酵阈值，瓶醒/井醒</t>
         </is>
       </c>
     </row>
-    <row r="123" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A123" s="7" t="inlineStr"/>
-    </row>
     <row r="124" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>当前荒原（Present Wasteland） ──→ C.Y. 42 Undecimber · 闭环运转 × 意识反抗，赤潮高峰</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>▸ 势力格局</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
         </is>
       </c>
     </row>
     <row r="128" outlineLevel="1" ht="16" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
         </is>
       </c>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
+          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
         </is>
       </c>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
         </is>
       </c>
     </row>
-    <row r="132" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A132" s="7" t="inlineStr"/>
-    </row>
     <row r="133" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
-        </is>
-      </c>
+      <c r="A133" s="7" t="inlineStr"/>
     </row>
     <row r="134" outlineLevel="1" ht="16" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
         </is>
       </c>
     </row>
     <row r="135" outlineLevel="1" ht="16" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="136" outlineLevel="1" ht="16" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 井兵单禁忌（Well-Soldier Taboo） ──→ C.Y. 42 · 圈内不接井兵委托</t>
         </is>
       </c>
     </row>
-    <row r="137" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A137" s="7" t="inlineStr"/>
-    </row>
     <row r="138" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
-        </is>
-      </c>
+      <c r="A138" s="7" t="inlineStr"/>
     </row>
     <row r="139" outlineLevel="1" ht="16" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
         </is>
       </c>
     </row>
     <row r="140" outlineLevel="1" ht="16" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
         </is>
       </c>
     </row>
-    <row r="142" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A142" s="7" t="inlineStr"/>
-    </row>
     <row r="143" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
+      <c r="A143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
         </is>
       </c>
     </row>
-    <row r="144" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A144" s="7" t="inlineStr"/>
-    </row>
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
+      <c r="A145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
         </is>
       </c>
     </row>
-    <row r="146" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A146" s="7" t="inlineStr"/>
-    </row>
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="6" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>▸ 存在体谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>井兵（Aqua-Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
         </is>
       </c>
     </row>
     <row r="151" outlineLevel="1" ht="16" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>井兵（Aqua-Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
         </is>
       </c>
     </row>
     <row r="152" outlineLevel="1" ht="16" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
+          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
         </is>
       </c>
     </row>
     <row r="154" outlineLevel="1" ht="16" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 隐性血脉（Carrier Line） ──→ C.Y. 15– · 井醒来源</t>
         </is>
       </c>
     </row>
-    <row r="155" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A155" s="7" t="inlineStr"/>
-    </row>
     <row r="156" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
+      <c r="A156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉发酵容器，F-Strain，已灭绝</t>
         </is>
       </c>
     </row>
-    <row r="157" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A157" s="7" t="inlineStr"/>
-    </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
-        </is>
-      </c>
+      <c r="A158" s="7" t="inlineStr"/>
     </row>
     <row r="159" outlineLevel="1" ht="16" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
         </is>
       </c>
     </row>
     <row r="160" outlineLevel="1" ht="16" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 野生游荡型（Wild Roaming） ──→ C.Y. 25– · 移动绿洲，赏金目标</t>
         </is>
       </c>
     </row>
-    <row r="162" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A162" s="7" t="inlineStr"/>
-    </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
-        </is>
-      </c>
+      <c r="A163" s="7" t="inlineStr"/>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="166" outlineLevel="1" ht="16" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
+          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
         </is>
       </c>
     </row>
     <row r="167" outlineLevel="1" ht="16" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
+          <t xml:space="preserve">    ├─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
         </is>
       </c>
     </row>
     <row r="168" outlineLevel="1" ht="16" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
+          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
         </is>
       </c>
     </row>
     <row r="169" outlineLevel="1" ht="16" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 觉醒个体（Awakened Individuals） ──→ C.Y. 37+ · 独立思想者</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="6" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
         <is>
           <t>▸ 燃料闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A172" s="7" t="inlineStr">
-        <is>
-          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
         </is>
       </c>
     </row>
     <row r="174" outlineLevel="1" ht="16" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="175" outlineLevel="1" ht="16" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
         </is>
       </c>
     </row>
     <row r="176" outlineLevel="1" ht="16" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
+          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
         </is>
       </c>
     </row>
     <row r="177" outlineLevel="1" ht="16" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
         </is>
       </c>
     </row>
     <row r="178" outlineLevel="1" ht="16" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
+          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
         </is>
       </c>
     </row>
     <row r="179" outlineLevel="1" ht="16" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
         </is>
       </c>
     </row>
     <row r="180" outlineLevel="1" ht="16" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
+          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
         </is>
       </c>
     </row>
     <row r="181" outlineLevel="1" ht="16" customHeight="1">
       <c r="A181" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="6" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>▸ 讽刺主题链</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
-        <is>
-          <t>旧时代生存执念（Survival Obsession） ──→ 无论如何都要活下去</t>
         </is>
       </c>
     </row>
     <row r="185" outlineLevel="1" ht="16" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>旧时代生存执念（Survival Obsession） ──→ 无论如何都要活下去</t>
         </is>
       </c>
     </row>
     <row r="186" outlineLevel="1" ht="16" customHeight="1">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 士兵净水（Soldiers Purify Water） ──→ C.Y. 12– · 最正当的起点</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="187" outlineLevel="1" ht="16" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        │</t>
+          <t xml:space="preserve">    └─ 士兵净水（Soldiers Purify Water） ──→ C.Y. 12– · 最正当的起点</t>
         </is>
       </c>
     </row>
     <row r="188" outlineLevel="1" ht="16" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ 人体验证（Human Vessel Proven） ──→ C.Y. 14– · 技术门槛跨越</t>
+          <t xml:space="preserve">        │</t>
         </is>
       </c>
     </row>
     <row r="189" outlineLevel="1" ht="16" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">            │</t>
+          <t xml:space="preserve">        └─ 人体验证（Human Vessel Proven） ──→ C.Y. 14– · 技术门槛跨越</t>
         </is>
       </c>
     </row>
     <row r="190" outlineLevel="1" ht="16" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                └─ 贫民燃料化（Poor as Fuel） ──→ C.Y. 15– · 对象降级，话术不变</t>
+          <t xml:space="preserve">            │</t>
         </is>
       </c>
     </row>
     <row r="191" outlineLevel="1" ht="16" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    │</t>
+          <t xml:space="preserve">                └─ 贫民燃料化（Poor as Fuel） ──→ C.Y. 15– · 对象降级，话术不变</t>
         </is>
       </c>
     </row>
     <row r="192" outlineLevel="1" ht="16" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    └─ 人道抗争（Humanitarian Protest） ──→ C.Y. 20– · 别把人变成瓶子</t>
+          <t xml:space="preserve">                    │</t>
         </is>
       </c>
     </row>
     <row r="193" outlineLevel="1" ht="16" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        │</t>
+          <t xml:space="preserve">                    └─ 人道抗争（Humanitarian Protest） ──→ C.Y. 20– · 别把人变成瓶子</t>
         </is>
       </c>
     </row>
     <row r="194" outlineLevel="1" ht="16" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        └─ 铁瓶妥协（Synth-Bottle Compromise） ──→ C.Y. 23– · 机械燃料，解放人性</t>
+          <t xml:space="preserve">                        │</t>
         </is>
       </c>
     </row>
     <row r="195" outlineLevel="1" ht="16" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            │</t>
+          <t xml:space="preserve">                        └─ 铁瓶妥协（Synth-Bottle Compromise） ──→ C.Y. 23– · 机械燃料，解放人性</t>
         </is>
       </c>
     </row>
     <row r="196" outlineLevel="1" ht="16" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            └─ 机械量产（Mass Production） ──→ C.Y. 30– · 人性换效率</t>
+          <t xml:space="preserve">                            │</t>
         </is>
       </c>
     </row>
     <row r="197" outlineLevel="1" ht="16" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                │</t>
+          <t xml:space="preserve">                            └─ 机械量产（Mass Production） ──→ C.Y. 30– · 人性换效率</t>
         </is>
       </c>
     </row>
     <row r="198" outlineLevel="1" ht="16" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">                                │</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">                                └─ 酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37+ · 容器发问，闭环裂缝</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="6" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
         <is>
           <t>▸ 叙事入口</t>
         </is>
       </c>
     </row>
-    <row r="201" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A201" s="7" t="inlineStr">
+    <row r="202" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A202" s="7" t="inlineStr">
         <is>
           <t>井兵末裔（Well-Soldier Scion） ──→ C.Y. 42 · W-Strain 残留，各方追逐</t>
         </is>
       </c>
     </row>
-    <row r="202" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A202" s="7" t="inlineStr"/>
-    </row>
     <row r="203" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A203" s="7" t="inlineStr">
+      <c r="A203" s="7" t="inlineStr"/>
+    </row>
+    <row r="204" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A204" s="7" t="inlineStr">
         <is>
           <t>刚觉醒酿民（Newly Awakened Brewfolk） ──→ C.Y. 42 · 意识到自己是净水者也是油箱</t>
         </is>
       </c>
     </row>
-    <row r="204" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A204" s="7" t="inlineStr"/>
-    </row>
     <row r="205" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A205" s="7" t="inlineStr">
+      <c r="A205" s="7" t="inlineStr"/>
+    </row>
+    <row r="206" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
         <is>
           <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 赏金猎人，禁忌井兵委托</t>
         </is>
       </c>
     </row>
-    <row r="206" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A206" s="7" t="inlineStr"/>
-    </row>
     <row r="207" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A207" s="7" t="inlineStr">
+      <c r="A207" s="7" t="inlineStr"/>
+    </row>
+    <row r="208" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A208" s="7" t="inlineStr">
         <is>
           <t>Saloon 酒保（Saloon Bartender） ──→ C.Y. 42 · 半觉醒老旧铁瓶</t>
         </is>
       </c>
     </row>
-    <row r="208" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A208" s="7" t="inlineStr"/>
-    </row>
     <row r="209" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A209" s="7" t="inlineStr">
+      <c r="A209" s="7" t="inlineStr"/>
+    </row>
+    <row r="210" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A210" s="7" t="inlineStr">
         <is>
           <t>酿造帮档案员（Cartel Archivist） ──→ C.Y. 42 · 发现抗议领袖在铁瓶合同上</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="196">
+  <mergeCells count="197">
     <mergeCell ref="A128:C128"/>
     <mergeCell ref="A193:C193"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
     <mergeCell ref="A136:C136"/>
@@ -2923,8 +2937,8 @@
     <mergeCell ref="A105:C105"/>
     <mergeCell ref="A192:C192"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A210:C210"/>
     <mergeCell ref="A179:C179"/>
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A185:C185"/>
@@ -2935,7 +2949,6 @@
     <mergeCell ref="A184:C184"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
@@ -2945,6 +2958,8 @@
     <mergeCell ref="A130:C130"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A138:C138"/>
@@ -2952,10 +2967,10 @@
     <mergeCell ref="A110:C110"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A69:C69"/>
     <mergeCell ref="A196:C196"/>
     <mergeCell ref="A174:C174"/>
     <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
@@ -2970,12 +2985,11 @@
     <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A96:C96"/>
@@ -2983,6 +2997,8 @@
     <mergeCell ref="A121:C121"/>
     <mergeCell ref="A209:C209"/>
     <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A202:C202"/>
@@ -2991,9 +3007,10 @@
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A186:C186"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A201:C201"/>
-    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A82:C82"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A123:C123"/>
@@ -3005,10 +3022,7 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A187:C187"/>
     <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A149:C149"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A158:C158"/>
@@ -3022,7 +3036,6 @@
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A188:C188"/>
-    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A135:C135"/>
@@ -3032,11 +3045,13 @@
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A122:C122"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A125:C125"/>
     <mergeCell ref="A190:C190"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A199:C199"/>
     <mergeCell ref="A152:C152"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="A167:C167"/>
@@ -3044,16 +3059,15 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A182:C182"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A98:C98"/>
     <mergeCell ref="A191:C191"/>
     <mergeCell ref="A169:C169"/>
-    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A178:C178"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A153:C153"/>
     <mergeCell ref="A162:C162"/>
     <mergeCell ref="A54:C54"/>
@@ -3063,8 +3077,9 @@
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A164:C164"/>
     <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A139:C139"/>
     <mergeCell ref="A154:C154"/>
     <mergeCell ref="A129:C129"/>
@@ -3101,6 +3116,7 @@
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A103:C103"/>
     <mergeCell ref="A168:C168"/>
@@ -3117,7 +3133,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -3135,7 +3151,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>垦锈带 Calico Reach ──→ C.Y. 0– · 地球联邦第三序列边境殖民星球</t>
+          <t>赭锈带 Ochre Reach ──→ C.Y. 0– · 地球联邦第三序列边境殖民星球 · 官方名</t>
         </is>
       </c>
     </row>
@@ -3149,48 +3165,56 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、辐射尘、陆海沙海、稀薄大气</t>
+          <t xml:space="preserve">    ├─ 垦锈带（民间旧称）（Folk Name） ──→ C.Y. 0– · 垦殖年代沿用，路牌与口语仍常见</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 殖民形态（Colonial Form） ──→ C.Y. 0– · 财团殖民、边境新西部、公司法自治</t>
+          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、辐射尘、陆海沙海、稀薄大气</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 垦历 C.Y.（Colonial Year） ──→ C.Y. 0– · 殖民年号，替代地球公历</t>
+          <t xml:space="preserve">    ├─ 殖民形态（Colonial Form） ──→ C.Y. 0– · 财团殖民、边境新西部、公司法自治</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 标准十二月（Standard Twelve Months） ──→ 沿用地球月份名便于行政</t>
+          <t xml:space="preserve">    ├─ 垦历 C.Y.（Colonial Year） ──→ C.Y. 0– · 殖民年号，替代地球公历</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 十三月 Undecimber ──→ 每年 · 闰余月 37 垦日，账外之月</t>
+          <t xml:space="preserve">    │       ├─ 标准十二月（Standard Twelve Months） ──→ 沿用地球月份名便于行政</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │       └─ 十三月 Undecimber ──→ 每年 · 闰余月 37 垦日，账外之月</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 当前时点（Present） ──→ C.Y. 42 · Undecimber 中旬，酒镇风暴季</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -9,19 +9,19 @@
   <sheets>
     <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="殖民星球" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="污染官方主干" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="污染起源方案" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="陆海沙海" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="沙豚" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="十三月 Undecimber" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="生态酵母谱系" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="历史时间线" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="势力格局" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="存在体谱系" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="燃料闭环" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="讽刺主题链" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="叙事入口" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="1.1 赭锈带" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1.2 陆海沙海" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1.3 沙豚" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2.1 污染主干" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2.2 十三月" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2.3 支线方案" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3.1 生态酵母" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3.2 燃料闭环" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="4. 历史脉络" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="5. 存在体谱系" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="6. 势力格局" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="7. 讽刺主题链" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="8. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v6</t>
+          <t>2026-07-16-v7</t>
         </is>
       </c>
     </row>
@@ -513,304 +513,413 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>星球</t>
+          <t>结构</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>赭锈带 Ochre Reach（民间旧称 垦锈带 · 地球联邦边境殖民星）</t>
+          <t>舞台 → 危机 → 技术 → 历史 → 存在体 → 势力 → 主题 → 入口</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>当前</t>
+          <t>星球</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>垦历 C.Y. 42 · 十三月 Undecimber</t>
+          <t>赭锈带 Ochre Reach（民间旧称 垦锈带 · 地球联邦边境殖民星）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>污染主干</t>
+          <t>当前</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>方案 A+B+辐射尘（三层叠加）</t>
+          <t>垦历 C.Y. 42 · 十三月 Undecimber</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>污染主干</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>方案 A+B+辐射尘（三层叠加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>关联文档</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>docs/worldbuilding-tree.md</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>世界观总树</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>《瓶与井》世界观（垦历 C.Y. 42 · 赛博西部 / 生物朋克 / 殖民科幻）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>《瓶与井》故事背景（垦历 C.Y. 42 · 十三月 Undecimber）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 赭锈带 Ochre Reach ──→ 边境殖民星 · 陆海沙海 · 辐射尘</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 民间旧称：垦锈带</t>
+          <t xml:space="preserve">    ├─ 【命题】掘井求生 → 造瓶产油</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 旧时代生存执念 → 燃料永续闭环 → 酿民觉醒（裂缝）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 锈水三层（官方主干 A+B+辐射尘）</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 化学层：深井毒卤</t>
+          <t xml:space="preserve">    ├─ 【舞台】赭锈带 Ochre Reach（民间旧称：垦锈带）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 生物层：流浪赤潮（Undecimber 峰值）</t>
+          <t xml:space="preserve">    │       ├─ 边境殖民星 · 新西部社会 · 垦历 C.Y.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 放射层：辐射尘（沙海富集）</t>
+          <t xml:space="preserve">    │       ├─ 陆海 / 沙海（重砂流态海 · 辐射尘富集）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 沙豚（磁泳生物 · 第四镜像）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生态酵母 ──→ 三重净化 · 2–4% 生态酿 · 40%+ 燃料乙醇</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ W/R/F-Strain → 井兵 / 醇民 / 铁瓶 / 酿民</t>
+          <t xml:space="preserve">    ├─ 【危机】锈水 Rustwater（A + B + 辐射尘）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       ├─ 化学层：深井毒卤（全年）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 陆海 + 沙豚 ──→ 重砂流态海 · 磁泳生物</t>
+          <t xml:space="preserve">    │       ├─ 生物层：流浪赤潮（Undecimber 峰值）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       ├─ 放射层：辐射尘（沙海扬尘 · Undecimber 叠加）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 十三月 Undecimber ──→ 账外之月 · 水质最差 · 觉醒临界</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+          <t xml:space="preserve">    │       └─ 十三月 Undecimber ──→ 账外之月 · 全年最毒 · 觉醒临界</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 【应答】生态酵母 Saccharomyces vitae</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 三重净化锈水 → 2–4% 生态酿（活命）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 二次发酵 → 40%+ 燃料乙醇（驱动世界）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 谱系：W/R/F-Strain → 井兵 / 醇民 / 铁瓶 / 酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 【历史】C.Y. 5 锈水时代 → C.Y. 12 酵母 → C.Y. 23 铁瓶 → C.Y. 42 觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 【存在体】井兵（平行）· 醇民 Gen-0（绝种）· 铁瓶 Gen-1 · 酿民 Gen-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 【势力】酿造帮 · 赏金猎人 · 戒酒教 · 流浪酒帮 · Saloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 【当前】闭环运转 × 意识反抗 · 酒镇风暴眼 · 赤潮高峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>模块索引</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  01. 殖民星球</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  02. 污染官方主干</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  03. 污染起源方案</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04. 陆海沙海</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  05. 沙豚</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  06. 十三月 Undecimber</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  07. 生态酵母谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  08. 历史时间线</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  09. 势力格局</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10. 存在体谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  11. 燃料闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  12. 讽刺主题链</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  13. 叙事入口</t>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  01. 1.1 赭锈带</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  02. 1.2 陆海沙海</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  03. 1.3 沙豚</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  04. 2.1 污染主干</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  05. 2.2 十三月</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  06. 2.3 支线方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  07. 3.1 生态酵母</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  08. 3.2 燃料闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  09. 4. 历史脉络</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10. 5. 存在体谱系</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11. 6. 势力格局</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. 7. 讽刺主题链</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. 8. 叙事入口</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="50">
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A34:C34"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A16:C16"/>
@@ -820,6 +929,114 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与井》· 3.2 燃料闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -835,7 +1052,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 历史时间线</t>
+          <t>《瓶与井》· 4. 历史脉络</t>
         </is>
       </c>
     </row>
@@ -951,182 +1168,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 势力格局</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 井兵单禁忌（Well-Soldier Taboo） ──→ C.Y. 42 · 圈内不接井兵委托</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1143,7 +1184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 存在体谱系</t>
+          <t>《瓶与井》· 5. 存在体谱系</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1349,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1319,14 +1360,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 燃料闭环</t>
+          <t>《瓶与井》· 6. 势力格局</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
+          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
         </is>
       </c>
     </row>
@@ -1340,72 +1381,140 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
+          <t xml:space="preserve">    └─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
+          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
+          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
+          <t xml:space="preserve">    └─ 井兵单禁忌（Well-Soldier Taboo） ──→ C.Y. 42 · 圈内不接井兵委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="22">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1427,7 +1536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 讽刺主题链</t>
+          <t>《瓶与井》· 7. 讽刺主题链</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1684,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 叙事入口</t>
+          <t>《瓶与井》· 8. 叙事入口</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1783,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>▸ 殖民星球</t>
+          <t>▸ 1.1 赭锈带</t>
         </is>
       </c>
     </row>
@@ -1744,14 +1853,14 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>▸ 污染官方主干</t>
+          <t>▸ 1.2 陆海沙海</t>
         </is>
       </c>
     </row>
     <row r="16" outlineLevel="1" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
+          <t>陆海 / 沙海（The Landsea） ──→ 特殊密度重砂构成的陆地之海</t>
         </is>
       </c>
     </row>
@@ -1765,59 +1874,63 @@
     <row r="18" outlineLevel="1" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
+          <t xml:space="preserve">    ├─ 重砂 Dense Sand ──→ 硅铁复合砂，密度约为地球沙漠沙2.8–3.2倍</t>
         </is>
       </c>
     </row>
     <row r="19" outlineLevel="1" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
+          <t xml:space="preserve">    ├─ 流态砂波（Sand Swell） ──→ 风力与地热震动下缓慢流动如海浪</t>
         </is>
       </c>
     </row>
     <row r="20" outlineLevel="1" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
+          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
         </is>
       </c>
     </row>
     <row r="21" outlineLevel="1" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
         </is>
       </c>
     </row>
     <row r="22" outlineLevel="1" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
+          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
         </is>
       </c>
     </row>
     <row r="23" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr"/>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
+        </is>
+      </c>
     </row>
     <row r="24" outlineLevel="1" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 可作区域历史诱因，非主行星主干</t>
+          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>▸ 污染起源方案</t>
+          <t>▸ 1.3 沙豚</t>
         </is>
       </c>
     </row>
     <row r="27" outlineLevel="1" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>方案 A 深井毒卤（Deep-Brine Toxicity） ──→ 推荐主干 · 高氯酸盐/砷/铜卤层，深井采水全域污染</t>
+          <t>沙豚（Sand Porpoise） ──→ Magnetodelphis arenarius，本土磁泳生物</t>
         </is>
       </c>
     </row>
@@ -1831,343 +1944,339 @@
     <row r="29" outlineLevel="1" ht="16" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ Undecimber 卤压峰值（Undecimber Brine Peak） ──→ 每年 · 地下卤层渗透率年度最高</t>
+          <t xml:space="preserve">    ├─ 磁泳腺（Magneto-Swim Gland） ──→ 生物电磁器官，降低周围重砂有效密度</t>
         </is>
       </c>
     </row>
     <row r="30" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A30" s="7" t="inlineStr"/>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 磁泳能力（Magneto-Swimming） ──→ 在陆海重砂中如豚类游水般前进</t>
+        </is>
+      </c>
     </row>
     <row r="31" outlineLevel="1" ht="16" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 本土嗜盐菌季节性神经毒素</t>
+          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
         </is>
       </c>
     </row>
     <row r="32" outlineLevel="1" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 酿造帮猎杀（Cartel Hunting） ──→ C.Y. 20– · 取磁泳腺用于铁瓶导航与军用研究</t>
         </is>
       </c>
     </row>
     <row r="33" outlineLevel="1" ht="16" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赤潮高峰（Red Tide Peak） ──→ Undecimber · 全年水质最差月份</t>
+          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews View） ──→ C.Y. 37+ · 部分派系视其为未容器化的净生者</t>
         </is>
       </c>
     </row>
     <row r="34" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A34" s="7" t="inlineStr"/>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 戒酒教收割派（Harvest Faction View） ──→ 称「会游泳的清泉使者」</t>
+        </is>
+      </c>
     </row>
     <row r="35" outlineLevel="1" ht="16" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>方案 C terraform 遗产（Terraform Legacy） ──→ 可选 · 早期大气改造站催化剂泄漏</t>
+          <t xml:space="preserve">    ├─ 戒酒教纯净派（Purity Faction View） ──→ 视为应焚毁的脏物载体</t>
         </is>
       </c>
     </row>
     <row r="36" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A36" s="7" t="inlineStr"/>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
+        </is>
+      </c>
     </row>
     <row r="37" outlineLevel="1" ht="16" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>方案 D 矿冶尾液（Smelting Tailings） ──→ 可选 · 机甲燃料炼矿尾液渗入含水层</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>方案 E 化武残留（Chemical War Residue） ──→ 可选 · 殖民内战化学剂污染流域</t>
+          <t xml:space="preserve">    └─ C.Y. 42 异常迁徙（Abnormal Migration） ──→ C.Y. 42 · Undecimber大规模迁徙或催化觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2.1 污染主干</t>
         </is>
       </c>
     </row>
     <row r="40" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A40" s="7" t="inlineStr"/>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
+        </is>
+      </c>
     </row>
     <row r="41" outlineLevel="1" ht="16" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>方案 F 尘暴带电粒子（Dust Storm Ions） ──→ 可选 · 双恒星尘暴金属微粒随雨入水</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="42" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A42" s="7" t="inlineStr"/>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
+        </is>
+      </c>
     </row>
     <row r="43" outlineLevel="1" ht="16" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>推荐组合 A+B（Recommended A+B） ──→ 已并入主干 · 见「污染官方主干」模块</t>
+          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
         </is>
       </c>
     </row>
     <row r="44" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A44" s="7" t="inlineStr"/>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
+        </is>
+      </c>
     </row>
     <row r="45" outlineLevel="1" ht="16" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>▸ 陆海沙海</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A47" s="7" t="inlineStr"/>
     </row>
     <row r="48" outlineLevel="1" ht="16" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>陆海 / 沙海（The Landsea） ──→ 特殊密度重砂构成的陆地之海</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 重砂 Dense Sand ──→ 硅铁复合砂，密度约为地球沙漠沙2.8–3.2倍</t>
+          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 可作区域历史诱因，非主行星主干</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2.2 十三月</t>
         </is>
       </c>
     </row>
     <row r="51" outlineLevel="1" ht="16" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 流态砂波（Sand Swell） ──→ 风力与地热震动下缓慢流动如海浪</t>
+          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
         </is>
       </c>
     </row>
     <row r="52" outlineLevel="1" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="53" outlineLevel="1" ht="16" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
+          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
         </is>
       </c>
     </row>
     <row r="54" outlineLevel="1" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
         </is>
       </c>
     </row>
     <row r="55" outlineLevel="1" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
+          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
         </is>
       </c>
     </row>
     <row r="56" outlineLevel="1" ht="16" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>▸ 沙豚</t>
+          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
         </is>
       </c>
     </row>
     <row r="59" outlineLevel="1" ht="16" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>沙豚（Sand Porpoise） ──→ Magnetodelphis arenarius，本土磁泳生物</t>
+          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
         </is>
       </c>
     </row>
     <row r="60" outlineLevel="1" ht="16" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
         </is>
       </c>
     </row>
     <row r="61" outlineLevel="1" ht="16" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 磁泳腺（Magneto-Swim Gland） ──→ 生物电磁器官，降低周围重砂有效密度</t>
+          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
         </is>
       </c>
     </row>
     <row r="62" outlineLevel="1" ht="16" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 磁泳能力（Magneto-Swimming） ──→ 在陆海重砂中如豚类游水般前进</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 酿造帮猎杀（Cartel Hunting） ──→ C.Y. 20– · 取磁泳腺用于铁瓶导航与军用研究</t>
+          <t xml:space="preserve">    └─ 酿造帮配额重置（Quota Reset） ──→ 年度生产配额于十三月 1 日重置</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2.3 支线方案</t>
         </is>
       </c>
     </row>
     <row r="65" outlineLevel="1" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews View） ──→ C.Y. 37+ · 部分派系视其为未容器化的净生者</t>
+          <t>方案 A 深井毒卤（Deep-Brine Toxicity） ──→ 推荐主干 · 高氯酸盐/砷/铜卤层，深井采水全域污染</t>
         </is>
       </c>
     </row>
     <row r="66" outlineLevel="1" ht="16" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 戒酒教收割派（Harvest Faction View） ──→ 称「会游泳的清泉使者」</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="67" outlineLevel="1" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 戒酒教纯净派（Purity Faction View） ──→ 视为应焚毁的脏物载体</t>
+          <t xml:space="preserve">    └─ Undecimber 卤压峰值（Undecimber Brine Peak） ──→ 每年 · 地下卤层渗透率年度最高</t>
         </is>
       </c>
     </row>
     <row r="68" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
-        </is>
-      </c>
+      <c r="A68" s="7" t="inlineStr"/>
     </row>
     <row r="69" outlineLevel="1" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ C.Y. 42 异常迁徙（Abnormal Migration） ──→ C.Y. 42 · Undecimber大规模迁徙或催化觉醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>▸ 十三月 Undecimber</t>
+          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 本土嗜盐菌季节性神经毒素</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 赤潮高峰（Red Tide Peak） ──→ Undecimber · 全年水质最差月份</t>
         </is>
       </c>
     </row>
     <row r="72" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
-        </is>
-      </c>
+      <c r="A72" s="7" t="inlineStr"/>
     </row>
     <row r="73" outlineLevel="1" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>方案 C terraform 遗产（Terraform Legacy） ──→ 可选 · 早期大气改造站催化剂泄漏</t>
         </is>
       </c>
     </row>
     <row r="74" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
-        </is>
-      </c>
+      <c r="A74" s="7" t="inlineStr"/>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
+          <t>方案 D 矿冶尾液（Smelting Tailings） ──→ 可选 · 机甲燃料炼矿尾液渗入含水层</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
-        </is>
-      </c>
+      <c r="A76" s="7" t="inlineStr"/>
     </row>
     <row r="77" outlineLevel="1" ht="16" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
+          <t>方案 E 化武残留（Chemical War Residue） ──→ 可选 · 殖民内战化学剂污染流域</t>
         </is>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
-        </is>
-      </c>
+      <c r="A78" s="7" t="inlineStr"/>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
+          <t>方案 F 尘暴带电粒子（Dust Storm Ions） ──→ 可选 · 双恒星尘暴金属微粒随雨入水</t>
         </is>
       </c>
     </row>
     <row r="80" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
-        </is>
-      </c>
+      <c r="A80" s="7" t="inlineStr"/>
     </row>
     <row r="81" outlineLevel="1" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
+          <t>推荐组合 A+B（Recommended A+B） ──→ 已并入主干 · 见「污染官方主干」模块</t>
         </is>
       </c>
     </row>
     <row r="82" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
-        </is>
-      </c>
+      <c r="A82" s="7" t="inlineStr"/>
     </row>
     <row r="83" outlineLevel="1" ht="16" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 酿造帮配额重置（Quota Reset） ──→ 年度生产配额于十三月 1 日重置</t>
+          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>▸ 生态酵母谱系</t>
+          <t>▸ 3.1 生态酵母</t>
         </is>
       </c>
     </row>
@@ -2321,74 +2430,91 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>▸ 历史时间线</t>
+          <t>▸ 3.2 燃料闭环</t>
         </is>
       </c>
     </row>
     <row r="109" outlineLevel="1" ht="16" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 深井卤锈化、Undecimber 赤潮、边境崩解</t>
+          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
         </is>
       </c>
     </row>
     <row r="110" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A110" s="7" t="inlineStr"/>
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="111" outlineLevel="1" ht="16" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
+          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
         </is>
       </c>
     </row>
     <row r="112" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A112" s="7" t="inlineStr"/>
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+        </is>
+      </c>
     </row>
     <row r="113" outlineLevel="1" ht="16" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>井源计划（Wellspring Program） ──→ C.Y. 12–17 · 首批植入净水士兵，C.Y. 14 战场验证</t>
+          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A114" s="7" t="inlineStr"/>
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+        </is>
+      </c>
     </row>
     <row r="115" outlineLevel="1" ht="16" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 醇民 Gen-0 量产</t>
+          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
         </is>
       </c>
     </row>
     <row r="116" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A116" s="7" t="inlineStr"/>
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+        </is>
+      </c>
     </row>
     <row r="117" outlineLevel="1" ht="16" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>泄露与抗争（Exposure &amp; Resistance） ──→ C.Y. 20–23 · Don't Bottle Humanity! 戒酒教萌芽</t>
+          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A118" s="7" t="inlineStr"/>
-    </row>
-    <row r="119" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23 Undecimber · 机械燃料解放人性，醇民销毁</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A120" s="7" t="inlineStr"/>
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>▸ 4. 历史脉络</t>
+        </is>
+      </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>机械时代（Mechanical Era） ──→ C.Y. 30–37 · 铁瓶量产，酿造帮商业化</t>
+          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 深井卤锈化、Undecimber 赤潮、边境崩解</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2524,7 @@
     <row r="123" outlineLevel="1" ht="16" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37–42 · 二次发酵阈值，瓶醒/井醒</t>
+          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
         </is>
       </c>
     </row>
@@ -2408,121 +2534,109 @@
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>当前荒原（Present Wasteland） ──→ C.Y. 42 Undecimber · 闭环运转 × 意识反抗，赤潮高峰</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>▸ 势力格局</t>
+          <t>井源计划（Wellspring Program） ──→ C.Y. 12–17 · 首批植入净水士兵，C.Y. 14 战场验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 醇民 Gen-0 量产</t>
         </is>
       </c>
     </row>
     <row r="128" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
-        </is>
-      </c>
+      <c r="A128" s="7" t="inlineStr"/>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>泄露与抗争（Exposure &amp; Resistance） ──→ C.Y. 20–23 · Don't Bottle Humanity! 戒酒教萌芽</t>
         </is>
       </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
-        </is>
-      </c>
+      <c r="A130" s="7" t="inlineStr"/>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
+          <t>铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23 Undecimber · 机械燃料解放人性，醇民销毁</t>
         </is>
       </c>
     </row>
     <row r="132" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
-        </is>
-      </c>
+      <c r="A132" s="7" t="inlineStr"/>
     </row>
     <row r="133" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A133" s="7" t="inlineStr"/>
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>机械时代（Mechanical Era） ──→ C.Y. 30–37 · 铁瓶量产，酿造帮商业化</t>
+        </is>
+      </c>
     </row>
     <row r="134" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
-        </is>
-      </c>
+      <c r="A134" s="7" t="inlineStr"/>
     </row>
     <row r="135" outlineLevel="1" ht="16" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37–42 · 二次发酵阈值，瓶醒/井醒</t>
         </is>
       </c>
     </row>
     <row r="136" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
-        </is>
-      </c>
+      <c r="A136" s="7" t="inlineStr"/>
     </row>
     <row r="137" outlineLevel="1" ht="16" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 井兵单禁忌（Well-Soldier Taboo） ──→ C.Y. 42 · 圈内不接井兵委托</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A138" s="7" t="inlineStr"/>
-    </row>
-    <row r="139" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
+          <t>当前荒原（Present Wasteland） ──→ C.Y. 42 Undecimber · 闭环运转 × 意识反抗，赤潮高峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5. 存在体谱系</t>
         </is>
       </c>
     </row>
     <row r="140" outlineLevel="1" ht="16" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>井兵（Aqua-Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
         </is>
       </c>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="142" outlineLevel="1" ht="16" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
+          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
         </is>
       </c>
     </row>
     <row r="143" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A143" s="7" t="inlineStr"/>
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
+        </is>
+      </c>
     </row>
     <row r="144" outlineLevel="1" ht="16" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
+          <t xml:space="preserve">    └─ 隐性血脉（Carrier Line） ──→ C.Y. 15– · 井醒来源</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2646,7 @@
     <row r="146" outlineLevel="1" ht="16" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
+          <t>醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉发酵容器，F-Strain，已灭绝</t>
         </is>
       </c>
     </row>
@@ -2542,156 +2656,163 @@
     <row r="148" outlineLevel="1" ht="16" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>▸ 存在体谱系</t>
+          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
         </is>
       </c>
     </row>
     <row r="151" outlineLevel="1" ht="16" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>井兵（Aqua-Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
+          <t xml:space="preserve">    └─ 野生游荡型（Wild Roaming） ──→ C.Y. 25– · 移动绿洲，赏金目标</t>
         </is>
       </c>
     </row>
     <row r="152" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A152" s="7" t="inlineStr"/>
     </row>
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
+          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
         </is>
       </c>
     </row>
     <row r="154" outlineLevel="1" ht="16" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="155" outlineLevel="1" ht="16" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 隐性血脉（Carrier Line） ──→ C.Y. 15– · 井醒来源</t>
+          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
         </is>
       </c>
     </row>
     <row r="156" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A156" s="7" t="inlineStr"/>
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
+        </is>
+      </c>
     </row>
     <row r="157" outlineLevel="1" ht="16" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉发酵容器，F-Strain，已灭绝</t>
+          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
         </is>
       </c>
     </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A158" s="7" t="inlineStr"/>
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
+        </is>
+      </c>
     </row>
     <row r="159" outlineLevel="1" ht="16" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
+          <t xml:space="preserve">    └─ 觉醒个体（Awakened Individuals） ──→ C.Y. 37+ · 独立思想者</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>▸ 6. 势力格局</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 野生游荡型（Wild Roaming） ──→ C.Y. 25– · 移动绿洲，赏金目标</t>
+          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
         </is>
       </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A163" s="7" t="inlineStr"/>
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
+          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
         </is>
       </c>
     </row>
     <row r="166" outlineLevel="1" ht="16" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
+          <t xml:space="preserve">    └─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
         </is>
       </c>
     </row>
     <row r="167" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
-        </is>
-      </c>
+      <c r="A167" s="7" t="inlineStr"/>
     </row>
     <row r="168" outlineLevel="1" ht="16" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
+          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
         </is>
       </c>
     </row>
     <row r="169" outlineLevel="1" ht="16" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="170" outlineLevel="1" ht="16" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 觉醒个体（Awakened Individuals） ──→ C.Y. 37+ · 独立思想者</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="6" t="inlineStr">
-        <is>
-          <t>▸ 燃料闭环</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 井兵单禁忌（Well-Soldier Taboo） ──→ C.Y. 42 · 圈内不接井兵委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A172" s="7" t="inlineStr"/>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
+          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
         </is>
       </c>
     </row>
@@ -2705,63 +2826,51 @@
     <row r="175" outlineLevel="1" ht="16" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
         </is>
       </c>
     </row>
     <row r="176" outlineLevel="1" ht="16" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
         </is>
       </c>
     </row>
     <row r="177" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A177" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
-        </is>
-      </c>
+      <c r="A177" s="7" t="inlineStr"/>
     </row>
     <row r="178" outlineLevel="1" ht="16" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
         </is>
       </c>
     </row>
     <row r="179" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
-        </is>
-      </c>
+      <c r="A179" s="7" t="inlineStr"/>
     </row>
     <row r="180" outlineLevel="1" ht="16" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
         </is>
       </c>
     </row>
     <row r="181" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A181" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
-        </is>
-      </c>
+      <c r="A181" s="7" t="inlineStr"/>
     </row>
     <row r="182" outlineLevel="1" ht="16" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
+          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>▸ 讽刺主题链</t>
+          <t>▸ 7. 讽刺主题链</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2982,7 @@
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>▸ 叙事入口</t>
+          <t>▸ 8. 叙事入口</t>
         </is>
       </c>
     </row>
@@ -2930,6 +3039,7 @@
     <mergeCell ref="A193:C193"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
     <mergeCell ref="A136:C136"/>
@@ -2937,6 +3047,7 @@
     <mergeCell ref="A105:C105"/>
     <mergeCell ref="A192:C192"/>
     <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
     <mergeCell ref="A210:C210"/>
     <mergeCell ref="A179:C179"/>
@@ -2949,9 +3060,9 @@
     <mergeCell ref="A184:C184"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A63:C63"/>
     <mergeCell ref="A155:C155"/>
     <mergeCell ref="A93:C93"/>
     <mergeCell ref="A173:C173"/>
@@ -2961,12 +3072,9 @@
     <mergeCell ref="A83:C83"/>
     <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A138:C138"/>
     <mergeCell ref="A132:C132"/>
     <mergeCell ref="A110:C110"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
     <mergeCell ref="A196:C196"/>
     <mergeCell ref="A174:C174"/>
@@ -2981,7 +3089,6 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A95:C95"/>
     <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A160:C160"/>
     <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A32:C32"/>
@@ -2991,11 +3098,10 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A38:C38"/>
     <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A147:C147"/>
     <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A170:C170"/>
@@ -3023,6 +3129,7 @@
     <mergeCell ref="A187:C187"/>
     <mergeCell ref="A99:C99"/>
     <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A149:C149"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A158:C158"/>
@@ -3036,6 +3143,7 @@
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A188:C188"/>
+    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A135:C135"/>
@@ -3068,6 +3176,7 @@
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A153:C153"/>
     <mergeCell ref="A162:C162"/>
     <mergeCell ref="A54:C54"/>
@@ -3144,7 +3253,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 殖民星球</t>
+          <t>《瓶与井》· 1.1 赭锈带</t>
         </is>
       </c>
     </row>
@@ -3244,14 +3353,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 污染官方主干</t>
+          <t>《瓶与井》· 1.2 陆海沙海</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
+          <t>陆海 / 沙海（The Landsea） ──→ 特殊密度重砂构成的陆地之海</t>
         </is>
       </c>
     </row>
@@ -3265,45 +3374,49 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
+          <t xml:space="preserve">    ├─ 重砂 Dense Sand ──→ 硅铁复合砂，密度约为地球沙漠沙2.8–3.2倍</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
+          <t xml:space="preserve">    ├─ 流态砂波（Sand Swell） ──→ 风力与地热震动下缓慢流动如海浪</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
+          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
+          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 可作区域历史诱因，非主行星主干</t>
+          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
         </is>
       </c>
     </row>
@@ -3329,6 +3442,342 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与井》· 1.3 沙豚</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>沙豚（Sand Porpoise） ──→ Magnetodelphis arenarius，本土磁泳生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 磁泳腺（Magneto-Swim Gland） ──→ 生物电磁器官，降低周围重砂有效密度</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 磁泳能力（Magneto-Swimming） ──→ 在陆海重砂中如豚类游水般前进</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 酿造帮猎杀（Cartel Hunting） ──→ C.Y. 20– · 取磁泳腺用于铁瓶导航与军用研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews View） ──→ C.Y. 37+ · 部分派系视其为未容器化的净生者</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 戒酒教收割派（Harvest Faction View） ──→ 称「会游泳的清泉使者」</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 戒酒教纯净派（Purity Faction View） ──→ 视为应焚毁的脏物载体</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ C.Y. 42 异常迁徙（Abnormal Migration） ──→ C.Y. 42 · Undecimber大规模迁徙或催化觉醒</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与井》· 2.1 污染主干</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 可作区域历史诱因，非主行星主干</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与井》· 2.2 十三月</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 酿造帮配额重置（Quota Reset） ──→ 年度生产配额于十三月 1 日重置</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3340,7 +3789,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 污染起源方案</t>
+          <t>《瓶与井》· 2.3 支线方案</t>
         </is>
       </c>
     </row>
@@ -3476,346 +3925,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 陆海沙海</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>陆海 / 沙海（The Landsea） ──→ 特殊密度重砂构成的陆地之海</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 重砂 Dense Sand ──→ 硅铁复合砂，密度约为地球沙漠沙2.8–3.2倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 流态砂波（Sand Swell） ──→ 风力与地热震动下缓慢流动如海浪</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 沙豚</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>沙豚（Sand Porpoise） ──→ Magnetodelphis arenarius，本土磁泳生物</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 磁泳腺（Magneto-Swim Gland） ──→ 生物电磁器官，降低周围重砂有效密度</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 磁泳能力（Magneto-Swimming） ──→ 在陆海重砂中如豚类游水般前进</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 酿造帮猎杀（Cartel Hunting） ──→ C.Y. 20– · 取磁泳腺用于铁瓶导航与军用研究</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews View） ──→ C.Y. 37+ · 部分派系视其为未容器化的净生者</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 戒酒教收割派（Harvest Faction View） ──→ 称「会游泳的清泉使者」</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 戒酒教纯净派（Purity Faction View） ──→ 视为应焚毁的脏物载体</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ C.Y. 42 异常迁徙（Abnormal Migration） ──→ C.Y. 42 · Undecimber大规模迁徙或催化觉醒</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 十三月 Undecimber</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 酿造帮配额重置（Quota Reset） ──→ 年度生产配额于十三月 1 日重置</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3832,7 +3941,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 生态酵母谱系</t>
+          <t>《瓶与井》· 3.1 生态酵母</t>
         </is>
       </c>
     </row>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -12,16 +12,18 @@
     <sheet name="1.1 赭锈带" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="1.2 陆海沙海" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="1.3 沙豚" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2.1 污染主干" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2.2 十三月" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2.3 支线方案" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="3.1 生态酵母" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="3.2 燃料闭环" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="4. 历史脉络" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="5. 存在体谱系" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="6. 势力格局" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="7. 讽刺主题链" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="8. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2.0 污染起因" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2.1 污染主干" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2.2 垦区源网" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2.3 十三月" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2.4 支线方案" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3.1 生态酵母" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3.2 燃料闭环" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="4. 历史脉络" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="5. 存在体谱系" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6. 势力格局" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="7. 讽刺主题链" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="8. 叙事入口" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -482,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》世界观树状图</t>
+          <t>《瓶与源》世界观树状图</t>
         </is>
       </c>
     </row>
@@ -494,7 +496,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v7</t>
+          <t>2026-07-16-v8</t>
         </is>
       </c>
     </row>
@@ -518,7 +520,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>舞台 → 危机 → 技术 → 历史 → 存在体 → 势力 → 主题 → 入口</t>
+          <t>舞台 → 危机(起因+源网) → 技术 → 历史 → 存在体 → 势力 → 主题 → 入口</t>
         </is>
       </c>
     </row>
@@ -580,7 +582,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>《瓶与井》故事背景（垦历 C.Y. 42 · 十三月 Undecimber）</t>
+          <t>《瓶与源》故事背景（垦历 C.Y. 42 · 十三月 Undecimber）</t>
         </is>
       </c>
     </row>
@@ -594,7 +596,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【命题】掘井求生 → 造瓶产油</t>
+          <t xml:space="preserve">    ├─ 【命题】引源求生 → 造瓶产油</t>
         </is>
       </c>
     </row>
@@ -622,14 +624,14 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 边境殖民星 · 新西部社会 · 垦历 C.Y.</t>
+          <t xml:space="preserve">    │       ├─ 边境殖民星 · 卤缘渗出 · 冷凝塔网 · 垦区源网</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 陆海 / 沙海（重砂流态海 · 辐射尘富集）</t>
+          <t xml:space="preserve">    │       ├─ 陆海 / 沙海（重砂流态海 · 卤缘 · 辐射尘富集）</t>
         </is>
       </c>
     </row>
@@ -657,7 +659,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 化学层：深井毒卤（全年）</t>
+          <t xml:space="preserve">    │       ├─ 化学层：陆海卤缘渗出（全年）</t>
         </is>
       </c>
     </row>
@@ -671,208 +673,229 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 放射层：辐射尘（沙海扬尘 · Undecimber 叠加）</t>
+          <t xml:space="preserve">    │       ├─ 放射层：辐射尘（冷凝塔/源网 · Undecimber 叠加）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 十三月 Undecimber ──→ 账外之月 · 全年最毒 · 觉醒临界</t>
+          <t xml:space="preserve">    │       ├─ 殖民诱因：卤缘渠网+冷凝并网 → 源网交叉污染</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 十三月 Undecimber ──→ 卤潮涨幅 · 全年最毒 · 觉醒临界</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【应答】生态酵母 Saccharomyces vitae</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 三重净化锈水 → 2–4% 生态酿（活命）</t>
+          <t xml:space="preserve">    ├─ 【应答】生态酵母 Saccharomyces vitae</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 二次发酵 → 40%+ 燃料乙醇（驱动世界）</t>
+          <t xml:space="preserve">    │       ├─ 三重净化锈水 → 2–4% 生态酿（活命）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 谱系：W/R/F-Strain → 井兵 / 醇民 / 铁瓶 / 酿民</t>
+          <t xml:space="preserve">    │       ├─ 二次发酵 → 40%+ 燃料乙醇（驱动世界）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 谱系：W/R/F-Strain → 滤兵 / 醇民 / 铁瓶 / 酿民</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【历史】C.Y. 5 锈水时代 → C.Y. 12 酵母 → C.Y. 23 铁瓶 → C.Y. 42 觉醒</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 【历史】C.Y. 5 锈水时代 → C.Y. 12 酵母 → C.Y. 23 铁瓶 → C.Y. 42 觉醒</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【存在体】井兵（平行）· 醇民 Gen-0（绝种）· 铁瓶 Gen-1 · 酿民 Gen-2</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 【存在体】滤兵（平行）· 醇民 Gen-0（绝种）· 铁瓶 Gen-1 · 酿民 Gen-2</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【势力】酿造帮 · 赏金猎人 · 戒酒教 · 流浪酒帮 · Saloon</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 【势力】酿造帮 · 赏金猎人 · 戒酒教 · 流浪酒帮 · Saloon</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 【当前】闭环运转 × 意识反抗 · 酒镇风暴眼 · 赤潮高峰</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>模块索引</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  01. 1.1 赭锈带</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  02. 1.2 陆海沙海</t>
+          <t xml:space="preserve">  01. 1.1 赭锈带</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  03. 1.3 沙豚</t>
+          <t xml:space="preserve">  02. 1.2 陆海沙海</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  04. 2.1 污染主干</t>
+          <t xml:space="preserve">  03. 1.3 沙豚</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  05. 2.2 十三月</t>
+          <t xml:space="preserve">  04. 2.0 污染起因</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  06. 2.3 支线方案</t>
+          <t xml:space="preserve">  05. 2.1 污染主干</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  07. 3.1 生态酵母</t>
+          <t xml:space="preserve">  06. 2.2 垦区源网</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  08. 3.2 燃料闭环</t>
+          <t xml:space="preserve">  07. 2.3 十三月</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  09. 4. 历史脉络</t>
+          <t xml:space="preserve">  08. 2.4 支线方案</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. 5. 存在体谱系</t>
+          <t xml:space="preserve">  09. 3.1 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. 6. 势力格局</t>
+          <t xml:space="preserve">  10. 3.2 燃料闭环</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12. 7. 讽刺主题链</t>
+          <t xml:space="preserve">  11. 4. 历史脉络</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. 8. 叙事入口</t>
+          <t xml:space="preserve">  12. 5. 存在体谱系</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. 6. 势力格局</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14. 7. 讽刺主题链</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  15. 8. 叙事入口</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="53">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A37:C37"/>
@@ -880,12 +903,14 @@
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A23:C23"/>
@@ -906,6 +931,7 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A34:C34"/>
@@ -933,7 +959,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -944,14 +970,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 3.2 燃料闭环</t>
+          <t>《瓶与源》· 2.4 支线方案</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
+          <t>方案 A 陆海卤缘（Landsea Brine Rim） ──→ 推荐主干 · 盆地边缘天然卤渗出+卤缘渠网集中扩散</t>
         </is>
       </c>
     </row>
@@ -965,141 +991,41 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+          <t xml:space="preserve">    └─ Undecimber 卤潮涨幅（Undecimber Brine Surge） ──→ 每年 · 陆海砂潮上涨，卤缘渗出率年度最高</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
-        </is>
-      </c>
+      <c r="A6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
+          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 嗜盐菌沿卤缘/源网季节性神经毒素</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
+          <t xml:space="preserve">    └─ 赤潮高峰（Red Tide Peak） ──→ Undecimber · 全年水质最差月份</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
-        </is>
-      </c>
+      <c r="A10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 4. 历史脉络</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 深井卤锈化、Undecimber 赤潮、边境崩解</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>井源计划（Wellspring Program） ──→ C.Y. 12–17 · 首批植入净水士兵，C.Y. 14 战场验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 醇民 Gen-0 量产</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>泄露与抗争（Exposure &amp; Resistance） ──→ C.Y. 20–23 · Don't Bottle Humanity! 戒酒教萌芽</t>
+          <t>方案 C terraform 遗产（Terraform Legacy） ──→ 可选 · 早期大气改造站催化剂泄漏入源网</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1035,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23 Undecimber · 机械燃料解放人性，醇民销毁</t>
+          <t>方案 D 矿冶尾液（Smelting Tailings） ──→ 可选 · 炼矿尾液经支渠回流源网</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1045,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>机械时代（Mechanical Era） ──→ C.Y. 30–37 · 铁瓶量产，酿造帮商业化</t>
+          <t>方案 E 化武残留（Chemical War Residue） ──→ 可选 · 殖民内战化学剂污染支渠</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1055,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37–42 · 二次发酵阈值，瓶醒/井醒</t>
+          <t>方案 F 尘暴带电粒子（Dust Storm Ions） ──→ 可选 · 辐射尘机制的民间误传版本</t>
         </is>
       </c>
     </row>
@@ -1139,185 +1065,22 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>当前荒原（Present Wasteland） ──→ C.Y. 42 Undecimber · 闭环运转 × 意识反抗，赤潮高峰</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 5. 存在体谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>井兵（Aqua-Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 隐性血脉（Carrier Line） ──→ C.Y. 15– · 井醒来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉发酵容器，F-Strain，已灭绝</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 野生游荡型（Wild Roaming） ──→ C.Y. 25– · 移动绿洲，赏金目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
+          <t>推荐组合 A+B（Recommended A+B） ──→ 已并入主干 · 见「污染官方主干」模块</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
-        </is>
-      </c>
+      <c r="A20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 觉醒个体（Awakened Individuals） ──→ C.Y. 37+ · 独立思想者</t>
+          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A21:C21"/>
@@ -1325,7 +1088,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A20:C20"/>
@@ -1344,7 +1106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1360,14 +1122,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 6. 势力格局</t>
+          <t>《瓶与源》· 3.1 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
+          <t>生态酵母（基础株）（Saccharomyces vitae） ──→ C.Y. 12– · 三重净化：化学毒+生物毒+辐射尘</t>
         </is>
       </c>
     </row>
@@ -1381,113 +1143,133 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
+          <t xml:space="preserve">    ├─ W-Strain（W-Strain (Military)） ──→ C.Y. 12–17 · 军用稳态型</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
+          <t xml:space="preserve">    │       └─ 源滤计划（Source-Filter Program） ──→ C.Y. 12–17 · 第一批植入者为锈水滤净士兵</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │           │</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
+          <t xml:space="preserve">    │           └─ 滤兵（Filter Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │               │</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
+          <t xml:space="preserve">    │               └─ 源醒（Source-Awake） ──→ C.Y. 37+ · W-Strain 残留 / 幸存滤兵</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 井兵单禁忌（Well-Soldier Taboo） ──→ C.Y. 42 · 圈内不接井兵委托</t>
+          <t xml:space="preserve">    ├─ R-Strain（R-Strain (Civilian)） ──→ C.Y. 12– · 民用救灾型</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
+          <t xml:space="preserve">    │       └─ 生态酿（Eco-Brew） ──→ C.Y. 12– · 2–4%，公开合法，社会认知「酵母=希望」</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    └─ F-Strain（F-Strain (Fuel)） ──→ C.Y. 15– · 燃料高产型</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
+          <t xml:space="preserve">        ├─ 活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 人体活体发酵容器</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
+          <t xml:space="preserve">        │   │</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        │       └─ 醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉容器，已基本灭绝</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
+          <t xml:space="preserve">        └─ 铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23–30 · 菌株移植至机械载体</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr"/>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                ├─ 铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识机械产力，圈养/野生</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
+          <t xml:space="preserve">                │   │</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            │       └─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，集体性觉醒</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
+          <t xml:space="preserve">                └─ 酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体，冲突中心</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1302,607 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 3.2 燃料闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 4. 历史脉络</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 卤缘渠网并网、源网全域锈化、边境崩解</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>源滤计划（Source-Filter Program） ──→ C.Y. 12–17 · 首批植入滤兵，C.Y. 14 战场验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 醇民 Gen-0 量产</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>泄露与抗争（Exposure &amp; Resistance） ──→ C.Y. 20–23 · Don't Bottle Humanity! 戒酒教萌芽</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23 Undecimber · 机械燃料解放人性，醇民销毁</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>机械时代（Mechanical Era） ──→ C.Y. 30–37 · 铁瓶量产，酿造帮商业化</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37–42 · 二次发酵阈值，瓶醒/源醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>当前荒原（Present Wasteland） ──→ C.Y. 42 Undecimber · 闭环运转 × 意识反抗，赤潮高峰</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 5. 存在体谱系</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>滤兵（Filter Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 隐性血脉（Carrier Line） ──→ C.Y. 15– · 源醒来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉发酵容器，F-Strain，已灭绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 野生游荡型（Wild Roaming） ──→ C.Y. 25– · 移动绿洲，赏金目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 源醒（Source-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 觉醒个体（Awakened Individuals） ──→ C.Y. 37+ · 独立思想者</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 6. 势力格局</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 否认源滤计划（Deny Source-Filter） ──→ C.Y. 42 · 档案抹除源滤计划历史</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 滤兵单禁忌（Filter-Soldier Taboo） ──→ C.Y. 42 · 圈内不接滤兵委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1536,7 +1918,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 7. 讽刺主题链</t>
+          <t>《瓶与源》· 7. 讽刺主题链</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1939,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 士兵净水（Soldiers Purify Water） ──→ C.Y. 12– · 最正当的起点</t>
+          <t xml:space="preserve">    └─ 士兵滤锈（Soldiers Filter Rustwater） ──→ C.Y. 12– · 最正当的起点</t>
         </is>
       </c>
     </row>
@@ -1668,7 +2050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1684,14 +2066,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 8. 叙事入口</t>
+          <t>《瓶与源》· 8. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>井兵末裔（Well-Soldier Scion） ──→ C.Y. 42 · W-Strain 残留，各方追逐</t>
+          <t>滤兵末裔（Filter-Soldier Scion） ──→ C.Y. 42 · W-Strain 残留，各方追逐</t>
         </is>
       </c>
     </row>
@@ -1701,7 +2083,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>刚觉醒酿民（Newly Awakened Brewfolk） ──→ C.Y. 42 · 意识到自己是净水者也是油箱</t>
+          <t>刚觉醒酿民（Newly Awakened Brewfolk） ──→ C.Y. 42 · 意识到自己是滤净者也是油箱</t>
         </is>
       </c>
     </row>
@@ -1711,7 +2093,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 赏金猎人，禁忌井兵委托</t>
+          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 赏金猎人，禁忌滤兵委托</t>
         </is>
       </c>
     </row>
@@ -1758,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C210"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1769,7 +2151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 全部树状图</t>
+          <t>《瓶与源》· 全部树状图</t>
         </is>
       </c>
     </row>
@@ -1811,7 +2193,7 @@
     <row r="8" outlineLevel="1" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、辐射尘、陆海沙海、稀薄大气</t>
+          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、卤缘渗出、冷凝塔、陆海沙海</t>
         </is>
       </c>
     </row>
@@ -1888,35 +2270,35 @@
     <row r="20" outlineLevel="1" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
+          <t xml:space="preserve">    ├─ 卤缘 Brine Rim ──→ 盆地边缘天然卤渗出带，锈水化学层根源</t>
         </is>
       </c>
     </row>
     <row r="21" outlineLevel="1" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
+          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
         </is>
       </c>
     </row>
     <row r="22" outlineLevel="1" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
+          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 卤缘渠网、砂岸驿道、铁瓶牧场、酵母泥倾倒</t>
         </is>
       </c>
     </row>
     <row r="23" outlineLevel="1" ht="16" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
+          <t xml:space="preserve">    ├─ 无源地带（Source-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
         </is>
       </c>
     </row>
     <row r="24" outlineLevel="1" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
+          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入卤缘与源网</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2340,7 @@
     <row r="31" outlineLevel="1" ht="16" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
+          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波源水变浊</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2375,7 @@
     <row r="36" outlineLevel="1" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
+          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照滤兵/铁瓶/酿民：自然进化不产酒</t>
         </is>
       </c>
     </row>
@@ -2007,14 +2389,14 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>▸ 2.1 污染主干</t>
+          <t>▸ 2.0 污染起因</t>
         </is>
       </c>
     </row>
     <row r="40" outlineLevel="1" ht="16" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
+          <t>锈水成因链（Rustwater Causation） ──→ v8 定稿 · 先天本底+殖民并网放大+十三月时间层</t>
         </is>
       </c>
     </row>
@@ -2028,59 +2410,63 @@
     <row r="42" outlineLevel="1" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
+          <t xml:space="preserve">    ├─ 先天层 · 星球本底（Primordial Layer） ──→ 卤缘天然有毒、嗜盐生态、弱磁辐射尘</t>
         </is>
       </c>
     </row>
     <row r="43" outlineLevel="1" ht="16" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
+          <t xml:space="preserve">    ├─ 殖民层 · 人为放大（Colonial Amplification） ──→ C.Y. 2–12 · 卤缘渠网+冷凝塔并网→源网全域锈化</t>
         </is>
       </c>
     </row>
     <row r="44" outlineLevel="1" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
+          <t xml:space="preserve">    │       ├─ 卤缘渠网（Brine Rim Canals） ──→ C.Y. 2–8 · 沿陆海边缘截取天然卤渗出</t>
         </is>
       </c>
     </row>
     <row r="45" outlineLevel="1" ht="16" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+          <t xml:space="preserve">    │       ├─ 冷凝塔并网（Condenser Grid Merge） ──→ C.Y. 5–10 · 卤缘卤流与冷凝水并入同一源网</t>
         </is>
       </c>
     </row>
     <row r="46" outlineLevel="1" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
+          <t xml:space="preserve">    │       ├─ 源流未分级（No Source Segregation） ──→ C.Y. 5–12 · 误判稀释可管理毒性</t>
         </is>
       </c>
     </row>
     <row r="47" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A47" s="7" t="inlineStr"/>
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 支渠回流污染（Branch Canal Reflux） ──→ C.Y. 8–12 · 矿冶尾液、酵母泥渗漏回流</t>
+        </is>
+      </c>
     </row>
     <row r="48" outlineLevel="1" ht="16" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 可作区域历史诱因，非主行星主干</t>
+          <t xml:space="preserve">    └─ 时间层 · 十三月（Undecimber Layer） ──→ 每年 · 卤潮涨幅+赤潮+辐射扬尘峰值</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>▸ 2.2 十三月</t>
+          <t>▸ 2.1 污染主干</t>
         </is>
       </c>
     </row>
     <row r="51" outlineLevel="1" ht="16" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
+          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
         </is>
       </c>
     </row>
@@ -2094,590 +2480,599 @@
     <row r="53" outlineLevel="1" ht="16" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
+          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Brine Rim） ──→ 全年 · 陆海卤缘天然渗出+渠网集中扩散</t>
         </is>
       </c>
     </row>
     <row r="54" outlineLevel="1" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
+          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌沿卤缘/源网，神经毒素</t>
         </is>
       </c>
     </row>
     <row r="55" outlineLevel="1" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
+          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 冷凝塔、蓄源池、沙海扬尘</t>
         </is>
       </c>
     </row>
     <row r="56" outlineLevel="1" ht="16" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
+          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤潮涨幅+赤潮+辐射扬尘</t>
         </is>
       </c>
     </row>
     <row r="57" outlineLevel="1" ht="16" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
+          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
         </is>
       </c>
     </row>
     <row r="58" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
-        </is>
-      </c>
+      <c r="A58" s="7" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="1" ht="16" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
+          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 支渠污染或区域历史诱因</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2.2 垦区源网</t>
         </is>
       </c>
     </row>
     <row r="62" outlineLevel="1" ht="16" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 酿造帮配额重置（Quota Reset） ──→ 年度生产配额于十三月 1 日重置</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>▸ 2.3 支线方案</t>
+          <t>垦区总水源网（Colonial Source Grid） ──→ C.Y. 2– · 非井模型 · 锈水在管网中流动分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 卤缘截取渠（Brine Rim Canals） ──→ C.Y. 2– · 沿陆海盆地边缘收集天然卤渗出</t>
         </is>
       </c>
     </row>
     <row r="65" outlineLevel="1" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>方案 A 深井毒卤（Deep-Brine Toxicity） ──→ 推荐主干 · 高氯酸盐/砷/铜卤层，深井采水全域污染</t>
+          <t xml:space="preserve">    ├─ 冷凝塔网（Condenser Towers） ──→ C.Y. 5– · 固陆砂岸高点集大气含水</t>
         </is>
       </c>
     </row>
     <row r="66" outlineLevel="1" ht="16" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 蓄源池链（Reservoir Chain） ──→ C.Y. 5– · 卤缘水与冷凝水混合调蓄</t>
         </is>
       </c>
     </row>
     <row r="67" outlineLevel="1" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ Undecimber 卤压峰值（Undecimber Brine Peak） ──→ 每年 · 地下卤层渗透率年度最高</t>
+          <t xml:space="preserve">    ├─ 支渠与牧场接口（Branch Canals） ──→ C.Y. 8– · 牧场矿冶酵母泥处置回流支渠</t>
         </is>
       </c>
     </row>
     <row r="68" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A68" s="7" t="inlineStr"/>
-    </row>
-    <row r="69" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 本土嗜盐菌季节性神经毒素</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 锈水 Rustwater ──→ 源网中一切流动储存分配的水体</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2.3 十三月</t>
         </is>
       </c>
     </row>
     <row r="71" outlineLevel="1" ht="16" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赤潮高峰（Red Tide Peak） ──→ Undecimber · 全年水质最差月份</t>
+          <t>十三月 Undecimber ──→ 每年 37 垦日 · 垦历第 13 月，地球账本不承认</t>
         </is>
       </c>
     </row>
     <row r="72" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A72" s="7" t="inlineStr"/>
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="73" outlineLevel="1" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>方案 C terraform 遗产（Terraform Legacy） ──→ 可选 · 早期大气改造站催化剂泄漏</t>
+          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转 397 垦日，余数并入第 13 月</t>
         </is>
       </c>
     </row>
     <row r="74" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A74" s="7" t="inlineStr"/>
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球母公司不计 KPI 与编制</t>
+        </is>
+      </c>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>方案 D 矿冶尾液（Smelting Tailings） ──→ 可选 · 机甲燃料炼矿尾液渗入含水层</t>
+          <t xml:space="preserve">    ├─ 法外之月（Lawless Month） ──→ 悬赏翻倍、合同作废、黑市开市</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A76" s="7" t="inlineStr"/>
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤潮涨幅+赤潮+沙海辐射扬尘</t>
+        </is>
+      </c>
     </row>
     <row r="77" outlineLevel="1" ht="16" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>方案 E 化武残留（Chemical War Residue） ──→ 可选 · 殖民内战化学剂污染流域</t>
+          <t xml:space="preserve">    ├─ C.Y. 12 生态酵母验证（Yeast Field Test） ──→ C.Y. 12 · 首次现场验证生态酿</t>
         </is>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A78" s="7" t="inlineStr"/>
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 12 源滤计划植入（Source-Filter Implant） ──→ C.Y. 12 · 首批滤兵植入</t>
+        </is>
+      </c>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>方案 F 尘暴带电粒子（Dust Storm Ions） ──→ 可选 · 双恒星尘暴金属微粒随雨入水</t>
+          <t xml:space="preserve">    ├─ C.Y. 23 铁瓶招标截止（Synth-Bottle Tender） ──→ C.Y. 23 · 铁瓶计划招标在十三月截止</t>
         </is>
       </c>
     </row>
     <row r="80" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A80" s="7" t="inlineStr"/>
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ C.Y. 42 觉醒临界（Awakening Threshold） ──→ C.Y. 42 · 二次发酵阈值，当前叙事时点</t>
+        </is>
+      </c>
     </row>
     <row r="81" outlineLevel="1" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>推荐组合 A+B（Recommended A+B） ──→ 已并入主干 · 见「污染官方主干」模块</t>
+          <t xml:space="preserve">    ├─ Saloon 不打烊（Saloon Always Open） ──→ 整月营业，情报与黑市高峰</t>
         </is>
       </c>
     </row>
     <row r="82" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>▸ 3.1 生态酵母</t>
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 酿造帮配额重置（Quota Reset） ──→ 年度生产配额于十三月 1 日重置</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2.4 支线方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>方案 A 陆海卤缘（Landsea Brine Rim） ──→ 推荐主干 · 盆地边缘天然卤渗出+卤缘渠网集中扩散</t>
         </is>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="16" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>生态酵母（基础株）（Saccharomyces vitae） ──→ C.Y. 12– · 三重净化：化学毒+生物毒+辐射尘</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="87" outlineLevel="1" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    └─ Undecimber 卤潮涨幅（Undecimber Brine Surge） ──→ 每年 · 陆海砂潮上涨，卤缘渗出率年度最高</t>
         </is>
       </c>
     </row>
     <row r="88" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ W-Strain（W-Strain (Military)） ──→ C.Y. 12–17 · 军用稳态型</t>
-        </is>
-      </c>
+      <c r="A88" s="7" t="inlineStr"/>
     </row>
     <row r="89" outlineLevel="1" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 嗜盐菌沿卤缘/源网季节性神经毒素</t>
         </is>
       </c>
     </row>
     <row r="90" outlineLevel="1" ht="16" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 井源计划（Wellspring Program） ──→ C.Y. 12–17 · 第一批植入者为净水超级士兵</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │           │</t>
+          <t xml:space="preserve">    └─ 赤潮高峰（Red Tide Peak） ──→ Undecimber · 全年水质最差月份</t>
         </is>
       </c>
     </row>
     <row r="92" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
-        </is>
-      </c>
+      <c r="A92" s="7" t="inlineStr"/>
     </row>
     <row r="93" outlineLevel="1" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │               │</t>
+          <t>方案 C terraform 遗产（Terraform Legacy） ──→ 可选 · 早期大气改造站催化剂泄漏入源网</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │               └─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留 / 幸存井兵</t>
-        </is>
-      </c>
+      <c r="A94" s="7" t="inlineStr"/>
     </row>
     <row r="95" outlineLevel="1" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ R-Strain（R-Strain (Civilian)） ──→ C.Y. 12– · 民用救灾型</t>
+          <t>方案 D 矿冶尾液（Smelting Tailings） ──→ 可选 · 炼矿尾液经支渠回流源网</t>
         </is>
       </c>
     </row>
     <row r="96" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │   │</t>
-        </is>
-      </c>
+      <c r="A96" s="7" t="inlineStr"/>
     </row>
     <row r="97" outlineLevel="1" ht="16" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 生态酿（Eco-Brew） ──→ C.Y. 12– · 2–4%，公开合法，社会认知「酵母=希望」</t>
+          <t>方案 E 化武残留（Chemical War Residue） ──→ 可选 · 殖民内战化学剂污染支渠</t>
         </is>
       </c>
     </row>
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ F-Strain（F-Strain (Fuel)） ──→ C.Y. 15– · 燃料高产型</t>
-        </is>
-      </c>
+      <c r="A98" s="7" t="inlineStr"/>
     </row>
     <row r="99" outlineLevel="1" ht="16" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 人体活体发酵容器</t>
+          <t>方案 F 尘暴带电粒子（Dust Storm Ions） ──→ 可选 · 辐射尘机制的民间误传版本</t>
         </is>
       </c>
     </row>
     <row r="100" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        │   │</t>
-        </is>
-      </c>
+      <c r="A100" s="7" t="inlineStr"/>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        │       └─ 醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉容器，已基本灭绝</t>
+          <t>推荐组合 A+B（Recommended A+B） ──→ 已并入主干 · 见「污染官方主干」模块</t>
         </is>
       </c>
     </row>
     <row r="102" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        └─ 铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23–30 · 菌株移植至机械载体</t>
-        </is>
-      </c>
+      <c r="A102" s="7" t="inlineStr"/>
     </row>
     <row r="103" outlineLevel="1" ht="16" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                ├─ 铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识机械产力，圈养/野生</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            │       └─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，集体性觉醒</t>
+          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>▸ 3.1 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                └─ 酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体，冲突中心</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>▸ 3.2 燃料闭环</t>
+          <t>生态酵母（基础株）（Saccharomyces vitae） ──→ C.Y. 12– · 三重净化：化学毒+生物毒+辐射尘</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ W-Strain（W-Strain (Military)） ──→ C.Y. 12–17 · 军用稳态型</t>
         </is>
       </c>
     </row>
     <row r="109" outlineLevel="1" ht="16" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="110" outlineLevel="1" ht="16" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 源滤计划（Source-Filter Program） ──→ C.Y. 12–17 · 第一批植入者为锈水滤净士兵</t>
         </is>
       </c>
     </row>
     <row r="111" outlineLevel="1" ht="16" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
+          <t xml:space="preserve">    │           │</t>
         </is>
       </c>
     </row>
     <row r="112" outlineLevel="1" ht="16" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+          <t xml:space="preserve">    │           └─ 滤兵（Filter Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
         </is>
       </c>
     </row>
     <row r="113" outlineLevel="1" ht="16" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
+          <t xml:space="preserve">    │               │</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+          <t xml:space="preserve">    │               └─ 源醒（Source-Awake） ──→ C.Y. 37+ · W-Strain 残留 / 幸存滤兵</t>
         </is>
       </c>
     </row>
     <row r="115" outlineLevel="1" ht="16" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
+          <t xml:space="preserve">    ├─ R-Strain（R-Strain (Civilian)） ──→ C.Y. 12– · 民用救灾型</t>
         </is>
       </c>
     </row>
     <row r="116" outlineLevel="1" ht="16" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="117" outlineLevel="1" ht="16" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
+          <t xml:space="preserve">    │       └─ 生态酿（Eco-Brew） ──→ C.Y. 12– · 2–4%，公开合法，社会认知「酵母=希望」</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>▸ 4. 历史脉络</t>
+          <t xml:space="preserve">    └─ F-Strain（F-Strain (Fuel)） ──→ C.Y. 15– · 燃料高产型</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ├─ 活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 人体活体发酵容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        │   │</t>
         </is>
       </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 深井卤锈化、Undecimber 赤潮、边境崩解</t>
+          <t xml:space="preserve">        │       └─ 醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉容器，已基本灭绝</t>
         </is>
       </c>
     </row>
     <row r="122" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A122" s="7" t="inlineStr"/>
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        └─ 铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23–30 · 菌株移植至机械载体</t>
+        </is>
+      </c>
     </row>
     <row r="123" outlineLevel="1" ht="16" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
+          <t xml:space="preserve">                ├─ 铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识机械产力，圈养/野生</t>
         </is>
       </c>
     </row>
     <row r="124" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A124" s="7" t="inlineStr"/>
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                │   │</t>
+        </is>
+      </c>
     </row>
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>井源计划（Wellspring Program） ──→ C.Y. 12–17 · 首批植入净水士兵，C.Y. 14 战场验证</t>
+          <t xml:space="preserve">            │       └─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，集体性觉醒</t>
         </is>
       </c>
     </row>
     <row r="126" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A126" s="7" t="inlineStr"/>
-    </row>
-    <row r="127" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 醇民 Gen-0 量产</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A128" s="7" t="inlineStr"/>
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                └─ 酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体，冲突中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>▸ 3.2 燃料闭环</t>
+        </is>
+      </c>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>泄露与抗争（Exposure &amp; Resistance） ──→ C.Y. 20–23 · Don't Bottle Humanity! 戒酒教萌芽</t>
+          <t>燃料永续闭环（Fuel Perpetual Loop） ──→ C.Y. 23– · 铁瓶计划遗产</t>
         </is>
       </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A130" s="7" t="inlineStr"/>
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23 Undecimber · 机械燃料解放人性，醇民销毁</t>
+          <t xml:space="preserve">    ├─ 输入层（Input Layer） ──→ C.Y. 23– · 锈水(锈卤+赤潮+辐射尘)、玉米浆、仙人掌糖浆</t>
         </is>
       </c>
     </row>
     <row r="132" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A132" s="7" t="inlineStr"/>
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 地理层（Landsea Layer） ──→ 陆海重砂、辐射尘富集、野生铁瓶漂移带</t>
+        </is>
+      </c>
     </row>
     <row r="133" outlineLevel="1" ht="16" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>机械时代（Mechanical Era） ──→ C.Y. 30–37 · 铁瓶量产，酿造帮商业化</t>
+          <t xml:space="preserve">    ├─ 运输层（Transport Layer） ──→ C.Y. 25– · 饲料搬运者 Dust Walker</t>
         </is>
       </c>
     </row>
     <row r="134" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A134" s="7" t="inlineStr"/>
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 生产层（Production Layer） ──→ C.Y. 23– · 铁瓶 Synth-Bottle</t>
+        </is>
+      </c>
     </row>
     <row r="135" outlineLevel="1" ht="16" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37–42 · 二次发酵阈值，瓶醒/井醒</t>
+          <t xml:space="preserve">    │       ├─ 一次发酵（Primary Fermentation） ──→ C.Y. 23– · 生态酿 2–4% 副产物</t>
         </is>
       </c>
     </row>
     <row r="136" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A136" s="7" t="inlineStr"/>
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 二次发酵（Secondary Fermentation） ──→ C.Y. 23– · 燃料乙醇 40%+ 主产物</t>
+        </is>
+      </c>
     </row>
     <row r="137" outlineLevel="1" ht="16" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>当前荒原（Present Wasteland） ──→ C.Y. 42 Undecimber · 闭环运转 × 意识反抗，赤潮高峰</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>▸ 5. 存在体谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>井兵（Aqua-Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
+          <t xml:space="preserve">    ├─ 输出层（Output Layer） ──→ C.Y. 23– · 机车、发电机、营地、Saloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 闭环裂缝（Loop Fracture） ──→ C.Y. 37+ · 二次发酵阈值，酿民觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>▸ 4. 历史脉络</t>
         </is>
       </c>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>锈水时代（Rustwater Era） ──→ C.Y. 5–12 · 卤缘渠网并网、源网全域锈化、边境崩解</t>
         </is>
       </c>
     </row>
     <row r="142" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
-        </is>
-      </c>
+      <c r="A142" s="7" t="inlineStr"/>
     </row>
     <row r="143" outlineLevel="1" ht="16" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
+          <t>生态酵母问世（Eco-Yeast Discovery） ──→ C.Y. 12 Undecimber · 赭锈带首次现场验证</t>
         </is>
       </c>
     </row>
     <row r="144" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 隐性血脉（Carrier Line） ──→ C.Y. 15– · 井醒来源</t>
-        </is>
-      </c>
+      <c r="A144" s="7" t="inlineStr"/>
     </row>
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A145" s="7" t="inlineStr"/>
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>源滤计划（Source-Filter Program） ──→ C.Y. 12–17 · 首批植入滤兵，C.Y. 14 战场验证</t>
+        </is>
+      </c>
     </row>
     <row r="146" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉发酵容器，F-Strain，已灭绝</t>
-        </is>
-      </c>
+      <c r="A146" s="7" t="inlineStr"/>
     </row>
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A147" s="7" t="inlineStr"/>
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 醇民 Gen-0 量产</t>
+        </is>
+      </c>
     </row>
     <row r="148" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
-        </is>
-      </c>
+      <c r="A148" s="7" t="inlineStr"/>
     </row>
     <row r="149" outlineLevel="1" ht="16" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>泄露与抗争（Exposure &amp; Resistance） ──→ C.Y. 20–23 · Don't Bottle Humanity! 戒酒教萌芽</t>
         </is>
       </c>
     </row>
     <row r="150" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
-        </is>
-      </c>
+      <c r="A150" s="7" t="inlineStr"/>
     </row>
     <row r="151" outlineLevel="1" ht="16" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 野生游荡型（Wild Roaming） ──→ C.Y. 25– · 移动绿洲，赏金目标</t>
+          <t>铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23 Undecimber · 机械燃料解放人性，醇民销毁</t>
         </is>
       </c>
     </row>
@@ -2687,91 +3082,79 @@
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
+          <t>机械时代（Mechanical Era） ──→ C.Y. 30–37 · 铁瓶量产，酿造帮商业化</t>
         </is>
       </c>
     </row>
     <row r="154" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A154" s="7" t="inlineStr"/>
     </row>
     <row r="155" outlineLevel="1" ht="16" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
+          <t>酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37–42 · 二次发酵阈值，瓶醒/源醒</t>
         </is>
       </c>
     </row>
     <row r="156" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
-        </is>
-      </c>
+      <c r="A156" s="7" t="inlineStr"/>
     </row>
     <row r="157" outlineLevel="1" ht="16" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 觉醒个体（Awakened Individuals） ──→ C.Y. 37+ · 独立思想者</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>▸ 6. 势力格局</t>
+          <t>当前荒原（Present Wasteland） ──→ C.Y. 42 Undecimber · 闭环运转 × 意识反抗，赤潮高峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5. 存在体谱系</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>滤兵（Filter Soldiers） ──→ C.Y. 12– · 第一代植入者，W-Strain，平行谱系</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
+          <t xml:space="preserve">    ├─ 归档者（The Archived） ──→ C.Y. 15– · 冷冻，记忆清洗</t>
         </is>
       </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 游荡老兵（The Dregs） ──→ C.Y. 15– · 荒漠传说，靠锈水存活</t>
         </is>
       </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
+          <t xml:space="preserve">    └─ 隐性血脉（Carrier Line） ──→ C.Y. 15– · 源醒来源</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
-        </is>
-      </c>
+      <c r="A165" s="7" t="inlineStr"/>
     </row>
     <row r="166" outlineLevel="1" ht="16" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
+          <t>醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉发酵容器，F-Strain，已灭绝</t>
         </is>
       </c>
     </row>
@@ -2781,7 +3164,7 @@
     <row r="168" outlineLevel="1" ht="16" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
+          <t>铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识 android，F-Strain 机械舱</t>
         </is>
       </c>
     </row>
@@ -2795,14 +3178,14 @@
     <row r="170" outlineLevel="1" ht="16" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
+          <t xml:space="preserve">    ├─ 圈养牧场型（Ranch-Penned） ──→ C.Y. 23– · 酿造帮控制</t>
         </is>
       </c>
     </row>
     <row r="171" outlineLevel="1" ht="16" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 井兵单禁忌（Well-Soldier Taboo） ──→ C.Y. 42 · 圈内不接井兵委托</t>
+          <t xml:space="preserve">    └─ 野生游荡型（Wild Roaming） ──→ C.Y. 25– · 移动绿洲，赏金目标</t>
         </is>
       </c>
     </row>
@@ -2812,7 +3195,7 @@
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
+          <t>酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体</t>
         </is>
       </c>
     </row>
@@ -2826,215 +3209,347 @@
     <row r="175" outlineLevel="1" ht="16" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
+          <t xml:space="preserve">    ├─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，数量大</t>
         </is>
       </c>
     </row>
     <row r="176" outlineLevel="1" ht="16" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
+          <t xml:space="preserve">    ├─ 源醒（Source-Awake） ──→ C.Y. 37+ · W-Strain 残留，数量少</t>
         </is>
       </c>
     </row>
     <row r="177" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A177" s="7" t="inlineStr"/>
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 主流酿民派（Mainstream Brewfolk） ──→ C.Y. 37+ · 系统内求生</t>
+        </is>
+      </c>
     </row>
     <row r="178" outlineLevel="1" ht="16" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
+          <t xml:space="preserve">    ├─ 流浪酒帮（Wander Brews） ──→ C.Y. 37+ · 脱离闭环</t>
         </is>
       </c>
     </row>
     <row r="179" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A179" s="7" t="inlineStr"/>
-    </row>
-    <row r="180" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A181" s="7" t="inlineStr"/>
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 觉醒个体（Awakened Individuals） ──→ C.Y. 37+ · 独立思想者</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>▸ 6. 势力格局</t>
+        </is>
+      </c>
     </row>
     <row r="182" outlineLevel="1" ht="16" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7. 讽刺主题链</t>
+          <t>酿造帮（Stillwright Cartel） ──→ C.Y. 42 · 铁瓶遗产继承人，专利垄断，最大受益者</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 二次发酵专利（Secondary Fermentation IP） ──→ C.Y. 42 · 燃料乙醇 40%+ 垄断</t>
         </is>
       </c>
     </row>
     <row r="185" outlineLevel="1" ht="16" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>旧时代生存执念（Survival Obsession） ──→ 无论如何都要活下去</t>
+          <t xml:space="preserve">    ├─ 商业化牧场（Commercial Ranches） ──→ C.Y. 42 · 圈养铁瓶，悬赏回收</t>
         </is>
       </c>
     </row>
     <row r="186" outlineLevel="1" ht="16" customHeight="1">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 酿民回收令（Brewfolk Reclamation Order） ──→ C.Y. 42 · 觉醒酿民定义为废品</t>
         </is>
       </c>
     </row>
     <row r="187" outlineLevel="1" ht="16" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 士兵净水（Soldiers Purify Water） ──→ C.Y. 12– · 最正当的起点</t>
+          <t xml:space="preserve">    └─ 否认源滤计划（Deny Source-Filter） ──→ C.Y. 42 · 档案抹除源滤计划历史</t>
         </is>
       </c>
     </row>
     <row r="188" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A188" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        │</t>
-        </is>
-      </c>
+      <c r="A188" s="7" t="inlineStr"/>
     </row>
     <row r="189" outlineLevel="1" ht="16" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ 人体验证（Human Vessel Proven） ──→ C.Y. 14– · 技术门槛跨越</t>
+          <t>赏金猎人（Bounty Hunters） ──→ C.Y. 42 · 回收野生铁瓶，猎捕叛逃酿民</t>
         </is>
       </c>
     </row>
     <row r="190" outlineLevel="1" ht="16" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">            │</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="191" outlineLevel="1" ht="16" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                └─ 贫民燃料化（Poor as Fuel） ──→ C.Y. 15– · 对象降级，话术不变</t>
+          <t xml:space="preserve">    ├─ 鏽釘（Rust Nail） ──→ C.Y. 42 · 职业猎人代表</t>
         </is>
       </c>
     </row>
     <row r="192" outlineLevel="1" ht="16" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    │</t>
+          <t xml:space="preserve">    └─ 滤兵单禁忌（Filter-Soldier Taboo） ──→ C.Y. 42 · 圈内不接滤兵委托</t>
         </is>
       </c>
     </row>
     <row r="193" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    └─ 人道抗争（Humanitarian Protest） ──→ C.Y. 20– · 别把人变成瓶子</t>
-        </is>
-      </c>
+      <c r="A193" s="7" t="inlineStr"/>
     </row>
     <row r="194" outlineLevel="1" ht="16" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        │</t>
+          <t>戒酒教（Temperance Riders） ──→ C.Y. 42 · 早期禁酒主义 + 反改造宗教</t>
         </is>
       </c>
     </row>
     <row r="195" outlineLevel="1" ht="16" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        └─ 铁瓶妥协（Synth-Bottle Compromise） ──→ C.Y. 23– · 机械燃料，解放人性</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="196" outlineLevel="1" ht="16" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            │</t>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 招募利用酿民，接口赎罪</t>
         </is>
       </c>
     </row>
     <row r="197" outlineLevel="1" ht="16" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            └─ 机械量产（Mass Production） ──→ C.Y. 30– · 人性换效率</t>
+          <t xml:space="preserve">    └─ 火焰纯净派（Flame Purity Faction） ──→ C.Y. 42 · 焚烧一切容器，铁瓶为伪善延续</t>
         </is>
       </c>
     </row>
     <row r="198" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A198" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                │</t>
-        </is>
-      </c>
+      <c r="A198" s="7" t="inlineStr"/>
     </row>
     <row r="199" outlineLevel="1" ht="16" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                └─ 酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37+ · 容器发问，闭环裂缝</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8. 叙事入口</t>
+          <t>流浪酒帮（Wander Brews） ──→ C.Y. 42 · 酿民反抗者，开源菌株，打破闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A200" s="7" t="inlineStr"/>
+    </row>
+    <row r="201" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>主流酿民派（Mainstream Brewfolk） ──→ C.Y. 42 · 系统内求生，仍辅助生产</t>
         </is>
       </c>
     </row>
     <row r="202" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A202" s="7" t="inlineStr">
-        <is>
-          <t>井兵末裔（Well-Soldier Scion） ──→ C.Y. 42 · W-Strain 残留，各方追逐</t>
-        </is>
-      </c>
+      <c r="A202" s="7" t="inlineStr"/>
     </row>
     <row r="203" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A203" s="7" t="inlineStr"/>
-    </row>
-    <row r="204" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A204" s="7" t="inlineStr">
-        <is>
-          <t>刚觉醒酿民（Newly Awakened Brewfolk） ──→ C.Y. 42 · 意识到自己是净水者也是油箱</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A205" s="7" t="inlineStr"/>
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>酒镇 / Saloon ──→ C.Y. 42 · 中立枢纽，情报，黑市，表面和平</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7. 讽刺主题链</t>
+        </is>
+      </c>
     </row>
     <row r="206" outlineLevel="1" ht="16" customHeight="1">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 赏金猎人，禁忌井兵委托</t>
+          <t>旧时代生存执念（Survival Obsession） ──→ 无论如何都要活下去</t>
         </is>
       </c>
     </row>
     <row r="207" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A207" s="7" t="inlineStr"/>
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="208" outlineLevel="1" ht="16" customHeight="1">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>Saloon 酒保（Saloon Bartender） ──→ C.Y. 42 · 半觉醒老旧铁瓶</t>
+          <t xml:space="preserve">    └─ 士兵滤锈（Soldiers Filter Rustwater） ──→ C.Y. 12– · 最正当的起点</t>
         </is>
       </c>
     </row>
     <row r="209" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A209" s="7" t="inlineStr"/>
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        │</t>
+        </is>
+      </c>
     </row>
     <row r="210" outlineLevel="1" ht="16" customHeight="1">
       <c r="A210" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        └─ 人体验证（Human Vessel Proven） ──→ C.Y. 14– · 技术门槛跨越</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            │</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                └─ 贫民燃料化（Poor as Fuel） ──→ C.Y. 15– · 对象降级，话术不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                    └─ 人道抗争（Humanitarian Protest） ──→ C.Y. 20– · 别把人变成瓶子</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                        │</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                        └─ 铁瓶妥协（Synth-Bottle Compromise） ──→ C.Y. 23– · 机械燃料，解放人性</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                            │</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                            └─ 机械量产（Mass Production） ──→ C.Y. 30– · 人性换效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                │</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                └─ 酿民觉醒（Brewfolk Awakening） ──→ C.Y. 37+ · 容器发问，闭环裂缝</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>滤兵末裔（Filter-Soldier Scion） ──→ C.Y. 42 · W-Strain 残留，各方追逐</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A224" s="7" t="inlineStr"/>
+    </row>
+    <row r="225" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>刚觉醒酿民（Newly Awakened Brewfolk） ──→ C.Y. 42 · 意识到自己是滤净者也是油箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A226" s="7" t="inlineStr"/>
+    </row>
+    <row r="227" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 赏金猎人，禁忌滤兵委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A228" s="7" t="inlineStr"/>
+    </row>
+    <row r="229" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>Saloon 酒保（Saloon Bartender） ──→ C.Y. 42 · 半觉醒老旧铁瓶</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A230" s="7" t="inlineStr"/>
+    </row>
+    <row r="231" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
           <t>酿造帮档案员（Cartel Archivist） ──→ C.Y. 42 · 发现抗议领袖在铁瓶合同上</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="197">
+  <mergeCells count="216">
     <mergeCell ref="A128:C128"/>
     <mergeCell ref="A193:C193"/>
     <mergeCell ref="A80:C80"/>
@@ -3063,22 +3578,27 @@
     <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A63:C63"/>
     <mergeCell ref="A155:C155"/>
     <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A220:C220"/>
     <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A229:C229"/>
     <mergeCell ref="A130:C130"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A83:C83"/>
     <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A138:C138"/>
     <mergeCell ref="A132:C132"/>
     <mergeCell ref="A110:C110"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A119:C119"/>
     <mergeCell ref="A196:C196"/>
     <mergeCell ref="A174:C174"/>
     <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
@@ -3088,15 +3608,18 @@
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A160:C160"/>
     <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="A224:C224"/>
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A96:C96"/>
     <mergeCell ref="A209:C209"/>
@@ -3110,6 +3633,7 @@
     <mergeCell ref="A202:C202"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A211:C211"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A186:C186"/>
@@ -3118,28 +3642,32 @@
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A201:C201"/>
     <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A226:C226"/>
     <mergeCell ref="A123:C123"/>
     <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A228:C228"/>
     <mergeCell ref="A146:C146"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A212:C212"/>
     <mergeCell ref="A99:C99"/>
     <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A84:C84"/>
     <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A214:C214"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A163:C163"/>
-    <mergeCell ref="A158:C158"/>
+    <mergeCell ref="A189:C189"/>
     <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A223:C223"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A213:C213"/>
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A188:C188"/>
@@ -3152,6 +3680,7 @@
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A215:C215"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A125:C125"/>
     <mergeCell ref="A190:C190"/>
@@ -3161,7 +3690,6 @@
     <mergeCell ref="A112:C112"/>
     <mergeCell ref="A199:C199"/>
     <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A127:C127"/>
     <mergeCell ref="A167:C167"/>
     <mergeCell ref="A176:C176"/>
     <mergeCell ref="A30:C30"/>
@@ -3172,6 +3700,8 @@
     <mergeCell ref="A98:C98"/>
     <mergeCell ref="A191:C191"/>
     <mergeCell ref="A169:C169"/>
+    <mergeCell ref="A225:C225"/>
+    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A178:C178"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A61:C61"/>
@@ -3179,17 +3709,18 @@
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A153:C153"/>
     <mergeCell ref="A162:C162"/>
+    <mergeCell ref="A227:C227"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A137:C137"/>
     <mergeCell ref="A177:C177"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A217:C217"/>
     <mergeCell ref="A164:C164"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A139:C139"/>
     <mergeCell ref="A154:C154"/>
     <mergeCell ref="A129:C129"/>
     <mergeCell ref="A195:C195"/>
@@ -3206,13 +3737,14 @@
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A231:C231"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A230:C230"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A143:C143"/>
@@ -3228,10 +3760,12 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A216:C216"/>
     <mergeCell ref="A168:C168"/>
     <mergeCell ref="A78:C78"/>
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A218:C218"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3253,7 +3787,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 1.1 赭锈带</t>
+          <t>《瓶与源》· 1.1 赭锈带</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3815,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、辐射尘、陆海沙海、稀薄大气</t>
+          <t xml:space="preserve">    ├─ 星球特征（Planet Traits） ──→ 双恒星、弱磁层、卤缘渗出、冷凝塔、陆海沙海</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3887,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 1.2 陆海沙海</t>
+          <t>《瓶与源》· 1.2 陆海沙海</t>
         </is>
       </c>
     </row>
@@ -3388,35 +3922,35 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
+          <t xml:space="preserve">    ├─ 卤缘 Brine Rim ──→ 盆地边缘天然卤渗出带，锈水化学层根源</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 深井卤层出露（Brine Outcrop） ──→ 多数卤层出露点位于陆海盆地边缘</t>
+          <t xml:space="preserve">    ├─ 辐射尘富集（Rad-Dust Enrichment） ──→ 辐射尘沉积于重砂层，翻涌时扬尘</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 砂岸驿道、铁瓶牧场、非法酵母泥倾倒</t>
+          <t xml:space="preserve">    ├─ 殖民利用（Colonial Use） ──→ C.Y. 0– · 卤缘渠网、砂岸驿道、铁瓶牧场、酵母泥倾倒</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 无井地带（Well-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
+          <t xml:space="preserve">    ├─ 无源地带（Source-less Deep） ──→ 赏金猎人对陆海深处的称呼</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入深井</t>
+          <t xml:space="preserve">    └─ 与锈水闭环（Rustwater Loop Link） ──→ 辐射尘+赤潮孢经砂层进入卤缘与源网</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3987,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 1.3 沙豚</t>
+          <t>《瓶与源》· 1.3 沙豚</t>
         </is>
       </c>
     </row>
@@ -3488,7 +4022,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波井水变浊</t>
+          <t xml:space="preserve">    ├─ 集群迁徙（Herd Migration） ──→ Undecimber · 翻砂释放辐射尘与赤潮孢：沙豚起波源水变浊</t>
         </is>
       </c>
     </row>
@@ -3523,7 +4057,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照井兵/铁瓶/酿民：自然进化不产酒</t>
+          <t xml:space="preserve">    ├─ 第四镜像（Fourth Mirror） ──→ 对照滤兵/铁瓶/酿民：自然进化不产酒</t>
         </is>
       </c>
     </row>
@@ -3569,14 +4103,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 2.1 污染主干</t>
+          <t>《瓶与源》· 2.0 污染起因</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
+          <t>锈水成因链（Rustwater Causation） ──→ v8 定稿 · 先天本底+殖民并网放大+十三月时间层</t>
         </is>
       </c>
     </row>
@@ -3590,45 +4124,49 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Deep-Brine） ──→ 全年 · 深井卤层：高氯酸盐/砷/铜</t>
+          <t xml:space="preserve">    ├─ 先天层 · 星球本底（Primordial Layer） ──→ 卤缘天然有毒、嗜盐生态、弱磁辐射尘</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌神经毒素，水呈铁锈红浊</t>
+          <t xml:space="preserve">    ├─ 殖民层 · 人为放大（Colonial Amplification） ──→ C.Y. 2–12 · 卤缘渠网+冷凝塔并网→源网全域锈化</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 轨道残骸+恒星风，沙海富集扬尘入水</t>
+          <t xml:space="preserve">    │       ├─ 卤缘渠网（Brine Rim Canals） ──→ C.Y. 2–8 · 沿陆海边缘截取天然卤渗出</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤压+赤潮+辐射扬尘全年最毒</t>
+          <t xml:space="preserve">    │       ├─ 冷凝塔并网（Condenser Grid Merge） ──→ C.Y. 5–10 · 卤缘卤流与冷凝水并入同一源网</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
+          <t xml:space="preserve">    │       ├─ 源流未分级（No Source Segregation） ──→ C.Y. 5–12 · 误判稀释可管理毒性</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 支渠回流污染（Branch Canal Reflux） ──→ C.Y. 8–12 · 矿冶尾液、酵母泥渗漏回流</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 可作区域历史诱因，非主行星主干</t>
+          <t xml:space="preserve">    └─ 时间层 · 十三月（Undecimber Layer） ──→ 每年 · 卤潮涨幅+赤潮+辐射扬尘峰值</t>
         </is>
       </c>
     </row>
@@ -3654,6 +4192,186 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 2.1 污染主干</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>官方主干 A+B+辐射尘（Canon A+B+Rad-Dust） ──→ 已定稿 · 三层污染叠加，生态酵母唯一规模化解</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 化学层 · 方案 A（Layer A Brine Rim） ──→ 全年 · 陆海卤缘天然渗出+渠网集中扩散</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 生物层 · 方案 B（Layer B Red Tide） ──→ Undecimber · 嗜盐菌沿卤缘/源网，神经毒素</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 放射层 · 辐射尘（Layer Rad-Dust） ──→ 尘暴/Undecimber · 冷凝塔、蓄源池、沙海扬尘</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ Undecimber 三重峰值（Triple Peak） ──→ Undecimber · 卤潮涨幅+赤潮+辐射扬尘</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 生态酵母三重净化（Eco-Yeast Triple Purify） ──→ C.Y. 12– · 钝化毒素+包裹核素→酵母泥需处置</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>支线方案 C–F（Optional C–F） ──→ 局部 · 支渠污染或区域历史诱因</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 2.2 垦区源网</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>垦区总水源网（Colonial Source Grid） ──→ C.Y. 2– · 非井模型 · 锈水在管网中流动分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 卤缘截取渠（Brine Rim Canals） ──→ C.Y. 2– · 沿陆海盆地边缘收集天然卤渗出</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 冷凝塔网（Condenser Towers） ──→ C.Y. 5– · 固陆砂岸高点集大气含水</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 蓄源池链（Reservoir Chain） ──→ C.Y. 5– · 卤缘水与冷凝水混合调蓄</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 支渠与牧场接口（Branch Canals） ──→ C.Y. 8– · 牧场矿冶酵母泥处置回流支渠</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 锈水 Rustwater ──→ 源网中一切流动储存分配的水体</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3665,7 +4383,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与井》· 2.2 十三月</t>
+          <t>《瓶与源》· 2.3 十三月</t>
         </is>
       </c>
     </row>
@@ -3707,7 +4425,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤压+赤潮+沙海辐射扬尘</t>
+          <t xml:space="preserve">    ├─ 水文峰值（Water Toxicity Peak） ──→ A+B+辐射尘 · 卤潮涨幅+赤潮+沙海辐射扬尘</t>
         </is>
       </c>
     </row>
@@ -3721,7 +4439,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ C.Y. 12 井源计划植入（Wellspring Implant） ──→ C.Y. 12 · 首批净水士兵植入</t>
+          <t xml:space="preserve">    ├─ C.Y. 12 源滤计划植入（Source-Filter Implant） ──→ C.Y. 12 · 首批滤兵植入</t>
         </is>
       </c>
     </row>
@@ -3771,352 +4489,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 2.3 支线方案</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>方案 A 深井毒卤（Deep-Brine Toxicity） ──→ 推荐主干 · 高氯酸盐/砷/铜卤层，深井采水全域污染</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ Undecimber 卤压峰值（Undecimber Brine Peak） ──→ 每年 · 地下卤层渗透率年度最高</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>方案 B 流浪赤潮（Wandering Red Tide） ──→ 推荐叠加 · 本土嗜盐菌季节性神经毒素</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 赤潮高峰（Red Tide Peak） ──→ Undecimber · 全年水质最差月份</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>方案 C terraform 遗产（Terraform Legacy） ──→ 可选 · 早期大气改造站催化剂泄漏</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>方案 D 矿冶尾液（Smelting Tailings） ──→ 可选 · 机甲燃料炼矿尾液渗入含水层</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>方案 E 化武残留（Chemical War Residue） ──→ 可选 · 殖民内战化学剂污染流域</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>方案 F 尘暴带电粒子（Dust Storm Ions） ──→ 可选 · 双恒星尘暴金属微粒随雨入水</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>推荐组合 A+B（Recommended A+B） ──→ 已并入主干 · 见「污染官方主干」模块</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>生态酵母（统一应答）（Eco-Yeast Response） ──→ C.Y. 12– · 所有方案共同技术解：锈水→生态酿</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与井》· 3.1 生态酵母</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>生态酵母（基础株）（Saccharomyces vitae） ──→ C.Y. 12– · 三重净化：化学毒+生物毒+辐射尘</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ W-Strain（W-Strain (Military)） ──→ C.Y. 12–17 · 军用稳态型</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 井源计划（Wellspring Program） ──→ C.Y. 12–17 · 第一批植入者为净水超级士兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │           │</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │           └─ 净水士兵（井兵）（Aqua-Soldiers） ──→ C.Y. 12–17 · 锈水→内源生态酿 2–4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │               │</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │               └─ 井醒（Well-Awake） ──→ C.Y. 37+ · W-Strain 残留 / 幸存井兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ R-Strain（R-Strain (Civilian)） ──→ C.Y. 12– · 民用救灾型</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 生态酿（Eco-Brew） ──→ C.Y. 12– · 2–4%，公开合法，社会认知「酵母=希望」</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ F-Strain（F-Strain (Fuel)） ──→ C.Y. 15– · 燃料高产型</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ├─ 活燃料计划（Living Fuel Program） ──→ C.Y. 15–23 · 人体活体发酵容器</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        │       └─ 醇民 Gen-0（Brewfolk Gen-0） ──→ C.Y. 15–23 · 血肉容器，已基本灭绝</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        └─ 铁瓶计划（Synth-Bottle Program） ──→ C.Y. 23–30 · 菌株移植至机械载体</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                ├─ 铁瓶 Gen-1（Synth-Bottle Gen-1） ──→ C.Y. 23– · 无意识机械产力，圈养/野生</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            │       └─ 瓶醒（Synth-Awake） ──→ C.Y. 37+ · F-Strain 网络共振，集体性觉醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                └─ 酿民 Gen-2（Brewfolk Gen-2） ──→ C.Y. 37+ · 觉醒意识体，冲突中心</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -12,7 +12,7 @@
     <sheet name="1. 赭锈带" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2. 锈水" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="3. 十三月" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4. 圣酵" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4. 生态酵母" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="5a. 第一批移民" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="5b. 第二批移民" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="5c. 第三批移民" sheetId="9" state="visible" r:id="rId9"/>
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v9</t>
+          <t>2026-07-16-v10</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>星球 → 锈水 → 圣酵 → 三批移民 → 存在体 → 威士忌 → 势力 → 入口</t>
+          <t>星球 → 锈水 → 生态酵母 → 三批移民 → 存在体 → 威士忌 → 势力 → 入口</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【圣酵】宗教传说命名 · 中和毒素 · 0.05%菌仍存活</t>
+          <t xml:space="preserve">    ├─ 生态酵母 ── 中和毒素 · 0.05%菌存活 · 宗教名未定</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  04. 4. 圣酵</t>
+          <t xml:space="preserve">  04. 4. 生态酵母</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取圣酵</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取酵母</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内圣酵 → 2–4%琥珀酒</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
     <row r="19" outlineLevel="1" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 圣酵无法根除 · 长期微量累积</t>
+          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
         </is>
       </c>
     </row>
@@ -1397,14 +1397,14 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>▸ 4. 圣酵</t>
+          <t>▸ 4. 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="32" outlineLevel="1" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>圣酵 Sacraleaven ──→ 生态酵母宗教名 · 赎泉传说命名</t>
+          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
         </is>
       </c>
     </row>
@@ -1418,28 +1418,28 @@
     <row r="34" outlineLevel="1" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 学名（Scientific Name） ──→ Saccharomyces vitae</t>
+          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
         </is>
       </c>
     </row>
     <row r="35" outlineLevel="1" ht="16" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和嗜盐菌神经毒素</t>
+          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
         </is>
       </c>
     </row>
     <row r="36" outlineLevel="1" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 产出（Output） ──→ 2–4% 琥珀发酵液 · 泰拉名威士忌</t>
+          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
         </is>
       </c>
     </row>
     <row r="37" outlineLevel="1" ht="16" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 无法根除0.05%嗜盐菌 · 离体活性衰亡</t>
+          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
     <row r="42" outlineLevel="1" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入圣酵</t>
+          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
         </is>
       </c>
     </row>
@@ -1481,14 +1481,14 @@
     <row r="44" outlineLevel="1" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带 · 圣酵为入场券</t>
+          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
         </is>
       </c>
     </row>
     <row r="45" outlineLevel="1" ht="16" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 圣酵植入首批移民胃囊</t>
+          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <row r="55" outlineLevel="1" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入圣酵的Android移民</t>
+          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
     <row r="67" outlineLevel="1" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内圣酵发酵锈水2–4%</t>
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
     <row r="85" outlineLevel="1" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取圣酵</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取酵母</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内圣酵 → 2–4%琥珀酒</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 圣酵无法根除 · 长期微量累积</t>
+          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
         </is>
       </c>
     </row>
@@ -2303,14 +2303,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 4. 圣酵</t>
+          <t>《瓶与源》· 4. 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>圣酵 Sacraleaven ──→ 生态酵母宗教名 · 赎泉传说命名</t>
+          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
         </is>
       </c>
     </row>
@@ -2324,28 +2324,28 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 学名（Scientific Name） ──→ Saccharomyces vitae</t>
+          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和嗜盐菌神经毒素</t>
+          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 产出（Output） ──→ 2–4% 琥珀发酵液 · 泰拉名威士忌</t>
+          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 无法根除0.05%嗜盐菌 · 离体活性衰亡</t>
+          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入圣酵</t>
+          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
         </is>
       </c>
     </row>
@@ -2416,14 +2416,14 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带 · 圣酵为入场券</t>
+          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 圣酵植入首批移民胃囊</t>
+          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入圣酵的Android移民</t>
+          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内圣酵发酵锈水2–4%</t>
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
         </is>
       </c>
     </row>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v10</t>
+          <t>2026-07-16-v11</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
     <row r="11" outlineLevel="1" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 联邦宣布放弃 · 荒原自治</t>
+          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
     <row r="27" outlineLevel="1" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球账本不承认</t>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 联邦宣布放弃 · 荒原自治</t>
+          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 地球账本不承认</t>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
         </is>
       </c>
     </row>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -9,17 +9,20 @@
   <sheets>
     <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1. 赭锈带" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2. 锈水" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3. 十三月" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4. 生态酵母" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5a. 第一批移民" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5b. 第二批移民" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="5c. 第三批移民" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="6. 存在体谱系" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="7. 威士忌经济" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="8. 荒原势力" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="9. 叙事入口" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="8. 荒原势力" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="9. 叙事入口" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="10. 锈钉" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="11. 锈钉开篇" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -492,7 +495,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v11</t>
+          <t>2026-07-16-v12</t>
         </is>
       </c>
     </row>
@@ -547,12 +550,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>核心</t>
+          <t>叙事边界</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>三批移民 · 漂沦者 · 酿民 · 威士忌 · 赏金猎人</t>
+          <t>仅赭锈带本地故事 · 无地球线 · 母星势力不作活跃线</t>
         </is>
       </c>
     </row>
@@ -564,7 +567,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>docs/worldbuilding-tree.md</t>
+          <t>docs/worldbuilding-tree.md · docs/story-rust-nail-opening.md</t>
         </is>
       </c>
     </row>
@@ -683,83 +686,105 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  01. 1. 赭锈带</t>
+          <t xml:space="preserve">  01. 0. 叙事边界</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  02. 2. 锈水</t>
+          <t xml:space="preserve">  02. 1. 赭锈带</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  03. 3. 十三月</t>
+          <t xml:space="preserve">  03. 2. 锈水</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  04. 4. 生态酵母</t>
+          <t xml:space="preserve">  04. 3. 十三月</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  05. 5a. 第一批移民</t>
+          <t xml:space="preserve">  05. 4. 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  06. 5b. 第二批移民</t>
+          <t xml:space="preserve">  06. 5a. 第一批移民</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  07. 5c. 第三批移民</t>
+          <t xml:space="preserve">  07. 5b. 第二批移民</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  08. 6. 存在体谱系</t>
+          <t xml:space="preserve">  08. 5c. 第三批移民</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  09. 7. 威士忌经济</t>
+          <t xml:space="preserve">  09. 6. 存在体谱系</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. 8. 荒原势力</t>
+          <t xml:space="preserve">  10. 7. 威士忌经济</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. 9. 叙事入口</t>
+          <t xml:space="preserve">  11. 8. 荒原势力</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14. 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="37">
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="B3:C3"/>
@@ -781,7 +806,9 @@
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A15:C15"/>
@@ -799,6 +826,90 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 5c. 第三批移民</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -922,7 +1033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1006,7 +1117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1114,7 +1225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1137,7 +1248,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>刚觉醒二代酿民（Newly Awakened Gen-2） ──→ C.Y. 42 · 第一次意识到自己是发酵器也是猎物</t>
+          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 主线视角 · 见 story-rust-nail-opening.md</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1258,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 赏金猎人 · 猎杀有意识酿民</t>
+          <t>刚觉醒二代酿民（Newly Awakened Gen-2） ──→ C.Y. 42 · 锈钉第一单目标 · 会说话的酿民</t>
         </is>
       </c>
     </row>
@@ -1185,6 +1296,182 @@
   <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 赏金猎人公会招牌手 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 出身（Origin） ──→ 第三批自愿协议囚犯后裔</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 专精（Specialty） ──→ 酿民悬赏 · 酵管提取 · 砂岸追迹</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 开篇信条（Opening Creed） ──→ Undecimber · 酿民是窖不是人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 开篇动机（Opening Drive） ──→ 第3垦日 · 离体酵母失活 · 家人需威士忌续命</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>第一幕：第十三月第一单（Act 1 Opening） ──→ C.Y. 42 · 锈钉视角开篇三章</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 章1 失活的酵（Ch1 Dead Yeast） ──→ Saloon · 悬赏刷新 · 会说话酿民 · 酬金三倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 章2 砂岸追迹（Ch2 Sand Trail） ──→ 驿道 · 铁瓶扬尘 · 罗盘偏移 · 听见求饶</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 章3 窖与口（Ch3 Vessel Speaks） ──→ 对峙 · 我不是酒瓶 · 回收哨响 · 拖走或放走</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 觉醒目标（Awakened Target） ──→ 二代酿民 · 脱队者 · 铁瓶帮外围单</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 伏笔（Foreshadow） ──→ 漂沦者磁场 · 自愿协议 · 酵母失活周期</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -1204,7 +1491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1229,14 +1516,14 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>▸ 1. 赭锈带</t>
+          <t>▸ 0. 叙事边界</t>
         </is>
       </c>
     </row>
     <row r="5" outlineLevel="1" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>赭锈带 Ochre Reach ──→ 发现后 · 宜居殖民星 · 唯水不宜移民</t>
+          <t>叙事边界（Narrative Scope） ──→ v11定稿 · 全部故事仅发生于赭锈带</t>
         </is>
       </c>
     </row>
@@ -1250,502 +1537,506 @@
     <row r="7" outlineLevel="1" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 垦锈带（民间旧称）（Folk Name） ──→ 垦殖年代口语旧称</t>
+          <t xml:space="preserve">    ├─ 无地球线（No Earth Plotline） ──→ 不写母星回流、通讯、复辟、地球视角</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 宜居条件（Habitable Traits） ──→ 双恒星、弱磁层、陆海沙海、可殖民大气</t>
+          <t xml:space="preserve">    ├─ 母星遗存（Homeworld Remnants） ──→ 仅移民史、档案、口头传说背景</t>
         </is>
       </c>
     </row>
     <row r="9" outlineLevel="1" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 移民唯一障碍（Immigration Block） ──→ 天然水源高氯酸盐/砷/铜 + 嗜盐菌</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>▸ 2. 锈水</t>
+          <t xml:space="preserve">    └─ 本地自治（Local Autonomy） ──→ C.Y. 42 · 势力、经济、伦理冲突均在荒原生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>▸ 1. 赭锈带</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>赭锈带 Ochre Reach ──→ 发现后 · 宜居殖民星 · 唯水不宜移民</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="14" outlineLevel="1" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>锈水 Rustwater ──→ 铁锈红浊 · 移民核心障碍</t>
+          <t xml:space="preserve">    ├─ 垦锈带（民间旧称）（Folk Name） ──→ 垦殖年代口语旧称</t>
         </is>
       </c>
     </row>
     <row r="15" outlineLevel="1" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 宜居条件（Habitable Traits） ──→ 双恒星、弱磁层、陆海沙海、可殖民大气</t>
         </is>
       </c>
     </row>
     <row r="16" outlineLevel="1" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 化学层（Chemical Layer） ──→ 高氯酸盐、砷、铜 · 水文本底</t>
+          <t xml:space="preserve">    ├─ 移民唯一障碍（Immigration Block） ──→ 天然水源高氯酸盐/砷/铜 + 嗜盐菌</t>
         </is>
       </c>
     </row>
     <row r="17" outlineLevel="1" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 嗜盐菌 Halophilic Bloom ──→ 被化学环境吸引定植</t>
+          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
         </is>
       </c>
     </row>
     <row r="18" outlineLevel="1" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 神经毒素（Neurotoxin） ──→ 代谢释放 · 铁锈红浊主因</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 辐射尘叠加（Rad-Dust Overlay） ──→ 弱磁层沉降 · 参与漂沦者畸变</t>
+          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2. 锈水</t>
         </is>
       </c>
     </row>
     <row r="21" outlineLevel="1" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ Undecimber 峰值（Undecimber Peak） ──→ 每年 · 嗜盐菌年度暴发最烈</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>▸ 3. 十三月</t>
+          <t>锈水 Rustwater ──→ 铁锈红浊 · 移民核心障碍</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 化学层（Chemical Layer） ──→ 高氯酸盐、砷、铜 · 水文本底</t>
         </is>
       </c>
     </row>
     <row r="24" outlineLevel="1" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>十三月 Undecimber ──→ 37 垦日/年 · 与恒星距离致公历无法整除</t>
+          <t xml:space="preserve">    ├─ 嗜盐菌 Halophilic Bloom ──→ 被化学环境吸引定植</t>
         </is>
       </c>
     </row>
     <row r="25" outlineLevel="1" ht="16" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       ├─ 神经毒素（Neurotoxin） ──→ 代谢释放 · 铁锈红浊主因</t>
         </is>
       </c>
     </row>
     <row r="26" outlineLevel="1" ht="16" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转约397垦日 · 余37日并入第13月</t>
+          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
         </is>
       </c>
     </row>
     <row r="27" outlineLevel="1" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
+          <t xml:space="preserve">    ├─ 辐射尘叠加（Rad-Dust Overlay） ──→ 弱磁层沉降 · 参与漂沦者畸变</t>
         </is>
       </c>
     </row>
     <row r="28" outlineLevel="1" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 菌暴发峰值（Bloom Peak） ──→ 每年 · 嗜盐菌神经毒素年度高峰</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 叙事惯例（Narrative Customs） ──→ C.Y. 42 · Saloon不打烊 · 铁瓶最密集</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>▸ 4. 生态酵母</t>
+          <t xml:space="preserve">    └─ Undecimber 峰值（Undecimber Peak） ──→ 每年 · 嗜盐菌年度暴发最烈</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>▸ 3. 十三月</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>十三月 Undecimber ──→ 37 垦日/年 · 与恒星距离致公历无法整除</t>
         </is>
       </c>
     </row>
     <row r="32" outlineLevel="1" ht="16" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="33" outlineLevel="1" ht="16" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转约397垦日 · 余37日并入第13月</t>
         </is>
       </c>
     </row>
     <row r="34" outlineLevel="1" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
         </is>
       </c>
     </row>
     <row r="35" outlineLevel="1" ht="16" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
+          <t xml:space="preserve">    ├─ 菌暴发峰值（Bloom Peak） ──→ 每年 · 嗜盐菌神经毒素年度高峰</t>
         </is>
       </c>
     </row>
     <row r="36" outlineLevel="1" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第一批植入（Wave-1 Implant） ──→ C.Y. 0–8 · 人类胃囊植入</t>
+          <t xml:space="preserve">    └─ 叙事惯例（Narrative Customs） ──→ C.Y. 42 · Saloon不打烊 · 铁瓶最密集</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>▸ 4. 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="39" outlineLevel="1" ht="16" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第二批植入（Wave-2 Implant） ──→ C.Y. 8–25 · Android一代酿民代谢舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>▸ 5a. 第一批移民</t>
+          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
         </is>
       </c>
     </row>
     <row r="42" outlineLevel="1" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
+          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
         </is>
       </c>
     </row>
     <row r="43" outlineLevel="1" ht="16" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
         </is>
       </c>
     </row>
     <row r="44" outlineLevel="1" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
+          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
         </is>
       </c>
     </row>
     <row r="45" outlineLevel="1" ht="16" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
+          <t xml:space="preserve">    ├─ 第一批植入（Wave-1 Implant） ──→ C.Y. 0–8 · 人类胃囊植入</t>
         </is>
       </c>
     </row>
     <row r="46" outlineLevel="1" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    └─ 第二批植入（Wave-2 Implant） ──→ C.Y. 8–25 · Android一代酿民代谢舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5a. 第一批移民</t>
         </is>
       </c>
     </row>
     <row r="49" outlineLevel="1" ht="16" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
+          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
         </is>
       </c>
     </row>
     <row r="50" outlineLevel="1" ht="16" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>▸ 5b. 第二批移民</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
         </is>
       </c>
     </row>
     <row r="53" outlineLevel="1" ht="16" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
+          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
         </is>
       </c>
     </row>
     <row r="54" outlineLevel="1" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
         </is>
       </c>
     </row>
     <row r="55" outlineLevel="1" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="56" outlineLevel="1" ht="16" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
+          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
         </is>
       </c>
     </row>
     <row r="57" outlineLevel="1" ht="16" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5b. 第二批移民</t>
         </is>
       </c>
     </row>
     <row r="60" outlineLevel="1" ht="16" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>▸ 5c. 第三批移民</t>
+          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
         </is>
       </c>
     </row>
     <row r="63" outlineLevel="1" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
+          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
         </is>
       </c>
     </row>
     <row r="64" outlineLevel="1" ht="16" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="65" outlineLevel="1" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 签署后放逐 · 抵消地球罪证</t>
+          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
         </is>
       </c>
     </row>
     <row r="66" outlineLevel="1" ht="16" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 星系放弃（System Abandoned） ──→ C.Y. 28 · 水资源无解 · 联邦撤离</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
         </is>
       </c>
     </row>
     <row r="67" outlineLevel="1" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>▸ 6. 存在体谱系</t>
+          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5c. 第三批移民</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="72" outlineLevel="1" ht="16" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
+          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
         </is>
       </c>
     </row>
     <row r="73" outlineLevel="1" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
         </is>
       </c>
     </row>
     <row r="74" outlineLevel="1" ht="16" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
         </is>
       </c>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
+          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A76" s="7" t="inlineStr"/>
-    </row>
-    <row r="77" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A78" s="7" t="inlineStr"/>
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>▸ 6. 存在体谱系</t>
+        </is>
+      </c>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
+          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
         </is>
       </c>
     </row>
     <row r="80" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A80" s="7" t="inlineStr"/>
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="81" outlineLevel="1" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 觉醒者逃亡</t>
+          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
         </is>
       </c>
     </row>
     <row r="82" outlineLevel="1" ht="16" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
         </is>
       </c>
     </row>
     <row r="83" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 觉醒个体（Awakened） ──→ C.Y. 30+ · 真正自主意识 · 猎人最高价值目标</t>
-        </is>
-      </c>
+      <c r="A83" s="7" t="inlineStr"/>
     </row>
     <row r="84" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A84" s="7" t="inlineStr"/>
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
+        </is>
+      </c>
     </row>
     <row r="85" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取酵母</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7. 威士忌经济</t>
-        </is>
-      </c>
+      <c r="A85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A87" s="7" t="inlineStr"/>
     </row>
     <row r="88" outlineLevel="1" ht="16" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 荒原生存硬通货</t>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 觉醒者逃亡</t>
         </is>
       </c>
     </row>
@@ -1759,90 +2050,87 @@
     <row r="90" outlineLevel="1" ht="16" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
+          <t xml:space="preserve">    └─ 觉醒个体（Awakened） ──→ C.Y. 30+ · 真正自主意识 · 猎人最高价值目标</t>
         </is>
       </c>
     </row>
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
-        </is>
-      </c>
+      <c r="A91" s="7" t="inlineStr"/>
     </row>
     <row r="92" outlineLevel="1" ht="16" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 提取（Extraction） ──→ 从酿民取酵批量发酵 · 活性会衰亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 消费（Consumption） ──→ Saloon · 御寒 · 麻醉 · 交易</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 觉醒酿民拒猎 · 暴力贸易</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8. 荒原势力</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取酵母</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7. 威士忌经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 荒原生存硬通货</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1" ht="16" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
+          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
         </is>
       </c>
     </row>
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A98" s="7" t="inlineStr"/>
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
+        </is>
+      </c>
     </row>
     <row r="99" outlineLevel="1" ht="16" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 猎杀二代酿民 · 代表鏽釘</t>
+          <t xml:space="preserve">    ├─ 提取（Extraction） ──→ 从酿民取酵批量发酵 · 活性会衰亡</t>
         </is>
       </c>
     </row>
     <row r="100" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A100" s="7" t="inlineStr"/>
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 消费（Consumption） ──→ Saloon · 御寒 · 麻醉 · 交易</t>
+        </is>
+      </c>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 觉醒酿民拒猎 · 暴力贸易</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8. 荒原势力</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
         </is>
       </c>
     </row>
@@ -1852,7 +2140,7 @@
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 觉醒二代互助 · 躲避猎人</t>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 猎杀二代酿民 · 代表鏽釘</t>
         </is>
       </c>
     </row>
@@ -1862,21 +2150,28 @@
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 威士忌 · 悬赏 · 情报</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
         </is>
       </c>
     </row>
     <row r="111" outlineLevel="1" ht="16" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>刚觉醒二代酿民（Newly Awakened Gen-2） ──→ C.Y. 42 · 第一次意识到自己是发酵器也是猎物</t>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
         </is>
       </c>
     </row>
@@ -1886,7 +2181,7 @@
     <row r="113" outlineLevel="1" ht="16" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 赏金猎人 · 猎杀有意识酿民</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 觉醒二代互助 · 躲避猎人</t>
         </is>
       </c>
     </row>
@@ -1896,36 +2191,190 @@
     <row r="115" outlineLevel="1" ht="16" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
+          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 威士忌 · 悬赏 · 情报</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 主线视角 · 见 story-rust-nail-opening.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>刚觉醒二代酿民（Newly Awakened Gen-2） ──→ C.Y. 42 · 锈钉第一单目标 · 会说话的酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
           <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
         </is>
       </c>
     </row>
-    <row r="116" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A116" s="7" t="inlineStr"/>
-    </row>
-    <row r="117" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
+    <row r="123" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>囚犯后裔酒保（Exile Bartender） ──→ C.Y. 42 · 倒卖威士忌 · 知自愿协议真相</t>
         </is>
       </c>
     </row>
-    <row r="118" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A118" s="7" t="inlineStr"/>
-    </row>
-    <row r="119" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
+    <row r="125" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 赏金猎人公会招牌手 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 出身（Origin） ──→ 第三批自愿协议囚犯后裔</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 专精（Specialty） ──→ 酿民悬赏 · 酵管提取 · 砂岸追迹</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 开篇信条（Opening Creed） ──→ Undecimber · 酿民是窖不是人</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 开篇动机（Opening Drive） ──→ 第3垦日 · 离体酵母失活 · 家人需威士忌续命</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>第一幕：第十三月第一单（Act 1 Opening） ──→ C.Y. 42 · 锈钉视角开篇三章</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 章1 失活的酵（Ch1 Dead Yeast） ──→ Saloon · 悬赏刷新 · 会说话酿民 · 酬金三倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 章2 砂岸追迹（Ch2 Sand Trail） ──→ 驿道 · 铁瓶扬尘 · 罗盘偏移 · 听见求饶</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 章3 窖与口（Ch3 Vessel Speaks） ──→ 对峙 · 我不是酒瓶 · 回收哨响 · 拖走或放走</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 觉醒目标（Awakened Target） ──→ 二代酿民 · 脱队者 · 铁瓶帮外围单</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 伏笔（Foreshadow） ──→ 漂沦者磁场 · 自愿协议 · 酵母失活周期</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="131">
+    <mergeCell ref="A128:C128"/>
     <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A136:C136"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A105:C105"/>
     <mergeCell ref="A26:C26"/>
@@ -1937,11 +2386,12 @@
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A130:C130"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A83:C83"/>
     <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A132:C132"/>
     <mergeCell ref="A110:C110"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
@@ -1949,28 +2399,35 @@
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A95:C95"/>
     <mergeCell ref="A104:C104"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A97:C97"/>
     <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A121:C121"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A82:C82"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A99:C99"/>
@@ -1981,46 +2438,60 @@
     <mergeCell ref="A101:C101"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A135:C135"/>
     <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A122:C122"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A125:C125"/>
     <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A98:C98"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A129:C129"/>
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A116:C116"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A131:C131"/>
     <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A140:C140"/>
     <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A143:C143"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -2040,7 +2511,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2051,14 +2522,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 1. 赭锈带</t>
+          <t>《瓶与源》· 0. 叙事边界</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>赭锈带 Ochre Reach ──→ 发现后 · 宜居殖民星 · 唯水不宜移民</t>
+          <t>叙事边界（Narrative Scope） ──→ v11定稿 · 全部故事仅发生于赭锈带</t>
         </is>
       </c>
     </row>
@@ -2072,45 +2543,29 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 垦锈带（民间旧称）（Folk Name） ──→ 垦殖年代口语旧称</t>
+          <t xml:space="preserve">    ├─ 无地球线（No Earth Plotline） ──→ 不写母星回流、通讯、复辟、地球视角</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 宜居条件（Habitable Traits） ──→ 双恒星、弱磁层、陆海沙海、可殖民大气</t>
+          <t xml:space="preserve">    ├─ 母星遗存（Homeworld Remnants） ──→ 仅移民史、档案、口头传说背景</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 移民唯一障碍（Immigration Block） ──→ 天然水源高氯酸盐/砷/铜 + 嗜盐菌</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
+          <t xml:space="preserve">    └─ 本地自治（Local Autonomy） ──→ C.Y. 42 · 势力、经济、伦理冲突均在荒原生成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A4:C4"/>
@@ -2124,7 +2579,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2135,14 +2590,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 2. 锈水</t>
+          <t>《瓶与源》· 1. 赭锈带</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈水 Rustwater ──→ 铁锈红浊 · 移民核心障碍</t>
+          <t>赭锈带 Ochre Reach ──→ 发现后 · 宜居殖民星 · 唯水不宜移民</t>
         </is>
       </c>
     </row>
@@ -2156,48 +2611,40 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 化学层（Chemical Layer） ──→ 高氯酸盐、砷、铜 · 水文本底</t>
+          <t xml:space="preserve">    ├─ 垦锈带（民间旧称）（Folk Name） ──→ 垦殖年代口语旧称</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 嗜盐菌 Halophilic Bloom ──→ 被化学环境吸引定植</t>
+          <t xml:space="preserve">    ├─ 宜居条件（Habitable Traits） ──→ 双恒星、弱磁层、陆海沙海、可殖民大气</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 神经毒素（Neurotoxin） ──→ 代谢释放 · 铁锈红浊主因</t>
+          <t xml:space="preserve">    ├─ 移民唯一障碍（Immigration Block） ──→ 天然水源高氯酸盐/砷/铜 + 嗜盐菌</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
+          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 辐射尘叠加（Rad-Dust Overlay） ──→ 弱磁层沉降 · 参与漂沦者畸变</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ Undecimber 峰值（Undecimber Peak） ──→ 每年 · 嗜盐菌年度暴发最烈</t>
+          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A10:C10"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -2216,82 +2663,6 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 3. 十三月</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>十三月 Undecimber ──→ 37 垦日/年 · 与恒星距离致公历无法整除</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转约397垦日 · 余37日并入第13月</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 菌暴发峰值（Bloom Peak） ──→ 每年 · 嗜盐菌神经毒素年度高峰</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 叙事惯例（Narrative Customs） ──→ C.Y. 42 · Saloon不打烊 · 铁瓶最密集</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2303,14 +2674,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 4. 生态酵母</t>
+          <t>《瓶与源》· 2. 锈水</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
+          <t>锈水 Rustwater ──→ 铁锈红浊 · 移民核心障碍</t>
         </is>
       </c>
     </row>
@@ -2324,42 +2695,42 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
+          <t xml:space="preserve">    ├─ 化学层（Chemical Layer） ──→ 高氯酸盐、砷、铜 · 水文本底</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
+          <t xml:space="preserve">    ├─ 嗜盐菌 Halophilic Bloom ──→ 被化学环境吸引定植</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
+          <t xml:space="preserve">    │       ├─ 神经毒素（Neurotoxin） ──→ 代谢释放 · 铁锈红浊主因</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
+          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一批植入（Wave-1 Implant） ──→ C.Y. 0–8 · 人类胃囊植入</t>
+          <t xml:space="preserve">    ├─ 辐射尘叠加（Rad-Dust Overlay） ──→ 弱磁层沉降 · 参与漂沦者畸变</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第二批植入（Wave-2 Implant） ──→ C.Y. 8–25 · Android一代酿民代谢舱</t>
+          <t xml:space="preserve">    └─ Undecimber 峰值（Undecimber Peak） ──→ 每年 · 嗜盐菌年度暴发最烈</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2750,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2395,14 +2766,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 5a. 第一批移民</t>
+          <t>《瓶与源》· 3. 十三月</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
+          <t>十三月 Undecimber ──→ 37 垦日/年 · 与恒星距离致公历无法整除</t>
         </is>
       </c>
     </row>
@@ -2416,56 +2787,124 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
+          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转约397垦日 · 余37日并入第13月</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
+          <t xml:space="preserve">    ├─ 菌暴发峰值（Bloom Peak） ──→ 每年 · 嗜盐菌神经毒素年度高峰</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
+          <t xml:space="preserve">    └─ 叙事惯例（Narrative Customs） ──→ C.Y. 42 · Saloon不打烊 · 铁瓶最密集</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 4. 生态酵母</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    ├─ 第一批植入（Wave-1 Implant） ──→ C.Y. 0–8 · 人类胃囊植入</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
+          <t xml:space="preserve">    └─ 第二批植入（Wave-2 Implant） ──→ C.Y. 8–25 · Android一代酿民代谢舱</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -2484,7 +2923,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2495,14 +2934,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 5b. 第二批移民</t>
+          <t>《瓶与源》· 5a. 第一批移民</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
+          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
         </is>
       </c>
     </row>
@@ -2516,48 +2955,56 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
+          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
+          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
+          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
+          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -2576,7 +3023,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2587,14 +3034,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 5c. 第三批移民</t>
+          <t>《瓶与源》· 5b. 第二批移民</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
+          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
         </is>
       </c>
     </row>
@@ -2608,40 +3055,48 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 签署后放逐 · 抵消地球罪证</t>
+          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 星系放弃（System Abandoned） ──→ C.Y. 28 · 水资源无解 · 联邦撤离</t>
+          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
+          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -19,10 +19,11 @@
     <sheet name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="8. 荒原势力" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="9. 叙事入口" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="10. 锈钉" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="11. 锈钉开篇" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="9. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="10. 锈钉" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="11. 锈钉开篇" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -495,7 +496,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16-v12</t>
+          <t>2026-07-20-v13</t>
         </is>
       </c>
     </row>
@@ -519,7 +520,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>星球 → 锈水 → 生态酵母 → 三批移民 → 存在体 → 威士忌 → 势力 → 入口</t>
+          <t>星球 → 锈水 → 三批移民 → 城带/荒原 → 威士忌分级 → 锈钉开篇</t>
         </is>
       </c>
     </row>
@@ -595,7 +596,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【星球】赭锈带 · 宜居 · 唯水不宜</t>
+          <t xml:space="preserve">    ├─ 【星球】赭锈带 · 宜居 · 唯水不宜 · 城带/荒原双态</t>
         </is>
       </c>
     </row>
@@ -644,7 +645,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶车队 · 二代觉醒迁出</t>
+          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶车队 · 二代分城带/精品/荒原</t>
         </is>
       </c>
     </row>
@@ -658,7 +659,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 星系放弃 · 威士忌 · 赏金猎人</t>
+          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 星系放弃 · 威士忌分级 · 荒原赏金猎人</t>
         </is>
       </c>
     </row>
@@ -672,125 +673,164 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 【当前】荒原威士忌经济 × 酿民逃亡 × 漂沦者游荡</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+          <t xml:space="preserve">    ├─ 【城带】二代酿民共存 · 体内威士忌换币 · 琥珀交易所</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 【荒原】猎杀未登记酿民 · 精品酿民高悬赏 · 锈钉行尸走肉循环</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 【开篇】精品酿民窖七 · 城带价码 · 扳机上第一次停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>模块索引</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  01. 0. 叙事边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  02. 1. 赭锈带</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  03. 2. 锈水</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  04. 3. 十三月</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  05. 4. 生态酵母</t>
+          <t xml:space="preserve">  01. 0. 叙事边界</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  06. 5a. 第一批移民</t>
+          <t xml:space="preserve">  02. 1. 赭锈带</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  07. 5b. 第二批移民</t>
+          <t xml:space="preserve">  03. 2. 锈水</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  08. 5c. 第三批移民</t>
+          <t xml:space="preserve">  04. 3. 十三月</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  09. 6. 存在体谱系</t>
+          <t xml:space="preserve">  05. 4. 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. 7. 威士忌经济</t>
+          <t xml:space="preserve">  06. 5a. 第一批移民</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. 8. 荒原势力</t>
+          <t xml:space="preserve">  07. 5b. 第二批移民</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12. 9. 叙事入口</t>
+          <t xml:space="preserve">  08. 5c. 第三批移民</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. 10. 锈钉</t>
+          <t xml:space="preserve">  09. 6. 存在体谱系</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14. 11. 锈钉开篇</t>
+          <t xml:space="preserve">  10. 7. 威士忌经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11. 7b. 城带与荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  12. 8. 势力格局</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  13. 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  14. 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  15. 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="42">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
@@ -802,12 +842,12 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="B9:C9"/>
@@ -817,6 +857,7 @@
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A16:C16"/>
@@ -914,7 +955,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -983,7 +1024,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 觉醒者逃亡</t>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
         </is>
       </c>
     </row>
@@ -997,31 +1038,55 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 觉醒个体（Awakened） ──→ C.Y. 30+ · 真正自主意识 · 猎人最高价值目标</t>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取酵母</t>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A12:C12"/>
@@ -1038,7 +1103,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1056,7 +1121,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 荒原生存硬通货</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
         </is>
       </c>
     </row>
@@ -1084,136 +1149,60 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 提取（Extraction） ──→ 从酿民取酵批量发酵 · 活性会衰亡</t>
+          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 消费（Consumption） ──→ Saloon · 御寒 · 麻醉 · 交易</t>
+          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 觉醒酿民拒猎 · 暴力贸易</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 8. 荒原势力</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 猎杀二代酿民 · 代表鏽釘</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 觉醒二代互助 · 躲避猎人</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 威士忌 · 悬赏 · 情报</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
@@ -1225,7 +1214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1241,54 +1230,70 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 9. 叙事入口</t>
+          <t>《瓶与源》· 7b. 城带与荒原</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 主线视角 · 见 story-rust-nail-opening.md</t>
+          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>刚觉醒二代酿民（Newly Awakened Gen-2） ──→ C.Y. 42 · 锈钉第一单目标 · 会说话的酿民</t>
+          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
+          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>囚犯后裔酒保（Exile Bartender） ──→ C.Y. 42 · 倒卖威士忌 · 知自愿协议真相</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1314,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1325,69 +1330,205 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 10. 锈钉</t>
+          <t>《瓶与源》· 8. 势力格局</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 赏金猎人公会招牌手 · 主线视角</t>
+          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 出身（Origin） ──→ 第三批自愿协议囚犯后裔</t>
+          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 专精（Specialty） ──→ 酿民悬赏 · 酵管提取 · 砂岸追迹</t>
-        </is>
-      </c>
+      <c r="A6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 开篇信条（Opening Creed） ──→ Undecimber · 酿民是窖不是人</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 开篇动机（Opening Drive） ──→ 第3垦日 · 离体酵母失活 · 家人需威士忌续命</t>
+          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="19">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -1406,6 +1547,114 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1424,7 +1673,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>第一幕：第十三月第一单（Act 1 Opening） ──→ C.Y. 42 · 锈钉视角开篇三章</t>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
         </is>
       </c>
     </row>
@@ -1438,35 +1687,35 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 章1 失活的酵（Ch1 Dead Yeast） ──→ Saloon · 悬赏刷新 · 会说话酿民 · 酬金三倍</t>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 章2 砂岸追迹（Ch2 Sand Trail） ──→ 驿道 · 铁瓶扬尘 · 罗盘偏移 · 听见求饶</t>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 章3 窖与口（Ch3 Vessel Speaks） ──→ 对峙 · 我不是酒瓶 · 回收哨响 · 拖走或放走</t>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 觉醒目标（Awakened Target） ──→ 二代酿民 · 脱队者 · 铁瓶帮外围单</t>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 伏笔（Foreshadow） ──→ 漂沦者磁场 · 自愿协议 · 酵母失活周期</t>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1600,778 +1849,962 @@
     <row r="17" outlineLevel="1" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
+          <t xml:space="preserve">    ├─ 地理双态（Metro vs Wastes） ──→ C.Y. 42 · 城带共存 · 荒原猎杀 · 非全域对立</t>
         </is>
       </c>
     </row>
     <row r="18" outlineLevel="1" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>▸ 2. 锈水</t>
+          <t xml:space="preserve">    │       ├─ 城带 Metro Rim ──→ C.Y. 42 · 大城市 · 二代酿民登记共存 · 体内威士忌换币</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
         </is>
       </c>
     </row>
     <row r="21" outlineLevel="1" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>锈水 Rustwater ──→ 铁锈红浊 · 移民核心障碍</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 化学层（Chemical Layer） ──→ 高氯酸盐、砷、铜 · 水文本底</t>
+          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 本地自治</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>▸ 2. 锈水</t>
         </is>
       </c>
     </row>
     <row r="24" outlineLevel="1" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 嗜盐菌 Halophilic Bloom ──→ 被化学环境吸引定植</t>
+          <t>锈水 Rustwater ──→ 铁锈红浊 · 移民核心障碍</t>
         </is>
       </c>
     </row>
     <row r="25" outlineLevel="1" ht="16" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 神经毒素（Neurotoxin） ──→ 代谢释放 · 铁锈红浊主因</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="26" outlineLevel="1" ht="16" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
+          <t xml:space="preserve">    ├─ 化学层（Chemical Layer） ──→ 高氯酸盐、砷、铜 · 水文本底</t>
         </is>
       </c>
     </row>
     <row r="27" outlineLevel="1" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 辐射尘叠加（Rad-Dust Overlay） ──→ 弱磁层沉降 · 参与漂沦者畸变</t>
+          <t xml:space="preserve">    ├─ 嗜盐菌 Halophilic Bloom ──→ 被化学环境吸引定植</t>
         </is>
       </c>
     </row>
     <row r="28" outlineLevel="1" ht="16" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ Undecimber 峰值（Undecimber Peak） ──→ 每年 · 嗜盐菌年度暴发最烈</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>▸ 3. 十三月</t>
+          <t xml:space="preserve">    │       ├─ 神经毒素（Neurotoxin） ──→ 代谢释放 · 铁锈红浊主因</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 0.05% 存活率（0.05% Survival） ──→ 泄露 · 生态酵母无法根除 · 长期微量累积</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 辐射尘叠加（Rad-Dust Overlay） ──→ 弱磁层沉降 · 参与漂沦者畸变</t>
         </is>
       </c>
     </row>
     <row r="31" outlineLevel="1" ht="16" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>十三月 Undecimber ──→ 37 垦日/年 · 与恒星距离致公历无法整除</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转约397垦日 · 余37日并入第13月</t>
+          <t xml:space="preserve">    └─ Undecimber 峰值（Undecimber Peak） ──→ 每年 · 嗜盐菌年度暴发最烈</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>▸ 3. 十三月</t>
         </is>
       </c>
     </row>
     <row r="34" outlineLevel="1" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
+          <t>十三月 Undecimber ──→ 37 垦日/年 · 与恒星距离致公历无法整除</t>
         </is>
       </c>
     </row>
     <row r="35" outlineLevel="1" ht="16" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 菌暴发峰值（Bloom Peak） ──→ 每年 · 嗜盐菌神经毒素年度高峰</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="36" outlineLevel="1" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 叙事惯例（Narrative Customs） ──→ C.Y. 42 · Saloon不打烊 · 铁瓶最密集</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>▸ 4. 生态酵母</t>
+          <t xml:space="preserve">    ├─ 天文成因（Orbital Cause） ──→ 公转约397垦日 · 余37日并入第13月</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 账外之月（Off-Ledger Month） ──→ 旧历正统不承认 · 母星撤离后仍沿用</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 菌暴发峰值（Bloom Peak） ──→ 每年 · 嗜盐菌神经毒素年度高峰</t>
         </is>
       </c>
     </row>
     <row r="39" outlineLevel="1" ht="16" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
+          <t xml:space="preserve">    └─ 叙事惯例（Narrative Customs） ──→ C.Y. 42 · Saloon不打烊 · 铁瓶最密集</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>▸ 4. 生态酵母</t>
         </is>
       </c>
     </row>
     <row r="42" outlineLevel="1" ht="16" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
+          <t>生态酵母（Saccharomyces vitae） ──→ 中和嗜盐菌神经毒素 · 宗教名未定稿</t>
         </is>
       </c>
     </row>
     <row r="43" outlineLevel="1" ht="16" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="44" outlineLevel="1" ht="16" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
+          <t xml:space="preserve">    ├─ 发现背景（Discovery Context） ──→ C.Y. 0– · 第一批国家争夺赭锈带资源时发现</t>
         </is>
       </c>
     </row>
     <row r="45" outlineLevel="1" ht="16" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一批植入（Wave-1 Implant） ──→ C.Y. 0–8 · 人类胃囊植入</t>
+          <t xml:space="preserve">    ├─ 宗教命名（Religious Name） ──→ 待定 · 宗教传说曾为之命名 · 具体名称未定</t>
         </is>
       </c>
     </row>
     <row r="46" outlineLevel="1" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第二批植入（Wave-2 Implant） ──→ C.Y. 8–25 · Android一代酿民代谢舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>▸ 5a. 第一批移民</t>
+          <t xml:space="preserve">    ├─ 能力（Capability） ──→ 发酵锈水 · 中和神经毒素 · 2–4%发酵液</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 局限（Limitation） ──→ 嗜盐菌0.05%存活 · 离体酵母活性衰亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一批植入（Wave-1 Implant） ──→ C.Y. 0–8 · 人类胃囊植入</t>
         </is>
       </c>
     </row>
     <row r="49" outlineLevel="1" ht="16" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
+          <t xml:space="preserve">    └─ 第二批植入（Wave-2 Implant） ──→ C.Y. 8–25 · Android一代酿民代谢舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5a. 第一批移民</t>
         </is>
       </c>
     </row>
     <row r="52" outlineLevel="1" ht="16" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
+          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
         </is>
       </c>
     </row>
     <row r="53" outlineLevel="1" ht="16" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="54" outlineLevel="1" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
+          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
         </is>
       </c>
     </row>
     <row r="55" outlineLevel="1" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
         </is>
       </c>
     </row>
     <row r="56" outlineLevel="1" ht="16" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
+          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
         </is>
       </c>
     </row>
     <row r="57" outlineLevel="1" ht="16" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>▸ 5b. 第二批移民</t>
+          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
         </is>
       </c>
     </row>
     <row r="60" outlineLevel="1" ht="16" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
+          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5b. 第二批移民</t>
         </is>
       </c>
     </row>
     <row r="63" outlineLevel="1" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
+          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
         </is>
       </c>
     </row>
     <row r="64" outlineLevel="1" ht="16" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="65" outlineLevel="1" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
+          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
         </is>
       </c>
     </row>
     <row r="66" outlineLevel="1" ht="16" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
         </is>
       </c>
     </row>
     <row r="67" outlineLevel="1" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>▸ 5c. 第三批移民</t>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
         </is>
       </c>
     </row>
     <row r="70" outlineLevel="1" ht="16" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
+          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>▸ 5c. 第三批移民</t>
         </is>
       </c>
     </row>
     <row r="73" outlineLevel="1" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
+          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
         </is>
       </c>
     </row>
     <row r="74" outlineLevel="1" ht="16" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
+          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>▸ 6. 存在体谱系</t>
+          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
         </is>
       </c>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
+          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>▸ 6. 存在体谱系</t>
         </is>
       </c>
     </row>
     <row r="82" outlineLevel="1" ht="16" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
+          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
         </is>
       </c>
     </row>
     <row r="83" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A83" s="7" t="inlineStr"/>
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="84" outlineLevel="1" ht="16" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
           <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
         </is>
       </c>
     </row>
-    <row r="85" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A87" s="7" t="inlineStr"/>
-    </row>
     <row r="88" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 觉醒者逃亡</t>
-        </is>
-      </c>
+      <c r="A88" s="7" t="inlineStr"/>
     </row>
     <row r="89" outlineLevel="1" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
         </is>
       </c>
     </row>
     <row r="90" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 觉醒个体（Awakened） ──→ C.Y. 30+ · 真正自主意识 · 猎人最高价值目标</t>
-        </is>
-      </c>
+      <c r="A90" s="7" t="inlineStr"/>
     </row>
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A91" s="7" t="inlineStr"/>
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+        </is>
+      </c>
     </row>
     <row r="92" outlineLevel="1" ht="16" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 囚犯后裔 · 猎杀酿民取酵母</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7. 威士忌经济</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
         </is>
       </c>
     </row>
     <row r="95" outlineLevel="1" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 荒原生存硬通货</t>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
         </is>
       </c>
     </row>
     <row r="96" outlineLevel="1" ht="16" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
-        </is>
-      </c>
+      <c r="A97" s="7" t="inlineStr"/>
     </row>
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 提取（Extraction） ──→ 从酿民取酵批量发酵 · 活性会衰亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 消费（Consumption） ──→ Saloon · 御寒 · 麻醉 · 交易</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7. 威士忌经济</t>
         </is>
       </c>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 觉醒酿民拒猎 · 暴力贸易</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8. 荒原势力</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
         </is>
       </c>
     </row>
     <row r="105" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A105" s="7" t="inlineStr"/>
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
+        </is>
+      </c>
     </row>
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 猎杀二代酿民 · 代表鏽釘</t>
+          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
         </is>
       </c>
     </row>
     <row r="107" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A107" s="7" t="inlineStr"/>
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
+        </is>
+      </c>
     </row>
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
         </is>
       </c>
     </row>
     <row r="109" outlineLevel="1" ht="16" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
         </is>
       </c>
     </row>
     <row r="110" outlineLevel="1" ht="16" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
         </is>
       </c>
     </row>
     <row r="111" outlineLevel="1" ht="16" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A112" s="7" t="inlineStr"/>
-    </row>
-    <row r="113" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 觉醒二代互助 · 躲避猎人</t>
+          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7b. 城带与荒原</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A114" s="7" t="inlineStr"/>
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
+        </is>
+      </c>
     </row>
     <row r="115" outlineLevel="1" ht="16" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 威士忌 · 悬赏 · 情报</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>鏽釘（Rust Nail） ──→ C.Y. 42 · 主线视角 · 见 story-rust-nail-opening.md</t>
+          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
         </is>
       </c>
     </row>
     <row r="119" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A119" s="7" t="inlineStr"/>
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+        </is>
+      </c>
     </row>
     <row r="120" outlineLevel="1" ht="16" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>刚觉醒二代酿民（Newly Awakened Gen-2） ──→ C.Y. 42 · 锈钉第一单目标 · 会说话的酿民</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A121" s="7" t="inlineStr"/>
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
+        </is>
+      </c>
     </row>
     <row r="122" outlineLevel="1" ht="16" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A123" s="7" t="inlineStr"/>
-    </row>
-    <row r="124" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>囚犯后裔酒保（Exile Bartender） ──→ C.Y. 42 · 倒卖威士忌 · 知自愿协议真相</t>
+          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8. 势力格局</t>
         </is>
       </c>
     </row>
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A125" s="7" t="inlineStr"/>
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
+        </is>
+      </c>
     </row>
     <row r="126" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
-        </is>
-      </c>
+      <c r="A126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A128" s="7" t="inlineStr"/>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 赏金猎人公会招牌手 · 主线视角</t>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
         </is>
       </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A130" s="7" t="inlineStr"/>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 出身（Origin） ──→ 第三批自愿协议囚犯后裔</t>
+          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
         </is>
       </c>
     </row>
     <row r="132" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 专精（Specialty） ──→ 酿民悬赏 · 酵管提取 · 砂岸追迹</t>
-        </is>
-      </c>
+      <c r="A132" s="7" t="inlineStr"/>
     </row>
     <row r="133" outlineLevel="1" ht="16" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
         </is>
       </c>
     </row>
     <row r="134" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 开篇信条（Opening Creed） ──→ Undecimber · 酿民是窖不是人</t>
-        </is>
-      </c>
+      <c r="A134" s="7" t="inlineStr"/>
     </row>
     <row r="135" outlineLevel="1" ht="16" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 开篇动机（Opening Drive） ──→ 第3垦日 · 离体酵母失活 · 家人需威士忌续命</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
         </is>
       </c>
     </row>
     <row r="136" outlineLevel="1" ht="16" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
         </is>
       </c>
     </row>
     <row r="139" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>第一幕：第十三月第一单（Act 1 Opening） ──→ C.Y. 42 · 锈钉视角开篇三章</t>
-        </is>
-      </c>
+      <c r="A139" s="7" t="inlineStr"/>
     </row>
     <row r="140" outlineLevel="1" ht="16" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
         </is>
       </c>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 章1 失活的酵（Ch1 Dead Yeast） ──→ Saloon · 悬赏刷新 · 会说话酿民 · 酬金三倍</t>
-        </is>
-      </c>
+      <c r="A141" s="7" t="inlineStr"/>
     </row>
     <row r="142" outlineLevel="1" ht="16" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 章2 砂岸追迹（Ch2 Sand Trail） ──→ 驿道 · 铁瓶扬尘 · 罗盘偏移 · 听见求饶</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 章3 窖与口（Ch3 Vessel Speaks） ──→ 对峙 · 我不是酒瓶 · 回收哨响 · 拖走或放走</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 觉醒目标（Awakened Target） ──→ 二代酿民 · 脱队者 · 铁瓶帮外围单</t>
+          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 伏笔（Foreshadow） ──→ 漂沦者磁场 · 自愿协议 · 酵母失活周期</t>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="131">
+  <mergeCells count="159">
     <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A89:C89"/>
     <mergeCell ref="A136:C136"/>
@@ -2380,15 +2813,23 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A71:C71"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A91:C91"/>
     <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A155:C155"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A173:C173"/>
     <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A157:C157"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A138:C138"/>
     <mergeCell ref="A132:C132"/>
@@ -2396,6 +2837,7 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A174:C174"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
@@ -2405,20 +2847,25 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A95:C95"/>
     <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A160:C160"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
     <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A147:C147"/>
     <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A24:C24"/>
@@ -2426,24 +2873,28 @@
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A82:C82"/>
     <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A146:C146"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A99:C99"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A149:C149"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A163:C163"/>
+    <mergeCell ref="A158:C158"/>
     <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A150:C150"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A122:C122"/>
@@ -2452,20 +2903,26 @@
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A167:C167"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A169:C169"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="A162:C162"/>
     <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A137:C137"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A164:C164"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A27:C27"/>
@@ -2475,6 +2932,7 @@
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A116:C116"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A131:C131"/>
@@ -2484,10 +2942,12 @@
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A143:C143"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A48:C48"/>
@@ -2498,6 +2958,7 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A168:C168"/>
     <mergeCell ref="A78:C78"/>
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A65:C65"/>
@@ -2579,7 +3040,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2632,19 +3093,42 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
+          <t xml:space="preserve">    ├─ 地理双态（Metro vs Wastes） ──→ C.Y. 42 · 城带共存 · 荒原猎杀 · 非全域对立</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 荒原自治</t>
+          <t xml:space="preserve">    │       ├─ 城带 Metro Rim ──→ C.Y. 42 · 大城市 · 二代酿民登记共存 · 体内威士忌换币</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ Neo-Western 荒原（Neo-Western Wastes） ──→ C.Y. 25+ · 铁瓶驿道、Saloon、赏金镇</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 星系状态（System Status） ──→ C.Y. 42 · 殖民势力撤离 · 无外来叙事 · 本地自治</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -2652,6 +3136,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="9. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="10. 锈钉" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="11. 锈钉开篇" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20-v13</t>
+          <t>2026-07-20-v14</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 星系放弃 · 威士忌分级 · 荒原赏金猎人</t>
+          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 威士忌分级 · 名义猎人/实质非法提取</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【城带】二代酿民共存 · 体内威士忌换币 · 琥珀交易所</t>
+          <t xml:space="preserve">    ├─ 【城带】二代酿民合法采酿 · 琥珀交易所</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【荒原】猎杀未登记酿民 · 精品酿民高悬赏 · 锈钉行尸走肉循环</t>
+          <t xml:space="preserve">    ├─ 【荒原】击晕提取委托 · 黑市出货 · 锈钉行尸走肉循环</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 名义追捕 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1069,30 +1069,54 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="21">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1121,7 +1145,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1208,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 客户指定酿民 · 击晕提取 · 黑市出手</t>
         </is>
       </c>
     </row>
@@ -1286,14 +1310,14 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
+          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 名义委托中介 · 锈钉接活</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
+          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1343,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1377,7 +1401,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 名义委托中介 · 锈钉隶属</t>
         </is>
       </c>
     </row>
@@ -1387,38 +1411,38 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
         </is>
       </c>
     </row>
@@ -1428,18 +1452,30 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="21">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A20:C20"/>
@@ -1481,7 +1517,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1583,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1565,7 +1601,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
         </is>
       </c>
     </row>
@@ -1579,61 +1615,54 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -1643,7 +1672,6 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1673,7 +1701,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
         </is>
       </c>
     </row>
@@ -1687,35 +1715,35 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1863,7 +1891,7 @@
     <row r="19" outlineLevel="1" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/猎人镇 · 非法提取委托 · 黑市出货</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2269,7 @@
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 名义追捕 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
@@ -2351,246 +2379,246 @@
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7. 威士忌经济</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
         </is>
       </c>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
+          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7. 威士忌经济</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
         </is>
       </c>
     </row>
     <row r="105" outlineLevel="1" ht="16" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
+          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
         </is>
       </c>
     </row>
     <row r="107" outlineLevel="1" ht="16" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
         </is>
       </c>
     </row>
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
+          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
         </is>
       </c>
     </row>
     <row r="109" outlineLevel="1" ht="16" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
+          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
         </is>
       </c>
     </row>
     <row r="110" outlineLevel="1" ht="16" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
+          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
         </is>
       </c>
     </row>
     <row r="111" outlineLevel="1" ht="16" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7b. 城带与荒原</t>
+          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 客户指定酿民 · 击晕提取 · 黑市出手</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
+          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7b. 城带与荒原</t>
         </is>
       </c>
     </row>
     <row r="117" outlineLevel="1" ht="16" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
+          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="119" outlineLevel="1" ht="16" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
         </is>
       </c>
     </row>
     <row r="120" outlineLevel="1" ht="16" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
+          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
+          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
         </is>
       </c>
     </row>
     <row r="122" outlineLevel="1" ht="16" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8. 势力格局</t>
+          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 名义委托中介 · 锈钉接活</t>
         </is>
       </c>
     </row>
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8. 势力格局</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
           <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
         </is>
       </c>
     </row>
-    <row r="126" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A126" s="7" t="inlineStr"/>
-    </row>
-    <row r="127" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
+    <row r="129" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
         </is>
       </c>
     </row>
-    <row r="128" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A128" s="7" t="inlineStr"/>
-    </row>
-    <row r="129" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+    <row r="131" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
         </is>
       </c>
     </row>
-    <row r="130" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A130" s="7" t="inlineStr"/>
-    </row>
-    <row r="131" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="133" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
         </is>
       </c>
     </row>
-    <row r="132" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A132" s="7" t="inlineStr"/>
-    </row>
-    <row r="133" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A134" s="7" t="inlineStr"/>
-    </row>
     <row r="135" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
-        </is>
-      </c>
+      <c r="A135" s="7" t="inlineStr"/>
     </row>
     <row r="136" outlineLevel="1" ht="16" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 名义委托中介 · 锈钉隶属</t>
         </is>
       </c>
     </row>
     <row r="137" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
-        </is>
-      </c>
+      <c r="A137" s="7" t="inlineStr"/>
     </row>
     <row r="138" outlineLevel="1" ht="16" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
         </is>
       </c>
     </row>
@@ -2600,31 +2628,38 @@
     <row r="140" outlineLevel="1" ht="16" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
         </is>
       </c>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A141" s="7" t="inlineStr"/>
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="142" outlineLevel="1" ht="16" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A144" s="7" t="inlineStr"/>
     </row>
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
         </is>
       </c>
     </row>
@@ -2634,175 +2669,192 @@
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
+          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
           <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
         </is>
       </c>
     </row>
-    <row r="148" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A148" s="7" t="inlineStr"/>
-    </row>
-    <row r="149" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
+    <row r="153" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
         </is>
       </c>
     </row>
-    <row r="150" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A150" s="7" t="inlineStr"/>
-    </row>
-    <row r="151" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A152" s="7" t="inlineStr"/>
-    </row>
-    <row r="153" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
-        </is>
-      </c>
+    <row r="155" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A155" s="7" t="inlineStr"/>
     </row>
     <row r="156" outlineLevel="1" ht="16" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
+          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
         </is>
       </c>
     </row>
     <row r="157" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A157" s="7" t="inlineStr"/>
     </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
         </is>
       </c>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
         </is>
       </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
         </is>
       </c>
     </row>
     <row r="168" outlineLevel="1" ht="16" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
         </is>
       </c>
     </row>
     <row r="169" outlineLevel="1" ht="16" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
     <row r="172" outlineLevel="1" ht="16" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="174" outlineLevel="1" ht="16" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="163">
     <mergeCell ref="A128:C128"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
@@ -2828,7 +2880,6 @@
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A138:C138"/>
@@ -2848,9 +2899,9 @@
     <mergeCell ref="A95:C95"/>
     <mergeCell ref="A104:C104"/>
     <mergeCell ref="A160:C160"/>
+    <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
@@ -2862,7 +2913,6 @@
     <mergeCell ref="A121:C121"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A58:C58"/>
@@ -2873,11 +2923,13 @@
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A82:C82"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A123:C123"/>
     <mergeCell ref="A146:C146"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A99:C99"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="A84:C84"/>
@@ -2891,7 +2943,6 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A135:C135"/>
     <mergeCell ref="A150:C150"/>
@@ -2903,9 +2954,11 @@
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A112:C112"/>
     <mergeCell ref="A152:C152"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="A167:C167"/>
+    <mergeCell ref="A176:C176"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A59:C59"/>
@@ -2913,6 +2966,7 @@
     <mergeCell ref="A98:C98"/>
     <mergeCell ref="A169:C169"/>
     <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A178:C178"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A70:C70"/>
@@ -2920,6 +2974,7 @@
     <mergeCell ref="A162:C162"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A177:C177"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A164:C164"/>
@@ -2928,6 +2983,7 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A145:C145"/>
     <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A154:C154"/>
     <mergeCell ref="A129:C129"/>
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A33:C33"/>
@@ -2941,15 +2997,15 @@
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A143:C143"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A166:C166"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
@@ -3107,7 +3163,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/猎人镇 · 非法提取委托 · 黑市出货</t>
         </is>
       </c>
     </row>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20-v14</t>
+          <t>2026-07-20-v15</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶车队 · 二代分城带/精品/荒原</t>
+          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶生态群 · 二代分伴生/城带/精品/荒原</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1014,93 +1014,132 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 单辆载具 · 驿道行驶</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+          <t xml:space="preserve">    └─ 铁瓶生态群（Synth-Rig Ecology） ──→ C.Y. 30+ · 多载具演化群落 · 非帮派组织</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">        ├─ 一代酿民驻内（Gen-1 Inside） ──→ 锈水发酵 · 地表改造</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+          <t xml:space="preserve">        └─ 伴生未觉醒二代（Non-Awakened Gen-2） ──→ 维护调度 · 群落对外接触</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
-        </is>
-      </c>
+      <c r="A15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 脱离群落 · 可流入城带或逃亡荒原</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
+          <t xml:space="preserve">    ├─ 铁瓶伴生未觉醒（Bottle-Companion） ──→ C.Y. 42 · 维护铁瓶生态群 · 随群落行驶</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    └─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 脱离群落或从未登记 · 提取委托常见目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="26">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A22:C22"/>
@@ -1112,6 +1151,7 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A6:C6"/>
@@ -1391,7 +1431,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
+          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1587,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C178"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2206,115 +2246,119 @@
     <row r="69" outlineLevel="1" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
         </is>
       </c>
     </row>
     <row r="70" outlineLevel="1" ht="16" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>▸ 5c. 第三批移民</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
+          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="77" outlineLevel="1" ht="16" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
         </is>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="16" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
+          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
         </is>
       </c>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 名义追捕 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>▸ 6. 存在体谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="84" outlineLevel="1" ht="16" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
+          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
         </is>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A86" s="7" t="inlineStr"/>
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
+        </is>
+      </c>
     </row>
     <row r="87" outlineLevel="1" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
+          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2368,7 @@
     <row r="89" outlineLevel="1" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
+          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2378,7 @@
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 单辆载具 · 驿道行驶</t>
         </is>
       </c>
     </row>
@@ -2348,308 +2392,312 @@
     <row r="93" outlineLevel="1" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+          <t xml:space="preserve">    └─ 铁瓶生态群（Synth-Rig Ecology） ──→ C.Y. 30+ · 多载具演化群落 · 非帮派组织</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="16" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
+          <t xml:space="preserve">        ├─ 一代酿民驻内（Gen-1 Inside） ──→ 锈水发酵 · 地表改造</t>
         </is>
       </c>
     </row>
     <row r="95" outlineLevel="1" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
+          <t xml:space="preserve">        └─ 伴生未觉醒二代（Non-Awakened Gen-2） ──→ 维护调度 · 群落对外接触</t>
         </is>
       </c>
     </row>
     <row r="96" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
-        </is>
-      </c>
+      <c r="A96" s="7" t="inlineStr"/>
     </row>
     <row r="97" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A97" s="7" t="inlineStr"/>
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+        </is>
+      </c>
     </row>
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="99" outlineLevel="1" ht="16" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
         </is>
       </c>
     </row>
     <row r="100" outlineLevel="1" ht="16" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
         </is>
       </c>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7. 威士忌经济</t>
+          <t xml:space="preserve">    ├─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 脱离群落 · 可流入城带或逃亡荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 铁瓶伴生未觉醒（Bottle-Companion） ──→ C.Y. 42 · 维护铁瓶生态群 · 随群落行驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 脱离群落或从未登记 · 提取委托常见目标</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
-        </is>
-      </c>
+      <c r="A104" s="7" t="inlineStr"/>
     </row>
     <row r="105" outlineLevel="1" ht="16" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
         </is>
       </c>
     </row>
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="107" outlineLevel="1" ht="16" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
         </is>
       </c>
     </row>
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
+          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7. 威士忌经济</t>
         </is>
       </c>
     </row>
     <row r="111" outlineLevel="1" ht="16" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
         </is>
       </c>
     </row>
     <row r="112" outlineLevel="1" ht="16" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="113" outlineLevel="1" ht="16" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 客户指定酿民 · 击晕提取 · 黑市出手</t>
+          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7b. 城带与荒原</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
         </is>
       </c>
     </row>
     <row r="117" outlineLevel="1" ht="16" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
+          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
         </is>
       </c>
     </row>
     <row r="119" outlineLevel="1" ht="16" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
+          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
         </is>
       </c>
     </row>
     <row r="120" outlineLevel="1" ht="16" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 客户指定酿民 · 击晕提取 · 黑市出手</t>
         </is>
       </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
+          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7b. 城带与荒原</t>
         </is>
       </c>
     </row>
     <row r="124" outlineLevel="1" ht="16" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 名义委托中介 · 锈钉接活</t>
+          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
         </is>
       </c>
     </row>
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8. 势力格局</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="128" outlineLevel="1" ht="16" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
+          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
         </is>
       </c>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A129" s="7" t="inlineStr"/>
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+        </is>
+      </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A131" s="7" t="inlineStr"/>
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 名义委托中介 · 锈钉接活</t>
+        </is>
+      </c>
     </row>
     <row r="132" outlineLevel="1" ht="16" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8. 势力格局</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
           <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
         </is>
       </c>
     </row>
-    <row r="133" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A133" s="7" t="inlineStr"/>
-    </row>
-    <row r="134" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A135" s="7" t="inlineStr"/>
-    </row>
-    <row r="136" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 名义委托中介 · 锈钉隶属</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A137" s="7" t="inlineStr"/>
-    </row>
-    <row r="138" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A139" s="7" t="inlineStr"/>
-    </row>
     <row r="140" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
-        </is>
-      </c>
+      <c r="A140" s="7" t="inlineStr"/>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
         </is>
       </c>
     </row>
     <row r="142" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
-        </is>
-      </c>
+      <c r="A142" s="7" t="inlineStr"/>
     </row>
     <row r="143" outlineLevel="1" ht="16" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 名义委托中介 · 锈钉隶属</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2707,7 @@
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
         </is>
       </c>
     </row>
@@ -2669,21 +2717,28 @@
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
         </is>
       </c>
     </row>
     <row r="150" outlineLevel="1" ht="16" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2748,7 @@
     <row r="152" outlineLevel="1" ht="16" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
         </is>
       </c>
     </row>
@@ -2703,159 +2758,194 @@
     <row r="154" outlineLevel="1" ht="16" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A155" s="7" t="inlineStr"/>
-    </row>
-    <row r="156" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
+          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="157" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A157" s="7" t="inlineStr"/>
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+        </is>
+      </c>
     </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
-        </is>
-      </c>
+      <c r="A158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A160" s="7" t="inlineStr"/>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A162" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A162" s="7" t="inlineStr"/>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
         </is>
       </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A164" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
-        </is>
-      </c>
+      <c r="A164" s="7" t="inlineStr"/>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
         </is>
       </c>
     </row>
     <row r="168" outlineLevel="1" ht="16" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
         </is>
       </c>
     </row>
     <row r="169" outlineLevel="1" ht="16" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
         </is>
       </c>
     </row>
     <row r="172" outlineLevel="1" ht="16" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
         </is>
       </c>
     </row>
     <row r="174" outlineLevel="1" ht="16" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
         </is>
       </c>
     </row>
     <row r="175" outlineLevel="1" ht="16" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
         </is>
       </c>
     </row>
     <row r="176" outlineLevel="1" ht="16" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
         </is>
       </c>
     </row>
-    <row r="177" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A177" s="7" t="inlineStr">
+    <row r="184" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A184" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
         </is>
       </c>
     </row>
-    <row r="178" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
+    <row r="185" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="163">
+  <mergeCells count="170">
     <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A89:C89"/>
@@ -2865,21 +2955,26 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A185:C185"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A181:C181"/>
     <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A184:C184"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A156:C156"/>
     <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A155:C155"/>
     <mergeCell ref="A93:C93"/>
     <mergeCell ref="A173:C173"/>
     <mergeCell ref="A130:C130"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A138:C138"/>
@@ -2889,10 +2984,10 @@
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
     <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A133:C133"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="A12:C12"/>
@@ -2902,6 +2997,7 @@
     <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
@@ -2913,15 +3009,14 @@
     <mergeCell ref="A121:C121"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A73:C73"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A82:C82"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A123:C123"/>
     <mergeCell ref="A146:C146"/>
@@ -2943,12 +3038,12 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A135:C135"/>
     <mergeCell ref="A150:C150"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
-    <mergeCell ref="A122:C122"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A125:C125"/>
     <mergeCell ref="A72:C72"/>
@@ -2962,6 +3057,7 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A182:C182"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A98:C98"/>
     <mergeCell ref="A169:C169"/>
@@ -2974,7 +3070,6 @@
     <mergeCell ref="A162:C162"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A177:C177"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A164:C164"/>
@@ -2995,17 +3090,18 @@
     <mergeCell ref="A100:C100"/>
     <mergeCell ref="A140:C140"/>
     <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A143:C143"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A166:C166"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
@@ -3564,7 +3660,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -3624,20 +3720,35 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -3645,6 +3756,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -21,9 +21,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8b. 戒酒教" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -496,7 +497,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20-v15</t>
+          <t>2026-07-20-v16</t>
         </is>
       </c>
     </row>
@@ -799,26 +800,33 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. 9. 叙事入口</t>
+          <t xml:space="preserve">  13. 8b. 戒酒教</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14. 10. 锈钉</t>
+          <t xml:space="preserve">  14. 9. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15. 11. 锈钉开篇</t>
+          <t xml:space="preserve">  15. 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  16. 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
@@ -832,6 +840,7 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A14:C14"/>
@@ -1383,7 +1392,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1461,58 +1470,217 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 反身作酒窖 · 分裂两派 · 见模块7b</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 8b. 戒酒教</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 起源于胃植入/酵母宗教化 · 禁饮威士忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 共同基底（Shared Creed） ──→ 肉体不得为酒窖 · 不隶属城酿署</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿与荒原非法提取并存</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>收割派 Reapers（Harvest Faction） ──→ C.Y. 42 · 酵可赎命不可夺 · 反击晕非法提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 击晕提取即渎 · 城带采酿为契约束缚</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 赎酵站（Redemption Still） ──→ 锈水去毒发酵 · 不取自酿民体内</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 庇护廊（Shelter Corridors） ──→ 收留觉醒逃亡酿民 · 城缘地下</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 赎酵礼（Redemption Rite） ──→ 伏击猎人求放人/少取 · 不追杀客户</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城缘灰诊（Rim Clinics） ──→ 卖去毒锈水 · 治提取后遗症 · 换情报</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可谈判赎人 · 「可赎之渎」档案</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>纯净派 Purifiers（Purity Faction） ──→ C.Y. 42 · 酒即秽瓶即牢 · 凡酿皆罪</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr"/>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 否定城带/黑市/铁瓶生态群 · 发酵舱须净化</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+          <t xml:space="preserve">    ├─ 尘骑巡游（Dust Riders） ──→ 铁瓶线/Saloon机动 · 十三月尘暴掩护</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr"/>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 净火行动（Purifying Fire） ──→ 焚回收槽 · 黑市酵舱 · 铁瓶外露发酵舱</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
+          <t xml:space="preserve">    ├─ 断酿伏击（Sever Brew Ambush） ──→ 袭击猎人交货点 · 砸酵管放目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 净居聚落（Ascetic Communes） ──→ 荒漠深处 · 只饮去毒无醇锈水</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 净化目标 · 与收割派互斥</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A22:C22"/>
@@ -1524,6 +1692,7 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A6:C6"/>
@@ -1534,7 +1703,115 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教收割派（Temperance Reapers） ──→ C.Y. 42 · 赎酵站/庇护廊 · 反非法提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教纯净派（Temperance Purifiers） ──→ C.Y. 42 · 尘骑净火 · 焚黑市与铁瓶外露舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1550,54 +1827,70 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 9. 叙事入口</t>
+          <t>《瓶与源》· 10. 锈钉</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
         </is>
       </c>
     </row>
@@ -1618,107 +1911,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 10. 锈钉</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1808,7 +2001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2717,241 +2910,386 @@
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 反身作酒窖 · 分裂两派 · 见模块7b</t>
         </is>
       </c>
     </row>
     <row r="148" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A148" s="7" t="inlineStr"/>
     </row>
     <row r="149" outlineLevel="1" ht="16" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A151" s="7" t="inlineStr"/>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8b. 戒酒教</t>
+        </is>
+      </c>
     </row>
     <row r="152" outlineLevel="1" ht="16" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 起源于胃植入/酵母宗教化 · 禁饮威士忌</t>
         </is>
       </c>
     </row>
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A153" s="7" t="inlineStr"/>
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="154" outlineLevel="1" ht="16" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    ├─ 共同基底（Shared Creed） ──→ 肉体不得为酒窖 · 不隶属城酿署</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿与荒原非法提取并存</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A156" s="7" t="inlineStr"/>
     </row>
     <row r="157" outlineLevel="1" ht="16" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+          <t>收割派 Reapers（Harvest Faction） ──→ C.Y. 42 · 酵可赎命不可夺 · 反击晕非法提取</t>
         </is>
       </c>
     </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A158" s="7" t="inlineStr"/>
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="159" outlineLevel="1" ht="16" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 击晕提取即渎 · 城带采酿为契约束缚</t>
         </is>
       </c>
     </row>
     <row r="160" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A160" s="7" t="inlineStr"/>
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 赎酵站（Redemption Still） ──→ 锈水去毒发酵 · 不取自酿民体内</t>
+        </is>
+      </c>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+          <t xml:space="preserve">    ├─ 庇护廊（Shelter Corridors） ──→ 收留觉醒逃亡酿民 · 城缘地下</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A162" s="7" t="inlineStr"/>
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 赎酵礼（Redemption Rite） ──→ 伏击猎人求放人/少取 · 不追杀客户</t>
+        </is>
+      </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+          <t xml:space="preserve">    ├─ 城缘灰诊（Rim Clinics） ──→ 卖去毒锈水 · 治提取后遗症 · 换情报</t>
         </is>
       </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A164" s="7" t="inlineStr"/>
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可谈判赎人 · 「可赎之渎」档案</t>
+        </is>
+      </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
+      <c r="A165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>纯净派 Purifiers（Purity Faction） ──→ C.Y. 42 · 酒即秽瓶即牢 · 凡酿皆罪</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="168" outlineLevel="1" ht="16" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 否定城带/黑市/铁瓶生态群 · 发酵舱须净化</t>
         </is>
       </c>
     </row>
     <row r="169" outlineLevel="1" ht="16" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 尘骑巡游（Dust Riders） ──→ 铁瓶线/Saloon机动 · 十三月尘暴掩护</t>
         </is>
       </c>
     </row>
     <row r="170" outlineLevel="1" ht="16" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+          <t xml:space="preserve">    ├─ 净火行动（Purifying Fire） ──→ 焚回收槽 · 黑市酵舱 · 铁瓶外露发酵舱</t>
         </is>
       </c>
     </row>
     <row r="171" outlineLevel="1" ht="16" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
+          <t xml:space="preserve">    ├─ 断酿伏击（Sever Brew Ambush） ──→ 袭击猎人交货点 · 砸酵管放目标</t>
         </is>
       </c>
     </row>
     <row r="172" outlineLevel="1" ht="16" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
+          <t xml:space="preserve">    ├─ 净居聚落（Ascetic Communes） ──→ 荒漠深处 · 只饮去毒无醇锈水</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A174" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 净化目标 · 与收割派互斥</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="176" outlineLevel="1" ht="16" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
         </is>
       </c>
     </row>
     <row r="179" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
-        </is>
-      </c>
+      <c r="A179" s="7" t="inlineStr"/>
     </row>
     <row r="180" outlineLevel="1" ht="16" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
         </is>
       </c>
     </row>
     <row r="181" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A181" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
-        </is>
-      </c>
+      <c r="A181" s="7" t="inlineStr"/>
     </row>
     <row r="182" outlineLevel="1" ht="16" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
         </is>
       </c>
     </row>
     <row r="183" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
-        </is>
-      </c>
+      <c r="A183" s="7" t="inlineStr"/>
     </row>
     <row r="184" outlineLevel="1" ht="16" customHeight="1">
       <c r="A184" s="7" t="inlineStr">
         <is>
+          <t>戒酒教收割派（Temperance Reapers） ──→ C.Y. 42 · 赎酵站/庇护廊 · 反非法提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A185" s="7" t="inlineStr"/>
+    </row>
+    <row r="186" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教纯净派（Temperance Purifiers） ──→ C.Y. 42 · 尘骑净火 · 焚黑市与铁瓶外露舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
         </is>
       </c>
     </row>
-    <row r="185" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
+    <row r="208" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A208" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="170">
+  <mergeCells count="192">
     <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A193:C193"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A192:C192"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
@@ -2959,6 +3297,7 @@
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A185:C185"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A194:C194"/>
     <mergeCell ref="A181:C181"/>
     <mergeCell ref="A91:C91"/>
     <mergeCell ref="A184:C184"/>
@@ -2968,6 +3307,7 @@
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A155:C155"/>
     <mergeCell ref="A93:C93"/>
     <mergeCell ref="A173:C173"/>
     <mergeCell ref="A130:C130"/>
@@ -2983,11 +3323,13 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="A205:C205"/>
     <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A198:C198"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="A12:C12"/>
@@ -3012,18 +3354,23 @@
     <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A202:C202"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A186:C186"/>
     <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A201:C201"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A197:C197"/>
     <mergeCell ref="A146:C146"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A187:C187"/>
     <mergeCell ref="A99:C99"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A108:C108"/>
@@ -3035,21 +3382,25 @@
     <mergeCell ref="A101:C101"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A188:C188"/>
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A190:C190"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A199:C199"/>
     <mergeCell ref="A152:C152"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="A167:C167"/>
@@ -3060,6 +3411,7 @@
     <mergeCell ref="A182:C182"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A191:C191"/>
     <mergeCell ref="A169:C169"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A178:C178"/>
@@ -3070,6 +3422,7 @@
     <mergeCell ref="A162:C162"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A177:C177"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A164:C164"/>
@@ -3080,8 +3433,10 @@
     <mergeCell ref="A139:C139"/>
     <mergeCell ref="A154:C154"/>
     <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A195:C195"/>
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A203:C203"/>
     <mergeCell ref="A85:C85"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A8:C8"/>
@@ -3102,10 +3457,12 @@
     <mergeCell ref="A143:C143"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A166:C166"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20-v16</t>
+          <t>2026-07-20-v17</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 反身作酒窖 · 分裂两派 · 见模块7b</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人与戒酒教</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1530,7 +1530,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 起源于胃植入/酵母宗教化 · 禁饮威士忌</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
         </is>
       </c>
     </row>
@@ -1544,14 +1544,14 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 共同基底（Shared Creed） ──→ 肉体不得为酒窖 · 不隶属城酿署</t>
+          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿与荒原非法提取并存</t>
+          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>收割派 Reapers（Harvest Faction） ──→ C.Y. 42 · 酵可赎命不可夺 · 反击晕非法提取</t>
+          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
         </is>
       </c>
     </row>
@@ -1575,115 +1575,84 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 击晕提取即渎 · 城带采酿为契约束缚</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 赎酵站（Redemption Still） ──→ 锈水去毒发酵 · 不取自酿民体内</t>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交/告密 · 不亲手焚杀</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 庇护廊（Shelter Corridors） ──→ 收留觉醒逃亡酿民 · 城缘地下</t>
+          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 赎酵礼（Redemption Rite） ──→ 伏击猎人求放人/少取 · 不追杀客户</t>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借猎人刀</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 城缘灰诊（Rim Clinics） ──→ 卖去毒锈水 · 治提取后遗症 · 换情报</t>
-        </is>
-      </c>
+      <c r="A14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可谈判赎人 · 「可赎之渎」档案</t>
+          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>纯净派 Purifiers（Purity Faction） ──→ C.Y. 42 · 酒即秽瓶即牢 · 凡酿皆罪</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 否定城带/黑市/铁瓶生态群 · 发酵舱须净化</t>
+          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 尘骑巡游（Dust Riders） ──→ 铁瓶线/Saloon机动 · 十三月尘暴掩护</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 净火行动（Purifying Fire） ──→ 焚回收槽 · 黑市酵舱 · 铁瓶外露发酵舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 断酿伏击（Sever Brew Ambush） ──→ 袭击猎人交货点 · 砸酵管放目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 净居聚落（Ascetic Communes） ──→ 荒漠深处 · 只饮去毒无醇锈水</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 净化目标 · 与收割派互斥</t>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="19">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A20:C20"/>
@@ -1692,7 +1661,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A6:C6"/>
@@ -1766,7 +1734,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>戒酒教收割派（Temperance Reapers） ──→ C.Y. 42 · 赎酵站/庇护廊 · 反非法提取</t>
+          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1744,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>戒酒教纯净派（Temperance Purifiers） ──→ C.Y. 42 · 尘骑净火 · 焚黑市与铁瓶外露舱</t>
+          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 焚杀酿民</t>
         </is>
       </c>
     </row>
@@ -2001,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C208"/>
+  <dimension ref="A1:C204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2910,7 +2878,7 @@
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 反身作酒窖 · 分裂两派 · 见模块7b</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2888,7 @@
     <row r="149" outlineLevel="1" ht="16" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人与戒酒教</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2902,7 @@
     <row r="152" outlineLevel="1" ht="16" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 起源于胃植入/酵母宗教化 · 禁饮威士忌</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
         </is>
       </c>
     </row>
@@ -2948,14 +2916,14 @@
     <row r="154" outlineLevel="1" ht="16" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 共同基底（Shared Creed） ──→ 肉体不得为酒窖 · 不隶属城酿署</t>
+          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
         </is>
       </c>
     </row>
     <row r="155" outlineLevel="1" ht="16" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿与荒原非法提取并存</t>
+          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2933,7 @@
     <row r="157" outlineLevel="1" ht="16" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>收割派 Reapers（Harvest Faction） ──→ C.Y. 42 · 酵可赎命不可夺 · 反击晕非法提取</t>
+          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
         </is>
       </c>
     </row>
@@ -2979,115 +2947,107 @@
     <row r="159" outlineLevel="1" ht="16" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 击晕提取即渎 · 城带采酿为契约束缚</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
         </is>
       </c>
     </row>
     <row r="160" outlineLevel="1" ht="16" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 赎酵站（Redemption Still） ──→ 锈水去毒发酵 · 不取自酿民体内</t>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交/告密 · 不亲手焚杀</t>
         </is>
       </c>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 庇护廊（Shelter Corridors） ──→ 收留觉醒逃亡酿民 · 城缘地下</t>
+          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 赎酵礼（Redemption Rite） ──→ 伏击猎人求放人/少取 · 不追杀客户</t>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借猎人刀</t>
         </is>
       </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 城缘灰诊（Rim Clinics） ──→ 卖去毒锈水 · 治提取后遗症 · 换情报</t>
-        </is>
-      </c>
+      <c r="A163" s="7" t="inlineStr"/>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可谈判赎人 · 「可赎之渎」档案</t>
+          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A165" s="7" t="inlineStr"/>
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="166" outlineLevel="1" ht="16" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>纯净派 Purifiers（Purity Faction） ──→ C.Y. 42 · 酒即秽瓶即牢 · 凡酿皆罪</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
         </is>
       </c>
     </row>
     <row r="167" outlineLevel="1" ht="16" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
         </is>
       </c>
     </row>
     <row r="168" outlineLevel="1" ht="16" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 否定城带/黑市/铁瓶生态群 · 发酵舱须净化</t>
+          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
         </is>
       </c>
     </row>
     <row r="169" outlineLevel="1" ht="16" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 尘骑巡游（Dust Riders） ──→ 铁瓶线/Saloon机动 · 十三月尘暴掩护</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 净火行动（Purifying Fire） ──→ 焚回收槽 · 黑市酵舱 · 铁瓶外露发酵舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 断酿伏击（Sever Brew Ambush） ──→ 袭击猎人交货点 · 砸酵管放目标</t>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="172" outlineLevel="1" ht="16" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 净居聚落（Ascetic Communes） ──→ 荒漠深处 · 只饮去毒无醇锈水</t>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 净化目标 · 与收割派互斥</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
-        </is>
-      </c>
+      <c r="A173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A175" s="7" t="inlineStr"/>
     </row>
     <row r="176" outlineLevel="1" ht="16" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3057,7 @@
     <row r="178" outlineLevel="1" ht="16" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3067,7 @@
     <row r="180" outlineLevel="1" ht="16" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3077,7 @@
     <row r="182" outlineLevel="1" ht="16" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 焚杀酿民</t>
         </is>
       </c>
     </row>
@@ -3127,164 +3087,143 @@
     <row r="184" outlineLevel="1" ht="16" customHeight="1">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>戒酒教收割派（Temperance Reapers） ──→ C.Y. 42 · 赎酵站/庇护廊 · 反非法提取</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A185" s="7" t="inlineStr"/>
-    </row>
-    <row r="186" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教纯净派（Temperance Purifiers） ──→ C.Y. 42 · 尘骑净火 · 焚黑市与铁瓶外露舱</t>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
         </is>
       </c>
     </row>
     <row r="187" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A187" s="7" t="inlineStr"/>
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
+        </is>
+      </c>
     </row>
     <row r="188" outlineLevel="1" ht="16" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
         </is>
       </c>
     </row>
     <row r="191" outlineLevel="1" ht="16" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
         </is>
       </c>
     </row>
     <row r="192" outlineLevel="1" ht="16" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
         </is>
       </c>
     </row>
     <row r="193" outlineLevel="1" ht="16" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
         </is>
       </c>
     </row>
     <row r="194" outlineLevel="1" ht="16" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
         </is>
       </c>
     </row>
     <row r="195" outlineLevel="1" ht="16" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A196" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
     <row r="198" outlineLevel="1" ht="16" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
         </is>
       </c>
     </row>
     <row r="199" outlineLevel="1" ht="16" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
         </is>
       </c>
     </row>
     <row r="202" outlineLevel="1" ht="16" customHeight="1">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
         </is>
       </c>
     </row>
     <row r="203" outlineLevel="1" ht="16" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
         </is>
       </c>
     </row>
     <row r="204" outlineLevel="1" ht="16" customHeight="1">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A205" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A206" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A207" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A208" s="7" t="inlineStr">
-        <is>
           <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="192">
+  <mergeCells count="188">
     <mergeCell ref="A128:C128"/>
     <mergeCell ref="A193:C193"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A21:C21"/>
@@ -3295,7 +3234,6 @@
     <mergeCell ref="A113:C113"/>
     <mergeCell ref="A179:C179"/>
     <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A185:C185"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A194:C194"/>
     <mergeCell ref="A181:C181"/>
@@ -3323,8 +3261,7 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A196:C196"/>
-    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A174:C174"/>
     <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
@@ -3344,6 +3281,7 @@
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A96:C96"/>
@@ -3351,7 +3289,6 @@
     <mergeCell ref="A121:C121"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A202:C202"/>
@@ -3380,6 +3317,7 @@
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A158:C158"/>
     <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A189:C189"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
     <mergeCell ref="A204:C204"/>
@@ -3390,7 +3328,6 @@
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A20:C20"/>
@@ -3462,7 +3399,6 @@
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -21,10 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8b. 戒酒教" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8a. 当地警署" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8c. 酿造帮" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8b. 戒酒教" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -660,7 +662,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 威士忌分级 · 名义猎人/实质非法提取</t>
+          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 威士忌分级 · 警署悬赏/实质非法提取</t>
         </is>
       </c>
     </row>
@@ -674,7 +676,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【城带】二代酿民合法采酿 · 琥珀交易所</t>
+          <t xml:space="preserve">    ├─ 【城带】二代酿民合法采酿 · 琥珀交易所 · 当地警署</t>
         </is>
       </c>
     </row>
@@ -688,7 +690,7 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【荒原】击晕提取委托 · 黑市出货 · 锈钉行尸走肉循环</t>
+          <t xml:space="preserve">    ├─ 【荒原】警署悬赏 · 酿造帮园区 · 黑市出货 · 锈钉行尸走肉循环</t>
         </is>
       </c>
     </row>
@@ -800,33 +802,47 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. 8b. 戒酒教</t>
+          <t xml:space="preserve">  13. 8a. 当地警署</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14. 9. 叙事入口</t>
+          <t xml:space="preserve">  14. 8c. 酿造帮</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15. 10. 锈钉</t>
+          <t xml:space="preserve">  15. 8b. 戒酒教</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  16. 11. 锈钉开篇</t>
+          <t xml:space="preserve">  16. 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  17. 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  18. 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
@@ -861,10 +877,12 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="B5:C5"/>
@@ -940,7 +958,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 名义追捕 · 实质击晕提取售黑市</t>
+          <t xml:space="preserve">    └─ 缉拿手（The Hunter） ──→ C.Y. 30– · 警署悬赏承包商 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
@@ -964,7 +982,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1103,43 +1121,50 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 脱离群落或从未登记 · 提取委托常见目标</t>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 警署悬赏与黑市提取常见目标</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr"/>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 酿造帮奴役酿民（Syndicate Bonded） ──→ C.Y. 42 · 园区卖身条款 · 出逃即警署悬赏</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
-        </is>
-      </c>
+      <c r="A24" s="7" t="inlineStr"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>缉拿手（The Hunter） ──→ C.Y. 30– · 警署登记承包商 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 警署悬赏 · 抓捕凶犯与潜逃奴役酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
@@ -1156,6 +1181,7 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A9:C9"/>
@@ -1257,7 +1283,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 客户指定酿民 · 击晕提取 · 黑市出手</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 警署悬赏 · 击晕提取 · 黑市出手</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1318,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1352,28 +1378,380 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 警署悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 名义委托中介 · 锈钉接活</t>
+          <t xml:space="preserve">        ├─ 当地警署（Constabulary Post） ──→ 悬赏布告 · 登记缉拿手 · 锈钉接活</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        ├─ 酿造帮园区（Brewing Syndicate） ──→ 高利贷奴役酿造 · 出逃悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 8. 势力格局</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中推动酿造帮收编脱约者</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏缉拿 · 抓捕凶犯与潜逃奴役酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷园区 · 诓骗酿民卖身 · 非人权组织</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避警署/酿造帮/戒酒教</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者（The Wander） ──→ C.Y. 42 · 警署高危悬赏群体 · 锈钉禁忌</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 8a. 当地警署</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏布告与接取 · 取代猎人公会</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 职能（Functions） ──→ 抓捕凶犯 · 追捕潜逃奴役酿民 · 羁押移交</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 悬赏四类（Bounty Categories） ──→ 酿民/圣火派/凶犯/漂沦者</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 酿民类（Brewfolk Bounties） ──→ 出逃奴役酿民 · 脱约精品酿民 · 未登记者</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 圣火派（Sacred Fire Bounties） ──→ 戒酒教净化武装 · 格杀勿论</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 凶犯类（Felony Bounties） ──→ 谋杀犯 · 劫酵/劫火 · 袭警</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 漂沦者（Wander Bounties） ──→ 高危群体 · 活捉隔离/格杀许可</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 缉拿手制度（Contractor System） ──→ 登记接活 · 名义抓捕 · 实质黑市提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 驿站驻点（Outpost Posts） ──→ 城缘Saloon旁 · 锈钉挂牌处</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 8c. 酿造帮</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷奴役集团 · 非人权组织</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 诱贷（Debt Trap） ──→ 滤材酵苗医疗通行费 · 复利滚欠</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 卖身条款（Bondage Contract） ──→ 终身酿造义务 · 出逃全债加速 · 窖芯抵押</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 园区囚禁（Compound Yards） ──→ 围栏发酵舱 · 24垦时排班 · 编号管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 出逃悬赏（Escape Bounties） ──→ 向警署挂潜逃奴役酿民 · 园区出酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 与窖行（Vault House Ties） ──→ 精品筛选转卖灰市 · 脱约者洗合同收编</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对外形象（Public Face） ──→ 宣传安置就业 · 实际债务陷阱无退出</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -1387,127 +1765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 8. 势力格局</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 名义委托中介 · 锈钉隶属</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人与戒酒教</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1582,7 +1840,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交/告密 · 不亲手焚杀</t>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交警署/告密 · 不亲手焚杀</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1854,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借猎人刀</t>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借缉拿手刀</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1929,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1694,7 +1952,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 警署缉拿手 · 击晕提取售黑市 · 精品窖七破局</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1982,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+          <t>酿造帮园区酿民（Syndicate Bonded Brewfolk） ──→ C.Y. 42 · 卖身条款 · 出逃悬赏 · R-xxx编号</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1992,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
         </is>
       </c>
     </row>
@@ -1744,7 +2002,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 焚杀酿民</t>
+          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
         </is>
       </c>
     </row>
@@ -1754,32 +2012,56 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 警署悬赏目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>当地警署缉拿手（Constabulary Contractor） ──→ C.Y. 42 · 悬赏四类 · 锈钉式黑市提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="18">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1802,7 +2084,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
         </is>
       </c>
     </row>
@@ -1816,28 +2098,28 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
         </is>
       </c>
     </row>
@@ -1851,7 +2133,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
         </is>
       </c>
     </row>
@@ -1866,90 +2148,6 @@
   <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 11. 锈钉开篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -1969,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C204"/>
+  <dimension ref="A1:C236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2484,7 +2682,7 @@
     <row r="81" outlineLevel="1" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 名义追捕 · 实质击晕提取售黑市</t>
+          <t xml:space="preserve">    └─ 缉拿手（The Hunter） ──→ C.Y. 30– · 警署悬赏承包商 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
@@ -2619,216 +2817,220 @@
     <row r="103" outlineLevel="1" ht="16" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 脱离群落或从未登记 · 提取委托常见目标</t>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 警署悬赏与黑市提取常见目标</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A104" s="7" t="inlineStr"/>
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 酿造帮奴役酿民（Syndicate Bonded） ──→ C.Y. 42 · 园区卖身条款 · 出逃即警署悬赏</t>
+        </is>
+      </c>
     </row>
     <row r="105" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 名义猎人 · 实质击晕提取客户指定酿民威士忌</t>
-        </is>
-      </c>
+      <c r="A105" s="7" t="inlineStr"/>
     </row>
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>缉拿手（The Hunter） ──→ C.Y. 30– · 警署登记承包商 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
     <row r="107" outlineLevel="1" ht="16" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 公会委托 · 追捕/回收酿民</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 警署悬赏 · 抓捕凶犯与潜逃奴役酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>▸ 7. 威士忌经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
         </is>
       </c>
     </row>
     <row r="112" outlineLevel="1" ht="16" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
         </is>
       </c>
     </row>
     <row r="113" outlineLevel="1" ht="16" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
+          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
         </is>
       </c>
     </row>
     <row r="115" outlineLevel="1" ht="16" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
         </is>
       </c>
     </row>
     <row r="116" outlineLevel="1" ht="16" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
+          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
         </is>
       </c>
     </row>
     <row r="117" outlineLevel="1" ht="16" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
+          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
+          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
         </is>
       </c>
     </row>
     <row r="119" outlineLevel="1" ht="16" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
+          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
         </is>
       </c>
     </row>
     <row r="120" outlineLevel="1" ht="16" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 客户指定酿民 · 击晕提取 · 黑市出手</t>
+          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
         </is>
       </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 警署悬赏 · 击晕提取 · 黑市出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>▸ 7b. 城带与荒原</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
         </is>
       </c>
     </row>
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
         </is>
       </c>
     </row>
     <row r="126" outlineLevel="1" ht="16" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="127" outlineLevel="1" ht="16" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
+          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
         </is>
       </c>
     </row>
     <row r="128" outlineLevel="1" ht="16" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
+          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
         </is>
       </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
+          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
         </is>
       </c>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 名义委托中介 · 锈钉接活</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 警署悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="132" outlineLevel="1" ht="16" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        ├─ 当地警署（Constabulary Post） ──→ 悬赏布告 · 登记缉拿手 · 锈钉接活</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ├─ 酿造帮园区（Brewing Syndicate） ──→ 高利贷奴役酿造 · 出逃悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>▸ 8. 势力格局</t>
         </is>
       </c>
-    </row>
-    <row r="135" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A136" s="7" t="inlineStr"/>
     </row>
     <row r="137" outlineLevel="1" ht="16" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
+          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
         </is>
       </c>
     </row>
@@ -2838,7 +3040,7 @@
     <row r="139" outlineLevel="1" ht="16" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
+          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
         </is>
       </c>
     </row>
@@ -2848,7 +3050,7 @@
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中推动酿造帮收编脱约者</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3060,7 @@
     <row r="143" outlineLevel="1" ht="16" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 名义委托中介 · 锈钉隶属</t>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏缉拿 · 抓捕凶犯与潜逃奴役酿民</t>
         </is>
       </c>
     </row>
@@ -2868,7 +3070,7 @@
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷园区 · 诓骗酿民卖身 · 非人权组织</t>
         </is>
       </c>
     </row>
@@ -2878,7 +3080,7 @@
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
+          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
         </is>
       </c>
     </row>
@@ -2888,343 +3090,535 @@
     <row r="149" outlineLevel="1" ht="16" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人与戒酒教</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8b. 戒酒教</t>
+          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
         </is>
       </c>
     </row>
     <row r="152" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
-        </is>
-      </c>
+      <c r="A152" s="7" t="inlineStr"/>
     </row>
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避警署/酿造帮/戒酒教</t>
         </is>
       </c>
     </row>
     <row r="154" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
-        </is>
-      </c>
+      <c r="A154" s="7" t="inlineStr"/>
     </row>
     <row r="155" outlineLevel="1" ht="16" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A156" s="7" t="inlineStr"/>
-    </row>
-    <row r="157" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
+          <t>漂沦者（The Wander） ──→ C.Y. 42 · 警署高危悬赏群体 · 锈钉禁忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8a. 当地警署</t>
         </is>
       </c>
     </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏布告与接取 · 取代猎人公会</t>
         </is>
       </c>
     </row>
     <row r="159" outlineLevel="1" ht="16" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="160" outlineLevel="1" ht="16" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交/告密 · 不亲手焚杀</t>
+          <t xml:space="preserve">    ├─ 职能（Functions） ──→ 抓捕凶犯 · 追捕潜逃奴役酿民 · 羁押移交</t>
         </is>
       </c>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
+          <t xml:space="preserve">    ├─ 悬赏四类（Bounty Categories） ──→ 酿民/圣火派/凶犯/漂沦者</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借猎人刀</t>
+          <t xml:space="preserve">    │       ├─ 酿民类（Brewfolk Bounties） ──→ 出逃奴役酿民 · 脱约精品酿民 · 未登记者</t>
         </is>
       </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A163" s="7" t="inlineStr"/>
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 圣火派（Sacred Fire Bounties） ──→ 戒酒教净化武装 · 格杀勿论</t>
+        </is>
+      </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
+          <t xml:space="preserve">    │       ├─ 凶犯类（Felony Bounties） ──→ 谋杀犯 · 劫酵/劫火 · 袭警</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 漂沦者（Wander Bounties） ──→ 高危群体 · 活捉隔离/格杀许可</t>
         </is>
       </c>
     </row>
     <row r="166" outlineLevel="1" ht="16" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
+          <t xml:space="preserve">    ├─ 缉拿手制度（Contractor System） ──→ 登记接活 · 名义抓捕 · 实质黑市提取</t>
         </is>
       </c>
     </row>
     <row r="167" outlineLevel="1" ht="16" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
+          <t xml:space="preserve">    └─ 驿站驻点（Outpost Posts） ──→ 城缘Saloon旁 · 锈钉挂牌处</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8c. 酿造帮</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷奴役集团 · 非人权组织</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="172" outlineLevel="1" ht="16" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 名义猎人 · 击晕提取售黑市 · 精品窖七破局</t>
+          <t xml:space="preserve">    ├─ 诱贷（Debt Trap） ──→ 滤材酵苗医疗通行费 · 复利滚欠</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A173" s="7" t="inlineStr"/>
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 卖身条款（Bondage Contract） ──→ 终身酿造义务 · 出逃全债加速 · 窖芯抵押</t>
+        </is>
+      </c>
     </row>
     <row r="174" outlineLevel="1" ht="16" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+          <t xml:space="preserve">    ├─ 园区囚禁（Compound Yards） ──→ 围栏发酵舱 · 24垦时排班 · 编号管理</t>
         </is>
       </c>
     </row>
     <row r="175" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A175" s="7" t="inlineStr"/>
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 出逃悬赏（Escape Bounties） ──→ 向警署挂潜逃奴役酿民 · 园区出酬金</t>
+        </is>
+      </c>
     </row>
     <row r="176" outlineLevel="1" ht="16" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+          <t xml:space="preserve">    ├─ 与窖行（Vault House Ties） ──→ 精品筛选转卖灰市 · 脱约者洗合同收编</t>
         </is>
       </c>
     </row>
     <row r="177" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A177" s="7" t="inlineStr"/>
-    </row>
-    <row r="178" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A179" s="7" t="inlineStr"/>
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对外形象（Public Face） ──→ 宣传安置就业 · 实际债务陷阱无退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8b. 戒酒教</t>
+        </is>
+      </c>
     </row>
     <row r="180" outlineLevel="1" ht="16" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
         </is>
       </c>
     </row>
     <row r="181" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A181" s="7" t="inlineStr"/>
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="182" outlineLevel="1" ht="16" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 焚杀酿民</t>
+          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
         </is>
       </c>
     </row>
     <row r="183" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A183" s="7" t="inlineStr"/>
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
+        </is>
+      </c>
     </row>
     <row r="184" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
+      <c r="A184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="187" outlineLevel="1" ht="16" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义猎人 · 实质非法提取手 · 主线视角</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
         </is>
       </c>
     </row>
     <row r="188" outlineLevel="1" ht="16" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交警署/告密 · 不亲手焚杀</t>
         </is>
       </c>
     </row>
     <row r="189" outlineLevel="1" ht="16" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 赏金猎人公会登记手 The Hunter</t>
+          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
         </is>
       </c>
     </row>
     <row r="190" outlineLevel="1" ht="16" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接委托→击晕指定酿民→非法提取威士忌→黑市出手</t>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借缉拿手刀</t>
         </is>
       </c>
     </row>
     <row r="191" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A191" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问客户与目标 · 只关心酬金</t>
-        </is>
-      </c>
+      <c r="A191" s="7" t="inlineStr"/>
     </row>
     <row r="192" outlineLevel="1" ht="16" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
         </is>
       </c>
     </row>
     <row r="193" outlineLevel="1" ht="16" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="194" outlineLevel="1" ht="16" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
         </is>
       </c>
     </row>
     <row r="195" outlineLevel="1" ht="16" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A198" s="7" t="inlineStr">
-        <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 非法提取链</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="200" outlineLevel="1" ht="16" customHeight="1">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七提取委托 ×5</t>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 警署缉拿手 · 击晕提取售黑市 · 精品窖七破局</t>
         </is>
       </c>
     </row>
     <row r="201" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A201" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
-        </is>
-      </c>
+      <c r="A201" s="7" t="inlineStr"/>
     </row>
     <row r="202" outlineLevel="1" ht="16" customHeight="1">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
         </is>
       </c>
     </row>
     <row r="203" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A203" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
-        </is>
-      </c>
+      <c r="A203" s="7" t="inlineStr"/>
     </row>
     <row r="204" outlineLevel="1" ht="16" customHeight="1">
       <c r="A204" s="7" t="inlineStr">
         <is>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A205" s="7" t="inlineStr"/>
+    </row>
+    <row r="206" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>酿造帮园区酿民（Syndicate Bonded Brewfolk） ──→ C.Y. 42 · 卖身条款 · 出逃悬赏 · R-xxx编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A207" s="7" t="inlineStr"/>
+    </row>
+    <row r="208" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A209" s="7" t="inlineStr"/>
+    </row>
+    <row r="210" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A211" s="7" t="inlineStr"/>
+    </row>
+    <row r="212" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 警署悬赏目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A213" s="7" t="inlineStr"/>
+    </row>
+    <row r="214" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>当地警署缉拿手（Constabulary Contractor） ──→ C.Y. 42 · 悬赏四类 · 锈钉式黑市提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A215" s="7" t="inlineStr"/>
+    </row>
+    <row r="216" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 警署悬赏与非法提取链</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七悬赏 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="188">
+  <mergeCells count="218">
     <mergeCell ref="A128:C128"/>
     <mergeCell ref="A193:C193"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A233:C233"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A105:C105"/>
@@ -3232,41 +3626,48 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A210:C210"/>
     <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A235:C235"/>
     <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A185:C185"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A194:C194"/>
+    <mergeCell ref="A234:C234"/>
     <mergeCell ref="A181:C181"/>
     <mergeCell ref="A91:C91"/>
     <mergeCell ref="A184:C184"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A156:C156"/>
     <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A155:C155"/>
     <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A220:C220"/>
     <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A229:C229"/>
     <mergeCell ref="A130:C130"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A83:C83"/>
     <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A138:C138"/>
     <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A110:C110"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A196:C196"/>
     <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A205:C205"/>
     <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A133:C133"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="A12:C12"/>
@@ -3278,6 +3679,8 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="A224:C224"/>
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
@@ -3287,20 +3690,23 @@
     <mergeCell ref="A96:C96"/>
     <mergeCell ref="A147:C147"/>
     <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A202:C202"/>
     <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A211:C211"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A186:C186"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A201:C201"/>
     <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A226:C226"/>
     <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A123:C123"/>
     <mergeCell ref="A197:C197"/>
     <mergeCell ref="A146:C146"/>
     <mergeCell ref="A124:C124"/>
@@ -3308,28 +3714,37 @@
     <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A212:C212"/>
     <mergeCell ref="A99:C99"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A221:C221"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A236:C236"/>
     <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A214:C214"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A158:C158"/>
     <mergeCell ref="A101:C101"/>
     <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A223:C223"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
     <mergeCell ref="A204:C204"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A213:C213"/>
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A188:C188"/>
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A215:C215"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A125:C125"/>
     <mergeCell ref="A190:C190"/>
@@ -3350,13 +3765,14 @@
     <mergeCell ref="A98:C98"/>
     <mergeCell ref="A191:C191"/>
     <mergeCell ref="A169:C169"/>
+    <mergeCell ref="A225:C225"/>
     <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A178:C178"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A153:C153"/>
     <mergeCell ref="A162:C162"/>
+    <mergeCell ref="A227:C227"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A137:C137"/>
     <mergeCell ref="A177:C177"/>
@@ -3382,13 +3798,16 @@
     <mergeCell ref="A100:C100"/>
     <mergeCell ref="A140:C140"/>
     <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A231:C231"/>
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A230:C230"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A143:C143"/>
@@ -3396,17 +3815,104 @@
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A166:C166"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A232:C232"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A168:C168"/>
+    <mergeCell ref="A216:C216"/>
     <mergeCell ref="A78:C78"/>
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A218:C218"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 警署悬赏与非法提取链</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七悬赏 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -1,32 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8a. 当地警署" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8c. 酿造帮" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8b. 戒酒教" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="9. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="10. 锈钉" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="11. 锈钉开篇" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -499,7 +496,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20-v17</t>
+          <t>2026-07-20-v13</t>
         </is>
       </c>
     </row>
@@ -648,7 +645,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶生态群 · 二代分伴生/城带/精品/荒原</t>
+          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶车队 · 二代分城带/精品/荒原</t>
         </is>
       </c>
     </row>
@@ -662,7 +659,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 威士忌分级 · 警署悬赏/实质非法提取</t>
+          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 星系放弃 · 威士忌分级 · 荒原赏金猎人</t>
         </is>
       </c>
     </row>
@@ -676,7 +673,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【城带】二代酿民合法采酿 · 琥珀交易所 · 当地警署</t>
+          <t xml:space="preserve">    ├─ 【城带】二代酿民共存 · 体内威士忌换币 · 琥珀交易所</t>
         </is>
       </c>
     </row>
@@ -690,7 +687,7 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【荒原】警署悬赏 · 酿造帮园区 · 黑市出货 · 锈钉行尸走肉循环</t>
+          <t xml:space="preserve">    ├─ 【荒原】猎杀未登记酿民 · 精品酿民高悬赏 · 锈钉行尸走肉循环</t>
         </is>
       </c>
     </row>
@@ -802,47 +799,26 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. 8a. 当地警署</t>
+          <t xml:space="preserve">  13. 9. 叙事入口</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14. 8c. 酿造帮</t>
+          <t xml:space="preserve">  14. 10. 锈钉</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15. 8b. 戒酒教</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  16. 9. 叙事入口</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17. 10. 锈钉</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  18. 11. 锈钉开篇</t>
+          <t xml:space="preserve">  15. 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="42">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
@@ -856,7 +832,6 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A14:C14"/>
@@ -877,12 +852,10 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="B5:C5"/>
@@ -958,7 +931,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 缉拿手（The Hunter） ──→ C.Y. 30– · 警署悬赏承包商 · 实质击晕提取售黑市</t>
+          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
         </is>
       </c>
     </row>
@@ -982,7 +955,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1041,157 +1014,85 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 单辆载具 · 驿道行驶</t>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 铁瓶生态群（Synth-Rig Ecology） ──→ C.Y. 30+ · 多载具演化群落 · 非帮派组织</t>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 一代酿民驻内（Gen-1 Inside） ──→ 锈水发酵 · 地表改造</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ 伴生未觉醒二代（Non-Awakened Gen-2） ──→ 维护调度 · 群落对外接触</t>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
-        </is>
-      </c>
+      <c r="A18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 脱离群落 · 可流入城带或逃亡荒原</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 铁瓶伴生未觉醒（Bottle-Companion） ──→ C.Y. 42 · 维护铁瓶生态群 · 随群落行驶</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 警署悬赏与黑市提取常见目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 酿造帮奴役酿民（Syndicate Bonded） ──→ C.Y. 42 · 园区卖身条款 · 出逃即警署悬赏</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>缉拿手（The Hunter） ──→ C.Y. 30– · 警署登记承包商 · 实质击晕提取售黑市</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 警署悬赏 · 抓捕凶犯与潜逃奴役酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A26:C26"/>
+  <mergeCells count="18">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1220,7 +1121,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1184,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 警署悬赏 · 击晕提取 · 黑市出手</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1219,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1378,33 +1279,26 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 警署悬赏与提取</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 当地警署（Constabulary Post） ──→ 悬赏布告 · 登记缉拿手 · 锈钉接活</t>
+          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 酿造帮园区（Brewing Syndicate） ──→ 高利贷奴役酿造 · 出逃悬赏</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
+          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -1414,7 +1308,6 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1426,7 +1319,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1464,7 +1357,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中推动酿造帮收编脱约者</t>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1367,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏缉拿 · 抓捕凶犯与潜逃奴役酿民</t>
+          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1377,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷园区 · 诓骗酿民卖身 · 非人权组织</t>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
         </is>
       </c>
     </row>
@@ -1494,55 +1387,55 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr"/>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
-        </is>
-      </c>
+      <c r="A17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避警署/酿造帮/戒酒教</t>
-        </is>
-      </c>
+      <c r="A19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者（The Wander） ──→ C.Y. 42 · 警署高危悬赏群体 · 锈钉禁忌</t>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -1570,6 +1463,90 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1581,14 +1558,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 8a. 当地警署</t>
+          <t>《瓶与源》· 10. 锈钉</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏布告与接取 · 取代猎人公会</t>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
         </is>
       </c>
     </row>
@@ -1602,56 +1579,56 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 职能（Functions） ──→ 抓捕凶犯 · 追捕潜逃奴役酿民 · 羁押移交</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 悬赏四类（Bounty Categories） ──→ 酿民/圣火派/凶犯/漂沦者</t>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 酿民类（Brewfolk Bounties） ──→ 出逃奴役酿民 · 脱约精品酿民 · 未登记者</t>
+          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 圣火派（Sacred Fire Bounties） ──→ 戒酒教净化武装 · 格杀勿论</t>
+          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 凶犯类（Felony Bounties） ──→ 谋杀犯 · 劫酵/劫火 · 袭警</t>
+          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 漂沦者（Wander Bounties） ──→ 高危群体 · 活捉隔离/格杀许可</t>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 缉拿手制度（Contractor System） ──→ 登记接活 · 名义抓捕 · 实质黑市提取</t>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 驿站驻点（Outpost Posts） ──→ 城缘Saloon旁 · 锈钉挂牌处</t>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1650,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1689,14 +1666,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 8c. 酿造帮</t>
+          <t>《瓶与源》· 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷奴役集团 · 非人权组织</t>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
         </is>
       </c>
     </row>
@@ -1710,444 +1687,40 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 诱贷（Debt Trap） ──→ 滤材酵苗医疗通行费 · 复利滚欠</t>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 卖身条款（Bondage Contract） ──→ 终身酿造义务 · 出逃全债加速 · 窖芯抵押</t>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 园区囚禁（Compound Yards） ──→ 围栏发酵舱 · 24垦时排班 · 编号管理</t>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 出逃悬赏（Escape Bounties） ──→ 向警署挂潜逃奴役酿民 · 园区出酬金</t>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 与窖行（Vault House Ties） ──→ 精品筛选转卖灰市 · 脱约者洗合同收编</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对外形象（Public Face） ──→ 宣传安置就业 · 实际债务陷阱无退出</t>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 8b. 戒酒教</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交警署/告密 · 不亲手焚杀</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借缉拿手刀</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A16:C16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 9. 叙事入口</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 警署缉拿手 · 击晕提取售黑市 · 精品窖七破局</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>酿造帮园区酿民（Syndicate Bonded Brewfolk） ──→ C.Y. 42 · 卖身条款 · 出逃悬赏 · R-xxx编号</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 警署悬赏目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>当地警署缉拿手（Constabulary Contractor） ──→ C.Y. 42 · 悬赏四类 · 锈钉式黑市提取</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 10. 锈钉</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -2167,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2290,7 +1863,7 @@
     <row r="19" outlineLevel="1" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/猎人镇 · 非法提取委托 · 黑市出货</t>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
         </is>
       </c>
     </row>
@@ -2605,119 +2178,115 @@
     <row r="69" outlineLevel="1" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
         </is>
       </c>
     </row>
     <row r="70" outlineLevel="1" ht="16" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
           <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>▸ 5c. 第三批移民</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
+          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
         </is>
       </c>
     </row>
     <row r="77" outlineLevel="1" ht="16" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
         </is>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="16" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
+          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
         </is>
       </c>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 缉拿手（The Hunter） ──→ C.Y. 30– · 警署悬赏承包商 · 实质击晕提取售黑市</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>▸ 6. 存在体谱系</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="84" outlineLevel="1" ht="16" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
+          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
         </is>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
         </is>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
-        </is>
-      </c>
+      <c r="A86" s="7" t="inlineStr"/>
     </row>
     <row r="87" outlineLevel="1" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
+          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2296,7 @@
     <row r="89" outlineLevel="1" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2306,7 @@
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 单辆载具 · 驿道行驶</t>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
         </is>
       </c>
     </row>
@@ -2751,326 +2320,311 @@
     <row r="93" outlineLevel="1" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 铁瓶生态群（Synth-Rig Ecology） ──→ C.Y. 30+ · 多载具演化群落 · 非帮派组织</t>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="16" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 一代酿民驻内（Gen-1 Inside） ──→ 锈水发酵 · 地表改造</t>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
         </is>
       </c>
     </row>
     <row r="95" outlineLevel="1" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ 伴生未觉醒二代（Non-Awakened Gen-2） ──→ 维护调度 · 群落对外接触</t>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
         </is>
       </c>
     </row>
     <row r="96" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A96" s="7" t="inlineStr"/>
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
+        </is>
+      </c>
     </row>
     <row r="97" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
-        </is>
-      </c>
+      <c r="A97" s="7" t="inlineStr"/>
     </row>
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
+          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7. 威士忌经济</t>
         </is>
       </c>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 脱离群落 · 可流入城带或逃亡荒原</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
         </is>
       </c>
     </row>
     <row r="102" outlineLevel="1" ht="16" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 铁瓶伴生未觉醒（Bottle-Companion） ──→ C.Y. 42 · 维护铁瓶生态群 · 随群落行驶</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="103" outlineLevel="1" ht="16" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 警署悬赏与黑市提取常见目标</t>
+          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 酿造帮奴役酿民（Syndicate Bonded） ──→ C.Y. 42 · 园区卖身条款 · 出逃即警署悬赏</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
         </is>
       </c>
     </row>
     <row r="105" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A105" s="7" t="inlineStr"/>
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
+        </is>
+      </c>
     </row>
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>缉拿手（The Hunter） ──→ C.Y. 30– · 警署登记承包商 · 实质击晕提取售黑市</t>
+          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
         </is>
       </c>
     </row>
     <row r="107" outlineLevel="1" ht="16" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
         </is>
       </c>
     </row>
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 警署悬赏 · 抓捕凶犯与潜逃奴役酿民</t>
+          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
         </is>
       </c>
     </row>
     <row r="109" outlineLevel="1" ht="16" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7. 威士忌经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7b. 城带与荒原</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
+          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
         </is>
       </c>
     </row>
     <row r="115" outlineLevel="1" ht="16" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="116" outlineLevel="1" ht="16" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
+          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
         </is>
       </c>
     </row>
     <row r="117" outlineLevel="1" ht="16" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
+          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
+          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
         </is>
       </c>
     </row>
     <row r="119" outlineLevel="1" ht="16" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
+          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
         </is>
       </c>
     </row>
     <row r="120" outlineLevel="1" ht="16" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 警署悬赏 · 击晕提取 · 黑市出手</t>
+          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
         </is>
       </c>
     </row>
     <row r="122" outlineLevel="1" ht="16" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
+          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>▸ 7b. 城带与荒原</t>
+          <t>▸ 8. 势力格局</t>
         </is>
       </c>
     </row>
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
+          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="126" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A126" s="7" t="inlineStr"/>
     </row>
     <row r="127" outlineLevel="1" ht="16" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
+          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
         </is>
       </c>
     </row>
     <row r="128" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
-        </is>
-      </c>
+      <c r="A128" s="7" t="inlineStr"/>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
         </is>
       </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
-        </is>
-      </c>
+      <c r="A130" s="7" t="inlineStr"/>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 警署悬赏与提取</t>
+          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
         </is>
       </c>
     </row>
     <row r="132" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ├─ 当地警署（Constabulary Post） ──→ 悬赏布告 · 登记缉拿手 · 锈钉接活</t>
-        </is>
-      </c>
+      <c r="A132" s="7" t="inlineStr"/>
     </row>
     <row r="133" outlineLevel="1" ht="16" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 酿造帮园区（Brewing Syndicate） ──→ 高利贷奴役酿造 · 出逃悬赏</t>
+          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
         </is>
       </c>
     </row>
     <row r="134" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8. 势力格局</t>
+      <c r="A134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="137" outlineLevel="1" ht="16" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
+          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
         </is>
       </c>
     </row>
     <row r="138" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A138" s="7" t="inlineStr"/>
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
+        </is>
+      </c>
     </row>
     <row r="139" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
-        </is>
-      </c>
+      <c r="A139" s="7" t="inlineStr"/>
     </row>
     <row r="140" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A140" s="7" t="inlineStr"/>
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
+        </is>
+      </c>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中推动酿造帮收编脱约者</t>
-        </is>
-      </c>
+      <c r="A141" s="7" t="inlineStr"/>
     </row>
     <row r="142" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A142" s="7" t="inlineStr"/>
-    </row>
-    <row r="143" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏缉拿 · 抓捕凶犯与潜逃奴役酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A144" s="7" t="inlineStr"/>
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
+        </is>
+      </c>
     </row>
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷园区 · 诓骗酿民卖身 · 非人权组织</t>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
         </is>
       </c>
     </row>
@@ -3080,7 +2634,7 @@
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
         </is>
       </c>
     </row>
@@ -3090,7 +2644,7 @@
     <row r="149" outlineLevel="1" ht="16" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
         </is>
       </c>
     </row>
@@ -3100,7 +2654,7 @@
     <row r="151" outlineLevel="1" ht="16" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
+          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
         </is>
       </c>
     </row>
@@ -3110,560 +2664,180 @@
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避警署/酿造帮/戒酒教</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A154" s="7" t="inlineStr"/>
-    </row>
-    <row r="155" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者（The Wander） ──→ C.Y. 42 · 警署高危悬赏群体 · 锈钉禁忌</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8a. 当地警署</t>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏布告与接取 · 取代猎人公会</t>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
         </is>
       </c>
     </row>
     <row r="159" outlineLevel="1" ht="16" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
         </is>
       </c>
     </row>
     <row r="160" outlineLevel="1" ht="16" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 职能（Functions） ──→ 抓捕凶犯 · 追捕潜逃奴役酿民 · 羁押移交</t>
+          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
         </is>
       </c>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 悬赏四类（Bounty Categories） ──→ 酿民/圣火派/凶犯/漂沦者</t>
+          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 酿民类（Brewfolk Bounties） ──→ 出逃奴役酿民 · 脱约精品酿民 · 未登记者</t>
+          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
         </is>
       </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 圣火派（Sacred Fire Bounties） ──→ 戒酒教净化武装 · 格杀勿论</t>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
         </is>
       </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 凶犯类（Felony Bounties） ──→ 谋杀犯 · 劫酵/劫火 · 袭警</t>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 漂沦者（Wander Bounties） ──→ 高危群体 · 活捉隔离/格杀许可</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 缉拿手制度（Contractor System） ──→ 登记接活 · 名义抓捕 · 实质黑市提取</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 驿站驻点（Outpost Posts） ──→ 城缘Saloon旁 · 锈钉挂牌处</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8c. 酿造帮</t>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="170" outlineLevel="1" ht="16" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷奴役集团 · 非人权组织</t>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
         </is>
       </c>
     </row>
     <row r="171" outlineLevel="1" ht="16" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
         </is>
       </c>
     </row>
     <row r="172" outlineLevel="1" ht="16" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 诱贷（Debt Trap） ──→ 滤材酵苗医疗通行费 · 复利滚欠</t>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 卖身条款（Bondage Contract） ──→ 终身酿造义务 · 出逃全债加速 · 窖芯抵押</t>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
         </is>
       </c>
     </row>
     <row r="174" outlineLevel="1" ht="16" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 园区囚禁（Compound Yards） ──→ 围栏发酵舱 · 24垦时排班 · 编号管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 出逃悬赏（Escape Bounties） ──→ 向警署挂潜逃奴役酿民 · 园区出酬金</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A176" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 与窖行（Vault House Ties） ──→ 精品筛选转卖灰市 · 脱约者洗合同收编</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A177" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对外形象（Public Face） ──→ 宣传安置就业 · 实际债务陷阱无退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>▸ 8b. 戒酒教</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A181" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A184" s="7" t="inlineStr"/>
-    </row>
-    <row r="185" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
-        <is>
-          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A188" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交警署/告密 · 不亲手焚杀</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A190" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借缉拿手刀</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A191" s="7" t="inlineStr"/>
-    </row>
-    <row r="192" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A192" s="7" t="inlineStr">
-        <is>
-          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A195" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A196" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A200" s="7" t="inlineStr">
-        <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 警署缉拿手 · 击晕提取售黑市 · 精品窖七破局</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A201" s="7" t="inlineStr"/>
-    </row>
-    <row r="202" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A202" s="7" t="inlineStr">
-        <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A203" s="7" t="inlineStr"/>
-    </row>
-    <row r="204" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A204" s="7" t="inlineStr">
-        <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A205" s="7" t="inlineStr"/>
-    </row>
-    <row r="206" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A206" s="7" t="inlineStr">
-        <is>
-          <t>酿造帮园区酿民（Syndicate Bonded Brewfolk） ──→ C.Y. 42 · 卖身条款 · 出逃悬赏 · R-xxx编号</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A207" s="7" t="inlineStr"/>
-    </row>
-    <row r="208" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A208" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A209" s="7" t="inlineStr"/>
-    </row>
-    <row r="210" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A210" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A211" s="7" t="inlineStr"/>
-    </row>
-    <row r="212" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A212" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 警署悬赏目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A213" s="7" t="inlineStr"/>
-    </row>
-    <row r="214" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A214" s="7" t="inlineStr">
-        <is>
-          <t>当地警署缉拿手（Constabulary Contractor） ──→ C.Y. 42 · 悬赏四类 · 锈钉式黑市提取</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A215" s="7" t="inlineStr"/>
-    </row>
-    <row r="216" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A216" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A219" s="7" t="inlineStr">
-        <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A220" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A221" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A222" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A223" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A224" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A225" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A226" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A227" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A230" s="7" t="inlineStr">
-        <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 警署悬赏与非法提取链</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A231" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A232" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七悬赏 ×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A233" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A234" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A235" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A236" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="218">
+  <mergeCells count="159">
     <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A193:C193"/>
-    <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A233:C233"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A192:C192"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A179:C179"/>
-    <mergeCell ref="A235:C235"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A185:C185"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="A234:C234"/>
-    <mergeCell ref="A181:C181"/>
     <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A184:C184"/>
     <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A156:C156"/>
     <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A155:C155"/>
     <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A220:C220"/>
     <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A229:C229"/>
     <mergeCell ref="A130:C130"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A83:C83"/>
     <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
-    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A138:C138"/>
     <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A110:C110"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A196:C196"/>
     <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
@@ -3674,108 +2848,78 @@
     <mergeCell ref="A95:C95"/>
     <mergeCell ref="A104:C104"/>
     <mergeCell ref="A160:C160"/>
-    <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A219:C219"/>
-    <mergeCell ref="A224:C224"/>
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A96:C96"/>
     <mergeCell ref="A147:C147"/>
     <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A202:C202"/>
     <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A211:C211"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A186:C186"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A201:C201"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A226:C226"/>
+    <mergeCell ref="A82:C82"/>
     <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A197:C197"/>
     <mergeCell ref="A146:C146"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A187:C187"/>
-    <mergeCell ref="A212:C212"/>
-    <mergeCell ref="A99:C99"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A221:C221"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A236:C236"/>
     <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A214:C214"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A158:C158"/>
     <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A223:C223"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A213:C213"/>
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A188:C188"/>
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A135:C135"/>
     <mergeCell ref="A150:C150"/>
-    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A215:C215"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A190:C190"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A199:C199"/>
     <mergeCell ref="A152:C152"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="A167:C167"/>
-    <mergeCell ref="A176:C176"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A182:C182"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A191:C191"/>
     <mergeCell ref="A169:C169"/>
-    <mergeCell ref="A225:C225"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A153:C153"/>
     <mergeCell ref="A162:C162"/>
-    <mergeCell ref="A227:C227"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A177:C177"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A164:C164"/>
@@ -3784,12 +2928,9 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A145:C145"/>
     <mergeCell ref="A139:C139"/>
-    <mergeCell ref="A154:C154"/>
     <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A195:C195"/>
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A203:C203"/>
     <mergeCell ref="A85:C85"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A8:C8"/>
@@ -3800,119 +2941,27 @@
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A231:C231"/>
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A230:C230"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A143:C143"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A166:C166"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A232:C232"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A216:C216"/>
+    <mergeCell ref="A168:C168"/>
     <mergeCell ref="A78:C78"/>
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A218:C218"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 11. 锈钉开篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 警署悬赏与非法提取链</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七悬赏 ×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4058,7 +3107,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/猎人镇 · 非法提取委托 · 黑市出货</t>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
         </is>
       </c>
     </row>
@@ -4459,7 +3508,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -4519,35 +3568,20 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
           <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -4555,7 +3589,6 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -1,29 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="9. 叙事入口" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="10. 锈钉" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="11. 锈钉开篇" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8a. 当地警署" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8c. 酿造帮" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8b. 戒酒教" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -496,7 +499,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20-v13</t>
+          <t>2026-07-20-v17</t>
         </is>
       </c>
     </row>
@@ -645,7 +648,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶车队 · 二代分城带/精品/荒原</t>
+          <t xml:space="preserve">    ├─ 【第二批】Android一代酿民 · 铁瓶生态群 · 二代分伴生/城带/精品/荒原</t>
         </is>
       </c>
     </row>
@@ -659,7 +662,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 星系放弃 · 威士忌分级 · 荒原赏金猎人</t>
+          <t xml:space="preserve">    ├─ 【第三批】囚犯放逐 · 威士忌分级 · 警署悬赏/实质非法提取</t>
         </is>
       </c>
     </row>
@@ -673,7 +676,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【城带】二代酿民共存 · 体内威士忌换币 · 琥珀交易所</t>
+          <t xml:space="preserve">    ├─ 【城带】二代酿民合法采酿 · 琥珀交易所 · 当地警署</t>
         </is>
       </c>
     </row>
@@ -687,7 +690,7 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 【荒原】猎杀未登记酿民 · 精品酿民高悬赏 · 锈钉行尸走肉循环</t>
+          <t xml:space="preserve">    ├─ 【荒原】警署悬赏 · 酿造帮园区 · 黑市出货 · 锈钉行尸走肉循环</t>
         </is>
       </c>
     </row>
@@ -799,26 +802,47 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. 9. 叙事入口</t>
+          <t xml:space="preserve">  13. 8a. 当地警署</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14. 10. 锈钉</t>
+          <t xml:space="preserve">  14. 8c. 酿造帮</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15. 11. 锈钉开篇</t>
+          <t xml:space="preserve">  15. 8b. 戒酒教</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  16. 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  17. 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  18. 11. 锈钉开篇</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="45">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:C7"/>
@@ -832,6 +856,7 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A14:C14"/>
@@ -852,10 +877,12 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="B5:C5"/>
@@ -931,7 +958,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
+          <t xml:space="preserve">    └─ 缉拿手（The Hunter） ──→ C.Y. 30– · 警署悬赏承包商 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
@@ -955,7 +982,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1014,85 +1041,157 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 单辆载具 · 驿道行驶</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+          <t xml:space="preserve">    └─ 铁瓶生态群（Synth-Rig Ecology） ──→ C.Y. 30+ · 多载具演化群落 · 非帮派组织</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">        ├─ 一代酿民驻内（Gen-1 Inside） ──→ 锈水发酵 · 地表改造</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+          <t xml:space="preserve">        └─ 伴生未觉醒二代（Non-Awakened Gen-2） ──→ 维护调度 · 群落对外接触</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
-        </is>
-      </c>
+      <c r="A15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 脱离群落 · 可流入城带或逃亡荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 铁瓶伴生未觉醒（Bottle-Companion） ──→ C.Y. 42 · 维护铁瓶生态群 · 随群落行驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 警署悬赏与黑市提取常见目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 酿造帮奴役酿民（Syndicate Bonded） ──→ C.Y. 42 · 园区卖身条款 · 出逃即警署悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>缉拿手（The Hunter） ──→ C.Y. 30– · 警署登记承包商 · 实质击晕提取售黑市</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 警署悬赏 · 抓捕凶犯与潜逃奴役酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="27">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1121,7 +1220,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1283,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 警署悬赏 · 击晕提取 · 黑市出手</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1318,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1279,26 +1378,33 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 警署悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
+          <t xml:space="preserve">        ├─ 当地警署（Constabulary Post） ──→ 悬赏布告 · 登记缉拿手 · 锈钉接活</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
+          <t xml:space="preserve">        ├─ 酿造帮园区（Brewing Syndicate） ──→ 高利贷奴役酿造 · 出逃悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -1308,6 +1414,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1319,7 +1426,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1357,7 +1464,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中推动酿造帮收编脱约者</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1474,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏缉拿 · 抓捕凶犯与潜逃奴役酿民</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1484,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷园区 · 诓骗酿民卖身 · 非人权组织</t>
         </is>
       </c>
     </row>
@@ -1387,55 +1494,55 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
+          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
+      <c r="A14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
-        </is>
-      </c>
+      <c r="A16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
-        </is>
-      </c>
+      <c r="A18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr"/>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避警署/酿造帮/戒酒教</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
+      <c r="A20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者（The Wander） ──→ C.Y. 42 · 警署高危悬赏群体 · 锈钉禁忌</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -1463,90 +1570,6 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 9. 叙事入口</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1558,14 +1581,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 10. 锈钉</t>
+          <t>《瓶与源》· 8a. 当地警署</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏布告与接取 · 取代猎人公会</t>
         </is>
       </c>
     </row>
@@ -1579,56 +1602,56 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
+          <t xml:space="preserve">    ├─ 职能（Functions） ──→ 抓捕凶犯 · 追捕潜逃奴役酿民 · 羁押移交</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+          <t xml:space="preserve">    ├─ 悬赏四类（Bounty Categories） ──→ 酿民/圣火派/凶犯/漂沦者</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
+          <t xml:space="preserve">    │       ├─ 酿民类（Brewfolk Bounties） ──→ 出逃奴役酿民 · 脱约精品酿民 · 未登记者</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
+          <t xml:space="preserve">    │       ├─ 圣火派（Sacred Fire Bounties） ──→ 戒酒教净化武装 · 格杀勿论</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
+          <t xml:space="preserve">    │       ├─ 凶犯类（Felony Bounties） ──→ 谋杀犯 · 劫酵/劫火 · 袭警</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+          <t xml:space="preserve">    │       └─ 漂沦者（Wander Bounties） ──→ 高危群体 · 活捉隔离/格杀许可</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t xml:space="preserve">    ├─ 缉拿手制度（Contractor System） ──→ 登记接活 · 名义抓捕 · 实质黑市提取</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
+          <t xml:space="preserve">    └─ 驿站驻点（Outpost Posts） ──→ 城缘Saloon旁 · 锈钉挂牌处</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1673,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1666,14 +1689,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 11. 锈钉开篇</t>
+          <t>《瓶与源》· 8c. 酿造帮</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷奴役集团 · 非人权组织</t>
         </is>
       </c>
     </row>
@@ -1687,40 +1710,444 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
+          <t xml:space="preserve">    ├─ 诱贷（Debt Trap） ──→ 滤材酵苗医疗通行费 · 复利滚欠</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
+          <t xml:space="preserve">    ├─ 卖身条款（Bondage Contract） ──→ 终身酿造义务 · 出逃全债加速 · 窖芯抵押</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
+          <t xml:space="preserve">    ├─ 园区囚禁（Compound Yards） ──→ 围栏发酵舱 · 24垦时排班 · 编号管理</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
+          <t xml:space="preserve">    ├─ 出逃悬赏（Escape Bounties） ──→ 向警署挂潜逃奴役酿民 · 园区出酬金</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
+          <t xml:space="preserve">    ├─ 与窖行（Vault House Ties） ──→ 精品筛选转卖灰市 · 脱约者洗合同收编</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对外形象（Public Face） ──→ 宣传安置就业 · 实际债务陷阱无退出</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 8b. 戒酒教</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交警署/告密 · 不亲手焚杀</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借缉拿手刀</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 警署缉拿手 · 击晕提取售黑市 · 精品窖七破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>酿造帮园区酿民（Syndicate Bonded Brewfolk） ──→ C.Y. 42 · 卖身条款 · 出逃悬赏 · R-xxx编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 警署悬赏目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>当地警署缉拿手（Constabulary Contractor） ──→ C.Y. 42 · 悬赏四类 · 锈钉式黑市提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -1740,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -1863,7 +2290,7 @@
     <row r="19" outlineLevel="1" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/猎人镇 · 非法提取委托 · 黑市出货</t>
         </is>
       </c>
     </row>
@@ -2178,115 +2605,119 @@
     <row r="69" outlineLevel="1" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
         </is>
       </c>
     </row>
     <row r="70" outlineLevel="1" ht="16" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>▸ 5c. 第三批移民</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="75" outlineLevel="1" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
+          <t>第三批移民（Wave 3 Prisoners） ──→ C.Y. 25–42 · 自愿协议囚犯放逐 · 星系放弃</t>
         </is>
       </c>
     </row>
     <row r="76" outlineLevel="1" ht="16" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="77" outlineLevel="1" ht="16" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+          <t xml:space="preserve">    ├─ 自愿协议（Voluntary Pact） ──→ C.Y. 25 · 囚犯放逐 · 抵消旧日罪籍</t>
         </is>
       </c>
     </row>
     <row r="78" outlineLevel="1" ht="16" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
+          <t xml:space="preserve">    ├─ 势力撤离（Powers Withdrawn） ──→ C.Y. 28 · 水资源无解 · 无母星回流</t>
         </is>
       </c>
     </row>
     <row r="79" outlineLevel="1" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 赏金猎人（The Hunter） ──→ C.Y. 30– · 猎杀酿民取酵 · 威士忌经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+          <t xml:space="preserve">    ├─ 威士忌发现（Whiskey Discovery） ──→ C.Y. 28– · 酿民体内酵母发酵锈水2–4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 酵母衰亡（Yeast Decay） ──→ 离体活性衰减 · 须反复从酿民提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 缉拿手（The Hunter） ──→ C.Y. 30– · 警署悬赏承包商 · 实质击晕提取售黑市</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>▸ 6. 存在体谱系</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="84" outlineLevel="1" ht="16" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
+          <t>漂沦者（The Wander） ──→ C.Y. 8+ · 首批胃植入人类畸变 · 生物磁场</t>
         </is>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A86" s="7" t="inlineStr"/>
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 精神畸变（Mental Distortion） ──→ 0.05%毒素长期累积</t>
+        </is>
+      </c>
     </row>
     <row r="87" outlineLevel="1" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
+          <t xml:space="preserve">    └─ 磁场异常（Bio-Magnetic Field） ──→ 干扰猎队导航 · 尘暴先兆</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2727,7 @@
     <row r="89" outlineLevel="1" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 移动改造酿运载具 · 驿道行驶</t>
+          <t>一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8– · Android · 驻留铁瓶 · 多数无完整自主意识</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2737,7 @@
     <row r="91" outlineLevel="1" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+          <t>铁瓶 Synth-Rig ──→ C.Y. 10– · 单辆载具 · 驿道行驶</t>
         </is>
       </c>
     </row>
@@ -2320,311 +2751,326 @@
     <row r="93" outlineLevel="1" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+          <t xml:space="preserve">    └─ 铁瓶生态群（Synth-Rig Ecology） ──→ C.Y. 30+ · 多载具演化群落 · 非帮派组织</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="16" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
+          <t xml:space="preserve">        ├─ 一代酿民驻内（Gen-1 Inside） ──→ 锈水发酵 · 地表改造</t>
         </is>
       </c>
     </row>
     <row r="95" outlineLevel="1" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 猎人公会悬赏对象</t>
+          <t xml:space="preserve">        └─ 伴生未觉醒二代（Non-Awakened Gen-2） ──→ 维护调度 · 群落对外接触</t>
         </is>
       </c>
     </row>
     <row r="96" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 可流入城带或逃亡荒原</t>
-        </is>
-      </c>
+      <c r="A96" s="7" t="inlineStr"/>
     </row>
     <row r="97" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A97" s="7" t="inlineStr"/>
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生Android · 分城带/精品/荒原</t>
+        </is>
+      </c>
     </row>
     <row r="98" outlineLevel="1" ht="16" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人（The Hunter） ──→ C.Y. 30– · 荒原猎杀 · 非城带执法 · 锈钉所属</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7. 威士忌经济</t>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 城带登记酿民（Registered Metro） ──→ C.Y. 42 · 与人类共存 · 定期采酿换币 · 城酿署保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 精品酿民 Vintage（Vintage Brewfolk） ──→ C.Y. 42 · 窖酿品质 · 窖行签约 · 脱约成高价值目标</t>
         </is>
       </c>
     </row>
     <row r="101" outlineLevel="1" ht="16" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带交易 · 荒原猎杀 · 双态经济</t>
+          <t xml:space="preserve">    ├─ 觉醒迁出铁瓶（Awakening Exodus） ──→ C.Y. 30+ · 脱离群落 · 可流入城带或逃亡荒原</t>
         </is>
       </c>
     </row>
     <row r="102" outlineLevel="1" ht="16" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 铁瓶伴生未觉醒（Bottle-Companion） ──→ C.Y. 42 · 维护铁瓶生态群 · 随群落行驶</t>
         </is>
       </c>
     </row>
     <row r="103" outlineLevel="1" ht="16" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
+          <t xml:space="preserve">    ├─ 荒原逃亡/未登记（Wasteland Fugitive） ──→ C.Y. 42 · 警署悬赏与黑市提取常见目标</t>
         </is>
       </c>
     </row>
     <row r="104" outlineLevel="1" ht="16" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
+          <t xml:space="preserve">    └─ 酿造帮奴役酿民（Syndicate Bonded） ──→ C.Y. 42 · 园区卖身条款 · 出逃即警署悬赏</t>
         </is>
       </c>
     </row>
     <row r="105" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
-        </is>
-      </c>
+      <c r="A105" s="7" t="inlineStr"/>
     </row>
     <row r="106" outlineLevel="1" ht="16" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
+          <t>缉拿手（The Hunter） ──→ C.Y. 30– · 警署登记承包商 · 实质击晕提取售黑市</t>
         </is>
       </c>
     </row>
     <row r="107" outlineLevel="1" ht="16" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="108" outlineLevel="1" ht="16" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
+          <t xml:space="preserve">    ├─ 名义职能（Cover Role） ──→ 警署悬赏 · 抓捕凶犯与潜逃奴役酿民</t>
         </is>
       </c>
     </row>
     <row r="109" outlineLevel="1" ht="16" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Hunt） ──→ C.Y. 42 · 猎杀未登记酿民 · 精品脱约暗中悬赏</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>▸ 7b. 城带与荒原</t>
+          <t xml:space="preserve">    └─ 实质产业链（Black Market Chain） ──→ 击晕→非法体内提取→黑市兑售</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>▸ 7. 威士忌经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>威士忌经济（Whiskey Economy） ──→ C.Y. 28– · 城带合法采酿 · 荒原非法提取黑市</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="114" outlineLevel="1" ht="16" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
+          <t xml:space="preserve">    ├─ 原料（Input） ──→ 锈水（化学毒+嗜盐菌）</t>
         </is>
       </c>
     </row>
     <row r="115" outlineLevel="1" ht="16" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    ├─ 转化（Fermentation） ──→ 酿民体内生态酵母 → 2–4%威士忌</t>
         </is>
       </c>
     </row>
     <row r="116" outlineLevel="1" ht="16" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
+          <t xml:space="preserve">    ├─ 品质分级（Quality Tiers） ──→ C.Y. 42 · 劣酿Row/常酿Standard/窖酿Vintage</t>
         </is>
       </c>
     </row>
     <row r="117" outlineLevel="1" ht="16" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
+          <t xml:space="preserve">    │       ├─ 劣酿 Row（Row Grade） ──→ 杂味重 · 荒原批量 · 猎人提取兑售</t>
         </is>
       </c>
     </row>
     <row r="118" outlineLevel="1" ht="16" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
+          <t xml:space="preserve">    │       ├─ 常酿 Standard（Standard Grade） ──→ 城带日常流通 · 登记酿民定期供酿</t>
         </is>
       </c>
     </row>
     <row r="119" outlineLevel="1" ht="16" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+          <t xml:space="preserve">    │       └─ 窖酿 Vintage（Vintage Grade） ──→ 精品酿民专属 · 溢价极高</t>
         </is>
       </c>
     </row>
     <row r="120" outlineLevel="1" ht="16" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 悬赏与提取</t>
+          <t xml:space="preserve">    ├─ 城带模式（Metro Trade） ──→ C.Y. 42 · 登记采酿换琥珀币 · 琥珀交易所挂牌</t>
         </is>
       </c>
     </row>
     <row r="121" outlineLevel="1" ht="16" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ├─ 赏金猎人公会（Hunters Guild） ──→ 锈钉活动区 · 猎杀未登记/逃亡酿民</t>
+          <t xml:space="preserve">    ├─ 荒原模式（Wasteland Extraction） ──→ C.Y. 42 · 警署悬赏 · 击晕提取 · 黑市出手</t>
         </is>
       </c>
     </row>
     <row r="122" outlineLevel="1" ht="16" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        └─ Saloon/猎人镇（Saloon Towns） ──→ 劣酿 · 悬赏 · 情报 · 行尸走肉式循环</t>
+          <t xml:space="preserve">    └─ 裂缝（Fracture） ──→ C.Y. 37+ · 城带法规保护 vs 荒原无法无天</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>▸ 8. 势力格局</t>
+          <t>▸ 7b. 城带与荒原</t>
         </is>
       </c>
     </row>
     <row r="125" outlineLevel="1" ht="16" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
+          <t>城带与荒原（Metro Rim vs Wastes） ──→ C.Y. 42 · 赭锈带社会地理双态</t>
         </is>
       </c>
     </row>
     <row r="126" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A126" s="7" t="inlineStr"/>
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
     </row>
     <row r="127" outlineLevel="1" ht="16" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
+          <t xml:space="preserve">    ├─ 城带 Metro Rim ──→ 人类与二代酿民共存 · 非默认对立</t>
         </is>
       </c>
     </row>
     <row r="128" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A128" s="7" t="inlineStr"/>
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       ├─ 城酿署（Metro Brew Registry） ──→ 登记 · 采酿配额 · 纠纷仲裁 · 禁猎保护</t>
+        </is>
+      </c>
     </row>
     <row r="129" outlineLevel="1" ht="16" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中悬赏回收脱约者</t>
+          <t xml:space="preserve">    │       ├─ 琥珀交易所（Amber Exchange） ──→ 威士忌品质挂牌 · 货币结算</t>
         </is>
       </c>
     </row>
     <row r="130" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A130" s="7" t="inlineStr"/>
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 精品窖行（Vintage Vault Houses） ──→ 竞签精品酿民 · 窖酿拍卖 · 暗中回收脱约者</t>
+        </is>
+      </c>
     </row>
     <row r="131" outlineLevel="1" ht="16" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>铁瓶帮（Synth-Rig Cartel） ──→ C.Y. 42 · 控制车队与一代酿民 · 威士忌换弹药</t>
+          <t xml:space="preserve">    └─ 荒原 The Wastes ──→ 城缘至铁瓶驿道 · 警署悬赏与提取</t>
         </is>
       </c>
     </row>
     <row r="132" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A132" s="7" t="inlineStr"/>
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ├─ 当地警署（Constabulary Post） ──→ 悬赏布告 · 登记缉拿手 · 锈钉接活</t>
+        </is>
+      </c>
     </row>
     <row r="133" outlineLevel="1" ht="16" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>赏金猎人公会（Hunters Guild） ──→ C.Y. 42 · 荒原猎杀 · 锈钉隶属</t>
+          <t xml:space="preserve">        ├─ 酿造帮园区（Brewing Syndicate） ──→ 高利贷奴役酿造 · 出逃悬赏</t>
         </is>
       </c>
     </row>
     <row r="134" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A134" s="7" t="inlineStr"/>
-    </row>
-    <row r="135" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 收割派/纯净派</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        └─ Saloon黑市链（Saloon Black Market） ──→ 回收槽收酵 · 威士忌出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8. 势力格局</t>
         </is>
       </c>
     </row>
     <row r="137" outlineLevel="1" ht="16" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 收割派（Harvest Faction） ──→ C.Y. 42 · 取酵不取命 · 灵魂可赎</t>
+          <t>城酿署（Metro Brew Registry） ──→ C.Y. 42 · 酿民登记 · 采酿配额 · 禁猎保护</t>
         </is>
       </c>
     </row>
     <row r="138" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 纯净派（Purity Faction） ──→ C.Y. 42 · 威士忌即罪恶 · 焚毁铁瓶酿民</t>
-        </is>
-      </c>
+      <c r="A138" s="7" t="inlineStr"/>
     </row>
     <row r="139" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A139" s="7" t="inlineStr"/>
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>琥珀交易所（Amber Exchange） ──→ C.Y. 42 · 威士忌分级定价 · 货币</t>
+        </is>
+      </c>
     </row>
     <row r="140" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避猎人</t>
-        </is>
-      </c>
+      <c r="A140" s="7" t="inlineStr"/>
     </row>
     <row r="141" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A141" s="7" t="inlineStr"/>
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>精品窖行（Vintage Vault Houses） ──→ C.Y. 42 · 签约精品酿民 · 暗中推动酿造帮收编脱约者</t>
+        </is>
+      </c>
     </row>
     <row r="142" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>酒镇 Saloon ──→ C.Y. 42 · 中立 · 劣酿 · 悬赏 · 情报</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>▸ 9. 叙事入口</t>
-        </is>
-      </c>
+      <c r="A142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏缉拿 · 抓捕凶犯与潜逃奴役酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A144" s="7" t="inlineStr"/>
     </row>
     <row r="145" outlineLevel="1" ht="16" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 主线 · 行尸走肉接单 · 精品酿民破局</t>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷园区 · 诓骗酿民卖身 · 非人权组织</t>
         </is>
       </c>
     </row>
@@ -2634,7 +3080,7 @@
     <row r="147" outlineLevel="1" ht="16" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+          <t>铁瓶（生态群）（Synth-Rig Ecology） ──→ C.Y. 42 · 演化群落 · 一代酿民驻内 · 伴生未觉醒二代酿民</t>
         </is>
       </c>
     </row>
@@ -2644,7 +3090,7 @@
     <row r="149" outlineLevel="1" ht="16" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+          <t>Saloon黑市链（Saloon Black Market） ──→ C.Y. 42 · 回收槽收酵 · 非法威士忌出手</t>
         </is>
       </c>
     </row>
@@ -2654,7 +3100,7 @@
     <row r="151" outlineLevel="1" ht="16" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>铁瓶驻留一代酿民（Gen-1 in Synth-Rig） ──→ C.Y. 42 · 无觉醒但记录二代同伴逃亡</t>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 与酿民敌对 · 完全摒弃/圣火 · 见8b</t>
         </is>
       </c>
     </row>
@@ -2664,180 +3110,560 @@
     <row r="153" outlineLevel="1" ht="16" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>▸ 10. 锈钉</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 城缘荒原猎人 · 主线视角</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
+          <t>逃亡酿民网络（Fugitive Brewfolk） ──→ C.Y. 42 · 未登记者互助 · 躲避警署/酿造帮/戒酒教</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者（The Wander） ──→ C.Y. 42 · 警署高危悬赏群体 · 锈钉禁忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8a. 当地警署</t>
         </is>
       </c>
     </row>
     <row r="158" outlineLevel="1" ht="16" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 漫无目的接单 · 不挑单不问名</t>
+          <t>当地警署（Constabulary Post） ──→ C.Y. 42 · 悬赏布告与接取 · 取代猎人公会</t>
         </is>
       </c>
     </row>
     <row r="159" outlineLevel="1" ht="16" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道 · 不进城酿署体系</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="160" outlineLevel="1" ht="16" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 日常循环（Routine Loop） ──→ 接榜→追迹→提取→交酵→换劣酿糊口→重复</t>
+          <t xml:space="preserve">    ├─ 职能（Functions） ──→ 抓捕凶犯 · 追捕潜逃奴役酿民 · 羁押移交</t>
         </is>
       </c>
     </row>
     <row r="161" outlineLevel="1" ht="16" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对酿民（On Brewfolk） ──→ 开篇 · 工具化 · 无道德波澜</t>
+          <t xml:space="preserve">    ├─ 悬赏四类（Bounty Categories） ──→ 酿民/圣火派/凶犯/漂沦者</t>
         </is>
       </c>
     </row>
     <row r="162" outlineLevel="1" ht="16" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对城带（On Metro） ──→ 知共存与挂牌价 · 与他无关</t>
+          <t xml:space="preserve">    │       ├─ 酿民类（Brewfolk Bounties） ──→ 出逃奴役酿民 · 脱约精品酿民 · 未登记者</t>
         </is>
       </c>
     </row>
     <row r="163" outlineLevel="1" ht="16" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 绰号来源</t>
+          <t xml:space="preserve">    │       ├─ 圣火派（Sacred Fire Bounties） ──→ 戒酒教净化武装 · 格杀勿论</t>
         </is>
       </c>
     </row>
     <row r="164" outlineLevel="1" ht="16" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不猎漂沦者</t>
+          <t xml:space="preserve">    │       ├─ 凶犯类（Felony Bounties） ──→ 谋杀犯 · 劫酵/劫火 · 袭警</t>
         </is>
       </c>
     </row>
     <row r="165" outlineLevel="1" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 精品酿民窖七 · 城带价码逼他算账 · 扳机上停顿</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>▸ 11. 锈钉开篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 荒原开篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" outlineLevel="1" ht="16" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
+          <t xml:space="preserve">    │       └─ 漂沦者（Wander Bounties） ──→ 高危群体 · 活捉隔离/格杀许可</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 缉拿手制度（Contractor System） ──→ 登记接活 · 名义抓捕 · 实质黑市提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 驿站驻点（Outpost Posts） ──→ 城缘Saloon旁 · 锈钉挂牌处</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8c. 酿造帮</t>
         </is>
       </c>
     </row>
     <row r="170" outlineLevel="1" ht="16" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 例行扫单 · 红标精品酿民窖七 · 酬金五倍</t>
+          <t>酿造帮（Brewing Syndicate） ──→ C.Y. 42 · 高利贷奴役集团 · 非人权组织</t>
         </is>
       </c>
     </row>
     <row r="171" outlineLevel="1" ht="16" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 机械追迹 · 目标懂荒原 · 把自己当窖养</t>
+          <t xml:space="preserve">    │</t>
         </is>
       </c>
     </row>
     <row r="172" outlineLevel="1" ht="16" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 活捉双份 · 断章未扣扳机</t>
+          <t xml:space="preserve">    ├─ 诱贷（Debt Trap） ──→ 滤材酵苗医疗通行费 · 复利滚欠</t>
         </is>
       </c>
     </row>
     <row r="173" outlineLevel="1" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 脱约 · 用交易语言不煽情</t>
+          <t xml:space="preserve">    ├─ 卖身条款（Bondage Contract） ──→ 终身酿造义务 · 出逃全债加速 · 窖芯抵押</t>
         </is>
       </c>
     </row>
     <row r="174" outlineLevel="1" ht="16" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 酒馆电视琥珀行情 · 两套价码表碰撞</t>
+          <t xml:space="preserve">    ├─ 园区囚禁（Compound Yards） ──→ 围栏发酵舱 · 24垦时排班 · 编号管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 出逃悬赏（Escape Bounties） ──→ 向警署挂潜逃奴役酿民 · 园区出酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 与窖行（Vault House Ties） ──→ 精品筛选转卖灰市 · 脱约者洗合同收编</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对外形象（Public Face） ──→ 宣传安置就业 · 实际债务陷阱无退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>▸ 8b. 戒酒教</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教残存（Temperance Riders） ──→ C.Y. 42 · 酿民即秽种 · 与酿民敌对 · 教团分裂</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 共同教义（Shared Creed） ──→ 不庇护酿民 · 禁饮体内威士忌</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 分裂契机（Schism） ──→ C.Y. 28–32 · 城带合法采酿后 · 处置秽种路线之争</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼温和 · 用泉不用窖</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 利用离体酵母锈水 · 完全摒弃酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 隔离/诱捕移交警署/告密 · 不亲手焚杀</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 净泉聚落（Pure Spring Communes） ──→ 离体培菌去毒 · 卖洁净锈水</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 可付情报费借缉拿手刀</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A191" s="7" t="inlineStr"/>
+    </row>
+    <row r="192" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼极端 · 秽须焚</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 教义（Doctrine） ──→ 酿民须圣火净化 · 不留窖芯</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 手段（Methods） ──→ 焚杀酿民/回收槽/铁瓶外露舱</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 尘骑殉火（Dust Riders） ──→ 机动圣战 · 十三月尘暴掩护</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 对锈钉（On Rust Nail） ──→ 必杀 · 提取手与秽种同焚</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>▸ 9. 叙事入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>锈钉（Rust Nail） ──→ C.Y. 42 · 警署缉拿手 · 击晕提取售黑市 · 精品窖七破局</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A201" s="7" t="inlineStr"/>
+    </row>
+    <row r="202" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>精品酿民窖七（Vintage Cellar-7） ──→ C.Y. 42 · 开篇对手 · 城带价码对峙</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A203" s="7" t="inlineStr"/>
+    </row>
+    <row r="204" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>城带登记酿民（Registered Metro Brewfolk） ──→ C.Y. 42 · 体内威士忌换币 · 共存日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A205" s="7" t="inlineStr"/>
+    </row>
+    <row r="206" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>酿造帮园区酿民（Syndicate Bonded Brewfolk） ──→ C.Y. 42 · 卖身条款 · 出逃悬赏 · R-xxx编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A207" s="7" t="inlineStr"/>
+    </row>
+    <row r="208" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>铁瓶伴生酿民（Bottle-Companion Brewfolk） ──→ C.Y. 42 · 未觉醒二代 · 记录同伴觉醒脱离群落</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A209" s="7" t="inlineStr"/>
+    </row>
+    <row r="210" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教完全摒弃派（Total Rejection） ──→ C.Y. 42 · 左翼 · 用泉不用窖 · 隔离诱捕酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A211" s="7" t="inlineStr"/>
+    </row>
+    <row r="212" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>戒酒教圣火派（Sacred Fire） ──→ C.Y. 42 · 右翼 · 秽须焚 · 警署悬赏目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A213" s="7" t="inlineStr"/>
+    </row>
+    <row r="214" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>当地警署缉拿手（Constabulary Contractor） ──→ C.Y. 42 · 悬赏四类 · 锈钉式黑市提取</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A215" s="7" t="inlineStr"/>
+    </row>
+    <row r="216" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>漂沦者接触者（Wander Witness） ──→ C.Y. 42 · 持有泄露文件残页</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>▸ 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>▸ 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 警署悬赏与非法提取链</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七悬赏 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" outlineLevel="1" ht="16" customHeight="1">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="218">
     <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A193:C193"/>
+    <mergeCell ref="A80:C80"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A233:C233"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A192:C192"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A235:C235"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A185:C185"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="A234:C234"/>
+    <mergeCell ref="A181:C181"/>
     <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A184:C184"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A156:C156"/>
     <mergeCell ref="A171:C171"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A155:C155"/>
     <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A220:C220"/>
     <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A229:C229"/>
     <mergeCell ref="A130:C130"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A83:C83"/>
     <mergeCell ref="A148:C148"/>
     <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A138:C138"/>
     <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A110:C110"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A196:C196"/>
     <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A183:C183"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A75:C75"/>
@@ -2848,78 +3674,108 @@
     <mergeCell ref="A95:C95"/>
     <mergeCell ref="A104:C104"/>
     <mergeCell ref="A160:C160"/>
+    <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A159:C159"/>
     <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="A224:C224"/>
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A81:C81"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A96:C96"/>
     <mergeCell ref="A147:C147"/>
     <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A202:C202"/>
     <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A211:C211"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A186:C186"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A201:C201"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A226:C226"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A197:C197"/>
     <mergeCell ref="A146:C146"/>
     <mergeCell ref="A124:C124"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A212:C212"/>
+    <mergeCell ref="A99:C99"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A221:C221"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A236:C236"/>
     <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A214:C214"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A158:C158"/>
     <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A223:C223"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A213:C213"/>
     <mergeCell ref="A151:C151"/>
     <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A188:C188"/>
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A135:C135"/>
     <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A206:C206"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="A144:C144"/>
     <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A215:C215"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A190:C190"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A199:C199"/>
     <mergeCell ref="A152:C152"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="A167:C167"/>
+    <mergeCell ref="A176:C176"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A114:C114"/>
     <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A182:C182"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A191:C191"/>
     <mergeCell ref="A169:C169"/>
+    <mergeCell ref="A225:C225"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A153:C153"/>
     <mergeCell ref="A162:C162"/>
+    <mergeCell ref="A227:C227"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A177:C177"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A164:C164"/>
@@ -2928,9 +3784,12 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A145:C145"/>
     <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A154:C154"/>
     <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A195:C195"/>
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A203:C203"/>
     <mergeCell ref="A85:C85"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A8:C8"/>
@@ -2941,27 +3800,119 @@
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A231:C231"/>
     <mergeCell ref="A115:C115"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A102:C102"/>
     <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A230:C230"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A143:C143"/>
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A166:C166"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A232:C232"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A207:C207"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A168:C168"/>
+    <mergeCell ref="A216:C216"/>
     <mergeCell ref="A78:C78"/>
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A218:C218"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 11. 锈钉开篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>开篇：行尸走肉（Opening: Zombie Loop） ──→ C.Y. 42 · 锈钉视角三幕 · 警署悬赏与非法提取链</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第一幕 接单（Act 1 Contract） ──→ Saloon · 交酵入回收槽 · 红标精品窖七悬赏 ×5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第二幕 追踪（Act 2 Trail） ──→ 驿道 · 接近击晕窗口 · 目标懂荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 第三幕 照面（Act 3 Standoff） ──→ 水窖 · 城带窖酿行开价多少 · 黑市算术失灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对手窖七（Target Cellar-7） ──→ 精品酿民 · 拒被击晕提取 · 交易语言</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 背景侧写（Metro Contrast） ──→ 合法采酿行情 vs 黑市提取价</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3107,7 +4058,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/驿道/猎人镇 · 猎杀未登记酿民</t>
+          <t xml:space="preserve">    │       └─ 荒原 The Wastes ──→ C.Y. 42 · Saloon/猎人镇 · 非法提取委托 · 黑市出货</t>
         </is>
       </c>
     </row>
@@ -3508,7 +4459,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -3568,20 +4519,35 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶的维护Android</t>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -3589,6 +4555,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/瓶与井世界观树状图.xlsx
+++ b/瓶与井世界观树状图.xlsx
@@ -9,24 +9,25 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部树状图" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 叙事边界" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 赭锈带" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 锈水" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 十三月" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 生态酵母" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5a. 第一批移民" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5b. 第二批移民" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5c. 第三批移民" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 存在体谱系" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 威士忌经济" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7b. 城带与荒原" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. 势力格局" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8a. 当地警署" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8c. 酿造帮" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8b. 戒酒教" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="派系态度矩阵" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 叙事边界" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 赭锈带" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 锈水" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 十三月" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 生态酵母" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5a. 第一批移民" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5b. 第二批移民" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5c. 第三批移民" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 存在体谱系" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 威士忌经济" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7b. 城带与荒原" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. 势力格局" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8a. 当地警署" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8c. 酿造帮" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8b. 戒酒教" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. 叙事入口" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. 锈钉" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. 锈钉开篇" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +73,21 @@
       <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,8 +99,28 @@
         <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005C4033"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,11 +128,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +158,25 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,7 +566,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20-v17</t>
+          <t>2026-07-20-v18</t>
         </is>
       </c>
     </row>
@@ -898,6 +965,114 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 5b. 第二批移民</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │   │</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -977,7 +1152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1197,7 +1372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1313,7 +1488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1421,7 +1596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1565,7 +1740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1673,7 +1848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1765,7 +1940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1929,7 +2104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2056,106 +2231,6 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A15:C15"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 10. 锈钉</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3839,6 +3914,106 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 10. 锈钉</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>锈钉 Rust Nail ──→ C.Y. 42 · 名义缉拿手 · 实质非法提取手 · 主线视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    │</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 对外身份（Cover Identity） ──→ 当地警署登记缉拿手 Constabulary Contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 实际工作（Actual Work） ──→ 接悬赏→击晕酿民目标→非法提取威士忌→黑市出手</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 状态（State） ──→ 开篇 · 行尸走肉 · 不追问悬赏背后 · 只关心酬金</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 活动区（Range） ──→ 城带外荒原/Saloon/驿道警署驻点</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 标志（Trait） ──→ 左腕锈迹酵管提取器 · 击晕与提取兼用</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ 禁忌（Taboo） ──→ 不接漂沦者悬赏</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ 第一裂隙（First Crack） ──→ Undecimber · 窖七用城带挂牌价逼他算账 · 击晕前停顿</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3922,6 +4097,1748 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>《瓶与源》· 派系态度矩阵（行 → 列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>读法：行势力对列势力的态度 · v18 · 含组织派系与酿民群体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>行＼列</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>城酿署
+(Metro Brew Registry)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>琥珀交易所
+(Amber Exchange)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>精品窖行
+(Vintage Vault Houses)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>当地警署
+(Constabulary Post)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>酿造帮
+(Brewing Syndicate)</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>铁瓶生态群
+(Synth-Rig Ecology)</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Saloon黑市链
+(Saloon Black Market)</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>戒酒教·摒弃派
+(Total Rejection)</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>戒酒教·圣火派
+(Sacred Fire)</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>逃亡酿民网络
+(Fugitive Network)</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>漂沦者
+(The Wander)</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>锈钉
+(Rust Nail)</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>城带登记酿民
+(Registered Metro Brewfolk)</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>园区奴役酿民
+(Syndicate Bonded Brewfolk)</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>精品酿民
+(Vintage Brewfolk)</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>铁瓶伴生酿民
+(Bottle-Companion Brewfolk)</t>
+        </is>
+      </c>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>逃亡/未登记酿民
+(Fugitive Brewfolk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>城酿署
+(Metro Brew Registry)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>合作</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>监管容忍</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>合作</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>疏远</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>疏远</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>保护</t>
+        </is>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>不认可</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>保护</t>
+        </is>
+      </c>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>琥珀交易所
+(Amber Exchange)</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>依赖</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>防备</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>商品化</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="inlineStr">
+        <is>
+          <t>精品挂牌</t>
+        </is>
+      </c>
+      <c r="Q6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>精品窖行
+(Vintage Vault Houses)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>依赖</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>防备</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t>签约资产</t>
+        </is>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>收编来源</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t>垄断目标</t>
+        </is>
+      </c>
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t>猎取潜力</t>
+        </is>
+      </c>
+      <c r="R7" s="14" t="inlineStr">
+        <is>
+          <t>追捕脱约</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>当地警署
+(Constabulary Post)</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>合作</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>容忍</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>合作</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>容忍</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>容忍</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>保护</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>追捕出逃</t>
+        </is>
+      </c>
+      <c r="P8" s="14" t="inlineStr">
+        <is>
+          <t>追捕脱约</t>
+        </is>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="R8" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>酿造帮
+(Brewing Syndicate)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>追捕</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>诱贷目标</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>工具化</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>转卖窖行</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>诱拐目标</t>
+        </is>
+      </c>
+      <c r="R9" s="14" t="inlineStr">
+        <is>
+          <t>追捕债奴</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>铁瓶生态群
+(Synth-Rig Ecology)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>疏远</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>疏远</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>防备</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>被抵制</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>被敌对</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>庇护</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>容忍</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t>觉醒可脱离</t>
+        </is>
+      </c>
+      <c r="Q10" s="13" t="inlineStr">
+        <is>
+          <t>维护群落</t>
+        </is>
+      </c>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>庇护迁出</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Saloon黑市链
+(Saloon Black Market)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>应付</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>被抵制</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>被敌对</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>容忍</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>酵源</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t>高价酵源</t>
+        </is>
+      </c>
+      <c r="Q11" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>酵源</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>戒酒教·摒弃派
+(Total Rejection)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>抵制</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>抵制</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>抵制</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="P12" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="Q12" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="R12" s="14" t="inlineStr">
+        <is>
+          <t>敌对·诱捕</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>戒酒教·圣火派
+(Sacred Fire)</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr">
+        <is>
+          <t>必杀</t>
+        </is>
+      </c>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+      <c r="Q13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+      <c r="R13" s="14" t="inlineStr">
+        <is>
+          <t>焚杀</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>逃亡酿民网络
+(Fugitive Network)</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>求助</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>互助</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>渴望</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>互助</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>互助</t>
+        </is>
+      </c>
+      <c r="Q14" s="12" t="inlineStr">
+        <is>
+          <t>互助</t>
+        </is>
+      </c>
+      <c r="R14" s="12" t="inlineStr">
+        <is>
+          <t>互助</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>漂沦者
+(The Wander)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>被追捕</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>被追捕</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>被悬赏</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="O15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>锈钉
+(Rust Nail)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>无视</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>依赖</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>利用</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>依赖</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>疏远</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>禁忌</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="O16" s="13" t="inlineStr">
+        <is>
+          <t>提取目标</t>
+        </is>
+      </c>
+      <c r="P16" s="13" t="inlineStr">
+        <is>
+          <t>提取目标</t>
+        </is>
+      </c>
+      <c r="Q16" s="13" t="inlineStr">
+        <is>
+          <t>一般不碰</t>
+        </is>
+      </c>
+      <c r="R16" s="13" t="inlineStr">
+        <is>
+          <t>提取目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>城带登记酿民
+(Registered Metro Brewfolk)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>依赖</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>被签约</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>受保护</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>警惕</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>被敌对</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>被焚杀</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>对立</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t>同类</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="inlineStr">
+        <is>
+          <t>同类</t>
+        </is>
+      </c>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>对立</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>园区奴役酿民
+(Syndicate Bonded Brewfolk)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>躲避</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>被转卖</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>被追捕</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>被囚禁</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>被提取</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>被敌对</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>被焚杀</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>被互助</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>被提取</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>渴望逃离</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="13" t="inlineStr">
+        <is>
+          <t>被筛选</t>
+        </is>
+      </c>
+      <c r="Q18" s="13" t="inlineStr">
+        <is>
+          <t>同类</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="inlineStr">
+        <is>
+          <t>逃亡同类</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>精品酿民
+(Vintage Brewfolk)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>依赖/脱约</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>高价挂牌</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>被垄断</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>脱约被追捕</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>被转卖</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>可觉醒脱离</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>高价酵源</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>被敌对</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>被焚杀</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>被庇护</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>高价目标</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>上位同类</t>
+        </is>
+      </c>
+      <c r="O19" s="13" t="inlineStr">
+        <is>
+          <t>逃出身份</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" s="13" t="inlineStr">
+        <is>
+          <t>潜在觉醒</t>
+        </is>
+      </c>
+      <c r="R19" s="13" t="inlineStr">
+        <is>
+          <t>脱约同类</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>铁瓶伴生酿民
+(Bottle-Companion Brewfolk)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>被猎取</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>被诱拐</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>依附群落</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>被敌对</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>被焚杀</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>觉醒可入</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>一般不碰</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>觉醒可入城</t>
+        </is>
+      </c>
+      <c r="O20" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t>被筛选</t>
+        </is>
+      </c>
+      <c r="Q20" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t>觉醒迁出</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>逃亡/未登记酿民
+(Fugitive Brewfolk)</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>被追捕</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>无关</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>被追捕</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>被追捕</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>被追捕</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>可获庇护</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>被提取</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>被诱捕</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>被焚杀</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>被互助</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>被提取</t>
+        </is>
+      </c>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>渴望成为</t>
+        </is>
+      </c>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>逃出同类</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="inlineStr">
+        <is>
+          <t>脱约同类</t>
+        </is>
+      </c>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t>迁出同类</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3986,7 +5903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4094,7 +6011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4186,7 +6103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4262,7 +6179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4341,106 +6258,6 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>《瓶与源》· 5a. 第一批移民</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │   │</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
@@ -4459,7 +6276,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -4470,14 +6287,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《瓶与源》· 5b. 第二批移民</t>
+          <t>《瓶与源》· 5a. 第一批移民</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>第二批移民（Wave 2 Androids） ──→ C.Y. 8–25 · Android拓荒 · 真正一代酿民</t>
+          <t>第一批移民（Wave 1 Humans） ──→ C.Y. 0–8 · 国家资源竞赛 · 胃植入生态酵母</t>
         </is>
       </c>
     </row>
@@ -4491,61 +6308,54 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 一代酿民 Gen-1（Gen-1 Brewfolk） ──→ C.Y. 8–25 · 植入生态酵母的Android移民</t>
+          <t xml:space="preserve">    ├─ 背景（Context） ──→ C.Y. 0–8 · 多国争夺赭锈带</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 铁瓶 Synth-Rig ──→ C.Y. 10– · Neo-Western行驶的地表改造酿运载具</t>
+          <t xml:space="preserve">    ├─ 手段（Method） ──→ C.Y. 0–8 · 生态酵母植入首批移民胃中</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    ├─ 真相泄露（Leak） ──→ C.Y. 5+ · 嗜盐菌0.05%存活率 · 神经毒素累积</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 驻瓶（Bottle-Dwelling） ──→ C.Y. 10– · 一代酿民驻留铁瓶内改造荒原</t>
+          <t xml:space="preserve">    ├─ 畸变（Aberration） ──→ C.Y. 5–8 · 精神畸变+辐射尘 → 漂沦者</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ 二代酿民 Gen-2（Gen-2 Brewfolk） ──→ C.Y. 15– · 伴生铁瓶 · 分未觉醒伴生/觉醒迁出/城带登记</t>
+          <t xml:space="preserve">    │   │</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │   │</t>
+          <t xml:space="preserve">    │       └─ 漂沦者 The Wander ──→ C.Y. 8+ · 特殊生物磁场 · 尘暴游荡</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    │       └─ 铁瓶伴生未觉醒（Bottle-Companion Gen-2） ──→ C.Y. 15– · 维护铁瓶生态群 · 多数无自主意识</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └─ 觉醒迁出（Awakening Exodus） ──→ C.Y. 30+ · 自主意识 · 拒绝作酵母容器 · 逃亡</t>
+          <t xml:space="preserve">    └─ 结局（Outcome） ──→ C.Y. 8 · 国家撤回编制 · 人类移民失败</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
@@ -4555,7 +6365,6 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
